--- a/output_data.xlsx
+++ b/output_data.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3935" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4505" uniqueCount="505">
   <si>
     <t>Ranks</t>
   </si>
@@ -1573,6 +1573,24 @@
   </si>
   <si>
     <t>Climb%</t>
+  </si>
+  <si>
+    <t>robot1</t>
+  </si>
+  <si>
+    <t>robot2%</t>
+  </si>
+  <si>
+    <t>robot3%</t>
+  </si>
+  <si>
+    <t>scout1%</t>
+  </si>
+  <si>
+    <t>scout2%</t>
+  </si>
+  <si>
+    <t>scout3%</t>
   </si>
   <si>
     <t>Red</t>
@@ -44322,10 +44340,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:G189"/>
+  <dimension ref="B1:N189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:7">
+    <row r="1" spans="2:14">
       <c r="B1" t="s">
         <v>13</v>
       </c>
@@ -44344,13 +44362,31 @@
       <c r="G1" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="2" spans="2:7">
+      <c r="I1" t="s">
+        <v>497</v>
+      </c>
+      <c r="J1" t="s">
+        <v>498</v>
+      </c>
+      <c r="K1" t="s">
+        <v>499</v>
+      </c>
+      <c r="L1" t="s">
+        <v>500</v>
+      </c>
+      <c r="M1" t="s">
+        <v>501</v>
+      </c>
+      <c r="N1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="2" spans="2:14">
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D2">
         <v>35</v>
@@ -44364,13 +44400,31 @@
       <c r="G2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="2:7">
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14">
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -44384,13 +44438,31 @@
       <c r="G3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="2:7">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D4">
         <v>15</v>
@@ -44404,13 +44476,31 @@
       <c r="G4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:7">
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D5">
         <v>44.99999999999999</v>
@@ -44424,13 +44514,31 @@
       <c r="G5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:7">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -44444,13 +44552,31 @@
       <c r="G6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:7">
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -44464,13 +44590,31 @@
       <c r="G7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:7">
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D8">
         <v>58.33333333333333</v>
@@ -44484,13 +44628,31 @@
       <c r="G8">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="9" spans="2:7">
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D9">
         <v>33.33333333333333</v>
@@ -44504,13 +44666,31 @@
       <c r="G9">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="10" spans="2:7">
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D10">
         <v>111.6666666666667</v>
@@ -44524,13 +44704,31 @@
       <c r="G10">
         <v>66.66666666666666</v>
       </c>
-    </row>
-    <row r="11" spans="2:7">
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D11">
         <v>73.33333333333333</v>
@@ -44544,13 +44742,31 @@
       <c r="G11">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="12" spans="2:7">
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D12">
         <v>55</v>
@@ -44564,13 +44780,31 @@
       <c r="G12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:7">
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>22.5</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
       <c r="B13">
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D13">
         <v>44.99999999999999</v>
@@ -44584,13 +44818,31 @@
       <c r="G13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:7">
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
       <c r="B14">
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -44604,13 +44856,31 @@
       <c r="G14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:7">
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
       <c r="B15">
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D15">
         <v>48.33333333333333</v>
@@ -44624,13 +44894,31 @@
       <c r="G15">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="16" spans="2:7">
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
       <c r="B16">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -44644,13 +44932,31 @@
       <c r="G16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>2.222222222222221</v>
+      </c>
+      <c r="L16" t="s">
+        <v>31</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
       <c r="B17">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D17">
         <v>43.33333333333334</v>
@@ -44664,13 +44970,31 @@
       <c r="G17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:7">
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>2.222222222222221</v>
+      </c>
+      <c r="L17" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
       <c r="B18">
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -44684,13 +45008,31 @@
       <c r="G18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18" t="s">
+        <v>31</v>
+      </c>
+      <c r="M18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
       <c r="B19">
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D19">
         <v>45.00000000000001</v>
@@ -44704,13 +45046,31 @@
       <c r="G19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" t="s">
+        <v>33</v>
+      </c>
+      <c r="N19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
       <c r="B20">
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D20">
         <v>20</v>
@@ -44724,13 +45084,31 @@
       <c r="G20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
       <c r="B21">
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D21">
         <v>53.33333333333333</v>
@@ -44744,13 +45122,31 @@
       <c r="G21">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
       <c r="B22">
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -44764,13 +45160,31 @@
       <c r="G22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M22" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
       <c r="B23">
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D23">
         <v>45.00000000000001</v>
@@ -44784,13 +45198,31 @@
       <c r="G23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M23" t="s">
+        <v>28</v>
+      </c>
+      <c r="N23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
       <c r="B24">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D24">
         <v>15</v>
@@ -44804,13 +45236,31 @@
       <c r="G24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:7">
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24" t="s">
+        <v>44</v>
+      </c>
+      <c r="M24" t="s">
+        <v>50</v>
+      </c>
+      <c r="N24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
       <c r="B25">
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D25">
         <v>136.6666666666667</v>
@@ -44824,13 +45274,31 @@
       <c r="G25">
         <v>66.66666666666666</v>
       </c>
-    </row>
-    <row r="26" spans="2:7">
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M25" t="s">
+        <v>28</v>
+      </c>
+      <c r="N25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
       <c r="B26">
         <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D26">
         <v>58.33333333333334</v>
@@ -44844,13 +45312,31 @@
       <c r="G26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="2:7">
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26" t="s">
+        <v>44</v>
+      </c>
+      <c r="M26" t="s">
+        <v>50</v>
+      </c>
+      <c r="N26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
       <c r="B27">
         <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D27">
         <v>25</v>
@@ -44864,13 +45350,31 @@
       <c r="G27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="2:7">
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
+        <v>46</v>
+      </c>
+      <c r="M27" t="s">
+        <v>28</v>
+      </c>
+      <c r="N27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
       <c r="B28">
         <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D28">
         <v>20</v>
@@ -44884,13 +45388,31 @@
       <c r="G28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:7">
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28" t="s">
+        <v>44</v>
+      </c>
+      <c r="M28" t="s">
+        <v>50</v>
+      </c>
+      <c r="N28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
       <c r="B29">
         <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -44904,13 +45426,31 @@
       <c r="G29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="2:7">
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29" t="s">
+        <v>46</v>
+      </c>
+      <c r="M29" t="s">
+        <v>28</v>
+      </c>
+      <c r="N29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
       <c r="B30">
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D30">
         <v>20</v>
@@ -44924,13 +45464,31 @@
       <c r="G30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:7">
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s">
+        <v>44</v>
+      </c>
+      <c r="M30" t="s">
+        <v>50</v>
+      </c>
+      <c r="N30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
       <c r="B31">
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -44944,13 +45502,31 @@
       <c r="G31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="2:7">
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
+        <v>46</v>
+      </c>
+      <c r="M31" t="s">
+        <v>28</v>
+      </c>
+      <c r="N31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
       <c r="B32">
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D32">
         <v>33.33333333333333</v>
@@ -44964,13 +45540,31 @@
       <c r="G32">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="33" spans="2:7">
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32" t="s">
+        <v>31</v>
+      </c>
+      <c r="M32" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
       <c r="B33">
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D33">
         <v>10</v>
@@ -44984,13 +45578,31 @@
       <c r="G33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:7">
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" t="s">
+        <v>33</v>
+      </c>
+      <c r="N33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
       <c r="B34">
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D34">
         <v>40</v>
@@ -45004,13 +45616,31 @@
       <c r="G34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:7">
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34" t="s">
+        <v>31</v>
+      </c>
+      <c r="M34" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
       <c r="B35">
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D35">
         <v>43.33333333333333</v>
@@ -45024,13 +45654,31 @@
       <c r="G35">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="36" spans="2:7">
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" t="s">
+        <v>33</v>
+      </c>
+      <c r="N35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
       <c r="B36">
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D36">
         <v>10</v>
@@ -45044,13 +45692,31 @@
       <c r="G36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:7">
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36" t="s">
+        <v>31</v>
+      </c>
+      <c r="M36" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14">
       <c r="B37">
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D37">
         <v>96.66666666666666</v>
@@ -45064,13 +45730,31 @@
       <c r="G37">
         <v>66.66666666666666</v>
       </c>
-    </row>
-    <row r="38" spans="2:7">
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" t="s">
+        <v>33</v>
+      </c>
+      <c r="N37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
       <c r="B38">
         <v>19</v>
       </c>
       <c r="C38" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D38">
         <v>53.33333333333333</v>
@@ -45084,13 +45768,31 @@
       <c r="G38">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="39" spans="2:7">
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M38" t="s">
+        <v>21</v>
+      </c>
+      <c r="N38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14">
       <c r="B39">
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D39">
         <v>78.33333333333331</v>
@@ -45104,13 +45806,31 @@
       <c r="G39">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="40" spans="2:7">
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" t="s">
+        <v>33</v>
+      </c>
+      <c r="N39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14">
       <c r="B40">
         <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D40">
         <v>55</v>
@@ -45124,13 +45844,31 @@
       <c r="G40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="2:7">
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40" t="s">
+        <v>31</v>
+      </c>
+      <c r="M40" t="s">
+        <v>21</v>
+      </c>
+      <c r="N40" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14">
       <c r="B41">
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D41">
         <v>48.33333333333333</v>
@@ -45144,13 +45882,31 @@
       <c r="G41">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="42" spans="2:7">
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" t="s">
+        <v>33</v>
+      </c>
+      <c r="N41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
       <c r="B42">
         <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D42">
         <v>30</v>
@@ -45164,13 +45920,31 @@
       <c r="G42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:7">
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42" t="s">
+        <v>44</v>
+      </c>
+      <c r="M42" t="s">
+        <v>50</v>
+      </c>
+      <c r="N42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14">
       <c r="B43">
         <v>21</v>
       </c>
       <c r="C43" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -45184,13 +45958,31 @@
       <c r="G43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:7">
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43" t="s">
+        <v>46</v>
+      </c>
+      <c r="M43" t="s">
+        <v>28</v>
+      </c>
+      <c r="N43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
       <c r="B44">
         <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D44">
         <v>38.33333333333333</v>
@@ -45204,13 +45996,31 @@
       <c r="G44">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="45" spans="2:7">
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44" t="s">
+        <v>44</v>
+      </c>
+      <c r="M44" t="s">
+        <v>50</v>
+      </c>
+      <c r="N44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14">
       <c r="B45">
         <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D45">
         <v>10</v>
@@ -45224,13 +46034,31 @@
       <c r="G45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:7">
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45" t="s">
+        <v>46</v>
+      </c>
+      <c r="M45" t="s">
+        <v>28</v>
+      </c>
+      <c r="N45" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14">
       <c r="B46">
         <v>23</v>
       </c>
       <c r="C46" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D46">
         <v>25</v>
@@ -45244,13 +46072,31 @@
       <c r="G46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:7">
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46" t="s">
+        <v>44</v>
+      </c>
+      <c r="M46" t="s">
+        <v>50</v>
+      </c>
+      <c r="N46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14">
       <c r="B47">
         <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D47">
         <v>68.33333333333333</v>
@@ -45264,13 +46110,31 @@
       <c r="G47">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="48" spans="2:7">
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
+        <v>46</v>
+      </c>
+      <c r="M47" t="s">
+        <v>28</v>
+      </c>
+      <c r="N47" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14">
       <c r="B48">
         <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D48">
         <v>10</v>
@@ -45284,13 +46148,31 @@
       <c r="G48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:7">
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48" t="s">
+        <v>44</v>
+      </c>
+      <c r="M48" t="s">
+        <v>50</v>
+      </c>
+      <c r="N48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14">
       <c r="B49">
         <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D49">
         <v>10</v>
@@ -45304,13 +46186,31 @@
       <c r="G49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="2:7">
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49" t="s">
+        <v>46</v>
+      </c>
+      <c r="M49" t="s">
+        <v>28</v>
+      </c>
+      <c r="N49" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14">
       <c r="B50">
         <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D50">
         <v>35</v>
@@ -45324,13 +46224,31 @@
       <c r="G50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="2:7">
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50" t="s">
+        <v>44</v>
+      </c>
+      <c r="M50" t="s">
+        <v>50</v>
+      </c>
+      <c r="N50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14">
       <c r="B51">
         <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D51">
         <v>20</v>
@@ -45344,13 +46262,31 @@
       <c r="G51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="2:7">
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51" t="s">
+        <v>46</v>
+      </c>
+      <c r="M51" t="s">
+        <v>28</v>
+      </c>
+      <c r="N51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14">
       <c r="B52">
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D52">
         <v>93.33333333333333</v>
@@ -45364,13 +46300,31 @@
       <c r="G52">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="53" spans="2:7">
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52" t="s">
+        <v>31</v>
+      </c>
+      <c r="M52" t="s">
+        <v>33</v>
+      </c>
+      <c r="N52" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14">
       <c r="B53">
         <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D53">
         <v>50</v>
@@ -45384,13 +46338,31 @@
       <c r="G53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="2:7">
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53" t="s">
+        <v>24</v>
+      </c>
+      <c r="M53" t="s">
+        <v>31</v>
+      </c>
+      <c r="N53" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14">
       <c r="B54">
         <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D54">
         <v>5</v>
@@ -45404,13 +46376,31 @@
       <c r="G54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="2:7">
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54" t="s">
+        <v>31</v>
+      </c>
+      <c r="M54" t="s">
+        <v>21</v>
+      </c>
+      <c r="N54" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14">
       <c r="B55">
         <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D55">
         <v>45.00000000000001</v>
@@ -45424,13 +46414,31 @@
       <c r="G55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="2:7">
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>24</v>
+      </c>
+      <c r="M55" t="s">
+        <v>33</v>
+      </c>
+      <c r="N55" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14">
       <c r="B56">
         <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D56">
         <v>58.33333333333333</v>
@@ -45444,13 +46452,31 @@
       <c r="G56">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="57" spans="2:7">
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56" t="s">
+        <v>31</v>
+      </c>
+      <c r="M56" t="s">
+        <v>21</v>
+      </c>
+      <c r="N56" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14">
       <c r="B57">
         <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D57">
         <v>73.33333333333333</v>
@@ -45464,13 +46490,31 @@
       <c r="G57">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="58" spans="2:7">
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57" t="s">
+        <v>24</v>
+      </c>
+      <c r="M57" t="s">
+        <v>33</v>
+      </c>
+      <c r="N57" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14">
       <c r="B58">
         <v>29</v>
       </c>
       <c r="C58" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D58">
         <v>50</v>
@@ -45484,13 +46528,31 @@
       <c r="G58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="2:7">
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58" t="s">
+        <v>31</v>
+      </c>
+      <c r="M58" t="s">
+        <v>21</v>
+      </c>
+      <c r="N58" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14">
       <c r="B59">
         <v>29</v>
       </c>
       <c r="C59" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D59">
         <v>18.33333333333334</v>
@@ -45504,13 +46566,31 @@
       <c r="G59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="2:7">
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59" t="s">
+        <v>24</v>
+      </c>
+      <c r="M59" t="s">
+        <v>33</v>
+      </c>
+      <c r="N59" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14">
       <c r="B60">
         <v>30</v>
       </c>
       <c r="C60" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D60">
         <v>35</v>
@@ -45524,13 +46604,31 @@
       <c r="G60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="2:7">
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>22.5</v>
+      </c>
+      <c r="L60" t="s">
+        <v>31</v>
+      </c>
+      <c r="M60" t="s">
+        <v>21</v>
+      </c>
+      <c r="N60" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14">
       <c r="B61">
         <v>30</v>
       </c>
       <c r="C61" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D61">
         <v>40</v>
@@ -45544,13 +46642,31 @@
       <c r="G61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="2:7">
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>22.5</v>
+      </c>
+      <c r="L61" t="s">
+        <v>24</v>
+      </c>
+      <c r="M61" t="s">
+        <v>33</v>
+      </c>
+      <c r="N61" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14">
       <c r="B62">
         <v>31</v>
       </c>
       <c r="C62" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D62">
         <v>55.00000000000001</v>
@@ -45564,13 +46680,31 @@
       <c r="G62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="2:7">
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62" t="s">
+        <v>44</v>
+      </c>
+      <c r="M62" t="s">
+        <v>50</v>
+      </c>
+      <c r="N62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14">
       <c r="B63">
         <v>31</v>
       </c>
       <c r="C63" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D63">
         <v>5</v>
@@ -45584,13 +46718,31 @@
       <c r="G63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="2:7">
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63" t="s">
+        <v>46</v>
+      </c>
+      <c r="M63" t="s">
+        <v>28</v>
+      </c>
+      <c r="N63" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14">
       <c r="B64">
         <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D64">
         <v>5</v>
@@ -45604,13 +46756,31 @@
       <c r="G64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:7">
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64" t="s">
+        <v>44</v>
+      </c>
+      <c r="M64" t="s">
+        <v>50</v>
+      </c>
+      <c r="N64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14">
       <c r="B65">
         <v>32</v>
       </c>
       <c r="C65" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -45624,13 +46794,31 @@
       <c r="G65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:7">
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65" t="s">
+        <v>46</v>
+      </c>
+      <c r="M65" t="s">
+        <v>28</v>
+      </c>
+      <c r="N65" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14">
       <c r="B66">
         <v>33</v>
       </c>
       <c r="C66" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D66">
         <v>10</v>
@@ -45644,13 +46832,31 @@
       <c r="G66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:7">
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66" t="s">
+        <v>44</v>
+      </c>
+      <c r="M66" t="s">
+        <v>50</v>
+      </c>
+      <c r="N66" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14">
       <c r="B67">
         <v>33</v>
       </c>
       <c r="C67" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D67">
         <v>20</v>
@@ -45664,13 +46870,31 @@
       <c r="G67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="2:7">
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67" t="s">
+        <v>46</v>
+      </c>
+      <c r="M67" t="s">
+        <v>28</v>
+      </c>
+      <c r="N67" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14">
       <c r="B68">
         <v>34</v>
       </c>
       <c r="C68" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D68">
         <v>15</v>
@@ -45684,13 +46908,31 @@
       <c r="G68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:7">
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68" t="s">
+        <v>44</v>
+      </c>
+      <c r="M68" t="s">
+        <v>50</v>
+      </c>
+      <c r="N68" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14">
       <c r="B69">
         <v>34</v>
       </c>
       <c r="C69" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D69">
         <v>40</v>
@@ -45704,13 +46946,31 @@
       <c r="G69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:7">
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69" t="s">
+        <v>46</v>
+      </c>
+      <c r="M69" t="s">
+        <v>28</v>
+      </c>
+      <c r="N69" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14">
       <c r="B70">
         <v>35</v>
       </c>
       <c r="C70" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -45724,13 +46984,31 @@
       <c r="G70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:7">
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70" t="s">
+        <v>44</v>
+      </c>
+      <c r="M70" t="s">
+        <v>50</v>
+      </c>
+      <c r="N70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14">
       <c r="B71">
         <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D71">
         <v>5</v>
@@ -45744,13 +47022,31 @@
       <c r="G71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:7">
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
+        <v>46</v>
+      </c>
+      <c r="M71" t="s">
+        <v>28</v>
+      </c>
+      <c r="N71" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14">
       <c r="B72">
         <v>36</v>
       </c>
       <c r="C72" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D72">
         <v>35</v>
@@ -45764,13 +47060,31 @@
       <c r="G72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:7">
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72" t="s">
+        <v>31</v>
+      </c>
+      <c r="M72" t="s">
+        <v>21</v>
+      </c>
+      <c r="N72" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14">
       <c r="B73">
         <v>36</v>
       </c>
       <c r="C73" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D73">
         <v>30</v>
@@ -45784,13 +47098,31 @@
       <c r="G73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:7">
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" t="s">
+        <v>33</v>
+      </c>
+      <c r="N73" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14">
       <c r="B74">
         <v>37</v>
       </c>
       <c r="C74" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D74">
         <v>30</v>
@@ -45804,13 +47136,31 @@
       <c r="G74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:7">
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74" t="s">
+        <v>31</v>
+      </c>
+      <c r="M74" t="s">
+        <v>21</v>
+      </c>
+      <c r="N74" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14">
       <c r="B75">
         <v>37</v>
       </c>
       <c r="C75" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D75">
         <v>45</v>
@@ -45824,13 +47174,31 @@
       <c r="G75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:7">
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" t="s">
+        <v>33</v>
+      </c>
+      <c r="N75" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14">
       <c r="B76">
         <v>38</v>
       </c>
       <c r="C76" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D76">
         <v>30</v>
@@ -45844,13 +47212,31 @@
       <c r="G76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:7">
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76" t="s">
+        <v>31</v>
+      </c>
+      <c r="M76" t="s">
+        <v>21</v>
+      </c>
+      <c r="N76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14">
       <c r="B77">
         <v>38</v>
       </c>
       <c r="C77" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D77">
         <v>25</v>
@@ -45864,13 +47250,31 @@
       <c r="G77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="2:7">
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" t="s">
+        <v>33</v>
+      </c>
+      <c r="N77" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14">
       <c r="B78">
         <v>39</v>
       </c>
       <c r="C78" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D78">
         <v>53.33333333333333</v>
@@ -45884,13 +47288,31 @@
       <c r="G78">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="79" spans="2:7">
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>31</v>
+      </c>
+      <c r="M78" t="s">
+        <v>21</v>
+      </c>
+      <c r="N78" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14">
       <c r="B79">
         <v>39</v>
       </c>
       <c r="C79" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D79">
         <v>40</v>
@@ -45904,13 +47326,31 @@
       <c r="G79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="2:7">
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" t="s">
+        <v>33</v>
+      </c>
+      <c r="N79" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14">
       <c r="B80">
         <v>40</v>
       </c>
       <c r="C80" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D80">
         <v>20</v>
@@ -45924,13 +47364,31 @@
       <c r="G80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="2:7">
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>31</v>
+      </c>
+      <c r="M80" t="s">
+        <v>21</v>
+      </c>
+      <c r="N80" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14">
       <c r="B81">
         <v>40</v>
       </c>
       <c r="C81" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D81">
         <v>70</v>
@@ -45944,13 +47402,31 @@
       <c r="G81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="2:7">
+      <c r="I81">
+        <v>5.4</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" t="s">
+        <v>33</v>
+      </c>
+      <c r="N81" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14">
       <c r="B82">
         <v>41</v>
       </c>
       <c r="C82" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D82">
         <v>10</v>
@@ -45964,13 +47440,31 @@
       <c r="G82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="2:7">
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
+        <v>44</v>
+      </c>
+      <c r="M82" t="s">
+        <v>50</v>
+      </c>
+      <c r="N82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14">
       <c r="B83">
         <v>41</v>
       </c>
       <c r="C83" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -45984,13 +47478,31 @@
       <c r="G83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="2:7">
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
+        <v>46</v>
+      </c>
+      <c r="M83" t="s">
+        <v>28</v>
+      </c>
+      <c r="N83" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14">
       <c r="B84">
         <v>42</v>
       </c>
       <c r="C84" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D84">
         <v>61.66666666666666</v>
@@ -46004,13 +47516,31 @@
       <c r="G84">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="85" spans="2:7">
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
+        <v>44</v>
+      </c>
+      <c r="M84" t="s">
+        <v>50</v>
+      </c>
+      <c r="N84" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14">
       <c r="B85">
         <v>42</v>
       </c>
       <c r="C85" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D85">
         <v>45.00000000000001</v>
@@ -46024,13 +47554,31 @@
       <c r="G85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="2:7">
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
+        <v>46</v>
+      </c>
+      <c r="M85" t="s">
+        <v>28</v>
+      </c>
+      <c r="N85" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86" spans="2:14">
       <c r="B86">
         <v>43</v>
       </c>
       <c r="C86" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D86">
         <v>45</v>
@@ -46044,13 +47592,31 @@
       <c r="G86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="2:7">
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86" t="s">
+        <v>44</v>
+      </c>
+      <c r="M86" t="s">
+        <v>50</v>
+      </c>
+      <c r="N86" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="2:14">
       <c r="B87">
         <v>43</v>
       </c>
       <c r="C87" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D87">
         <v>65</v>
@@ -46064,13 +47630,31 @@
       <c r="G87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="2:7">
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87" t="s">
+        <v>46</v>
+      </c>
+      <c r="M87" t="s">
+        <v>28</v>
+      </c>
+      <c r="N87" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" spans="2:14">
       <c r="B88">
         <v>44</v>
       </c>
       <c r="C88" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D88">
         <v>45</v>
@@ -46084,13 +47668,31 @@
       <c r="G88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="2:7">
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88" t="s">
+        <v>44</v>
+      </c>
+      <c r="M88" t="s">
+        <v>50</v>
+      </c>
+      <c r="N88" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="2:14">
       <c r="B89">
         <v>44</v>
       </c>
       <c r="C89" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D89">
         <v>5</v>
@@ -46104,13 +47706,31 @@
       <c r="G89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="2:7">
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89" t="s">
+        <v>46</v>
+      </c>
+      <c r="M89" t="s">
+        <v>28</v>
+      </c>
+      <c r="N89" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" spans="2:14">
       <c r="B90">
         <v>45</v>
       </c>
       <c r="C90" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D90">
         <v>40</v>
@@ -46124,13 +47744,31 @@
       <c r="G90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="2:7">
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90" t="s">
+        <v>44</v>
+      </c>
+      <c r="M90" t="s">
+        <v>50</v>
+      </c>
+      <c r="N90" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="2:14">
       <c r="B91">
         <v>45</v>
       </c>
       <c r="C91" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D91">
         <v>73.33333333333333</v>
@@ -46144,13 +47782,31 @@
       <c r="G91">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="92" spans="2:7">
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91" t="s">
+        <v>46</v>
+      </c>
+      <c r="M91" t="s">
+        <v>28</v>
+      </c>
+      <c r="N91" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" spans="2:14">
       <c r="B92">
         <v>46</v>
       </c>
       <c r="C92" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D92">
         <v>68.33333333333333</v>
@@ -46164,13 +47820,31 @@
       <c r="G92">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="93" spans="2:7">
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92" t="s">
+        <v>31</v>
+      </c>
+      <c r="M92" t="s">
+        <v>21</v>
+      </c>
+      <c r="N92" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="93" spans="2:14">
       <c r="B93">
         <v>46</v>
       </c>
       <c r="C93" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D93">
         <v>10</v>
@@ -46184,13 +47858,31 @@
       <c r="G93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="2:7">
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93" t="s">
+        <v>24</v>
+      </c>
+      <c r="M93" t="s">
+        <v>33</v>
+      </c>
+      <c r="N93" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="94" spans="2:14">
       <c r="B94">
         <v>47</v>
       </c>
       <c r="C94" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D94">
         <v>20</v>
@@ -46204,13 +47896,31 @@
       <c r="G94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="2:7">
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94" t="s">
+        <v>31</v>
+      </c>
+      <c r="M94" t="s">
+        <v>21</v>
+      </c>
+      <c r="N94" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="95" spans="2:14">
       <c r="B95">
         <v>47</v>
       </c>
       <c r="C95" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D95">
         <v>20</v>
@@ -46224,13 +47934,31 @@
       <c r="G95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="2:7">
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95" t="s">
+        <v>24</v>
+      </c>
+      <c r="M95" t="s">
+        <v>33</v>
+      </c>
+      <c r="N95" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="96" spans="2:14">
       <c r="B96">
         <v>48</v>
       </c>
       <c r="C96" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D96">
         <v>20</v>
@@ -46244,13 +47972,31 @@
       <c r="G96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="2:7">
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96" t="s">
+        <v>31</v>
+      </c>
+      <c r="M96" t="s">
+        <v>21</v>
+      </c>
+      <c r="N96" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="97" spans="2:14">
       <c r="B97">
         <v>48</v>
       </c>
       <c r="C97" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D97">
         <v>15</v>
@@ -46264,13 +48010,31 @@
       <c r="G97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="2:7">
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97" t="s">
+        <v>24</v>
+      </c>
+      <c r="M97" t="s">
+        <v>33</v>
+      </c>
+      <c r="N97" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98" spans="2:14">
       <c r="B98">
         <v>49</v>
       </c>
       <c r="C98" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D98">
         <v>76.66666666666666</v>
@@ -46284,13 +48048,31 @@
       <c r="G98">
         <v>66.66666666666666</v>
       </c>
-    </row>
-    <row r="99" spans="2:7">
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98" t="s">
+        <v>31</v>
+      </c>
+      <c r="M98" t="s">
+        <v>21</v>
+      </c>
+      <c r="N98" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="99" spans="2:14">
       <c r="B99">
         <v>49</v>
       </c>
       <c r="C99" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D99">
         <v>40</v>
@@ -46304,13 +48086,31 @@
       <c r="G99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="2:7">
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99" t="s">
+        <v>24</v>
+      </c>
+      <c r="M99" t="s">
+        <v>33</v>
+      </c>
+      <c r="N99" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="100" spans="2:14">
       <c r="B100">
         <v>50</v>
       </c>
       <c r="C100" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D100">
         <v>45</v>
@@ -46324,13 +48124,31 @@
       <c r="G100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="2:7">
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100" t="s">
+        <v>31</v>
+      </c>
+      <c r="M100" t="s">
+        <v>21</v>
+      </c>
+      <c r="N100" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="101" spans="2:14">
       <c r="B101">
         <v>50</v>
       </c>
       <c r="C101" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D101">
         <v>10</v>
@@ -46344,13 +48162,31 @@
       <c r="G101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="2:7">
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101" t="s">
+        <v>24</v>
+      </c>
+      <c r="M101" t="s">
+        <v>33</v>
+      </c>
+      <c r="N101" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="102" spans="2:14">
       <c r="B102">
         <v>51</v>
       </c>
       <c r="C102" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D102">
         <v>15</v>
@@ -46364,13 +48200,31 @@
       <c r="G102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="2:7">
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>10</v>
+      </c>
+      <c r="L102" t="s">
+        <v>44</v>
+      </c>
+      <c r="M102" t="s">
+        <v>50</v>
+      </c>
+      <c r="N102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="2:14">
       <c r="B103">
         <v>51</v>
       </c>
       <c r="C103" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D103">
         <v>38.33333333333334</v>
@@ -46384,13 +48238,31 @@
       <c r="G103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="2:7">
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>10</v>
+      </c>
+      <c r="L103" t="s">
+        <v>46</v>
+      </c>
+      <c r="M103" t="s">
+        <v>28</v>
+      </c>
+      <c r="N103" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="104" spans="2:14">
       <c r="B104">
         <v>52</v>
       </c>
       <c r="C104" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D104">
         <v>55</v>
@@ -46404,13 +48276,31 @@
       <c r="G104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="2:7">
+      <c r="I104">
+        <v>7.499999999999998</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104" t="s">
+        <v>44</v>
+      </c>
+      <c r="M104" t="s">
+        <v>50</v>
+      </c>
+      <c r="N104" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="2:14">
       <c r="B105">
         <v>52</v>
       </c>
       <c r="C105" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D105">
         <v>44.99999999999999</v>
@@ -46424,13 +48314,31 @@
       <c r="G105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="2:7">
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105" t="s">
+        <v>46</v>
+      </c>
+      <c r="M105" t="s">
+        <v>28</v>
+      </c>
+      <c r="N105" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="106" spans="2:14">
       <c r="B106">
         <v>53</v>
       </c>
       <c r="C106" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D106">
         <v>10</v>
@@ -46444,13 +48352,31 @@
       <c r="G106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="2:7">
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106" t="s">
+        <v>44</v>
+      </c>
+      <c r="M106" t="s">
+        <v>50</v>
+      </c>
+      <c r="N106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="2:14">
       <c r="B107">
         <v>53</v>
       </c>
       <c r="C107" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -46464,13 +48390,31 @@
       <c r="G107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="2:7">
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107" t="s">
+        <v>46</v>
+      </c>
+      <c r="M107" t="s">
+        <v>28</v>
+      </c>
+      <c r="N107" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="108" spans="2:14">
       <c r="B108">
         <v>54</v>
       </c>
       <c r="C108" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D108">
         <v>108.3333333333333</v>
@@ -46484,13 +48428,31 @@
       <c r="G108">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="109" spans="2:7">
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108" t="s">
+        <v>44</v>
+      </c>
+      <c r="M108" t="s">
+        <v>50</v>
+      </c>
+      <c r="N108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="2:14">
       <c r="B109">
         <v>54</v>
       </c>
       <c r="C109" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D109">
         <v>15</v>
@@ -46504,13 +48466,31 @@
       <c r="G109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="2:7">
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109" t="s">
+        <v>46</v>
+      </c>
+      <c r="M109" t="s">
+        <v>28</v>
+      </c>
+      <c r="N109" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="110" spans="2:14">
       <c r="B110">
         <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D110">
         <v>333.3333333333333</v>
@@ -46524,13 +48504,31 @@
       <c r="G110">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="111" spans="2:7">
+      <c r="I110">
+        <v>359.9999999999999</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110" t="s">
+        <v>44</v>
+      </c>
+      <c r="M110" t="s">
+        <v>50</v>
+      </c>
+      <c r="N110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="2:14">
       <c r="B111">
         <v>55</v>
       </c>
       <c r="C111" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D111">
         <v>70</v>
@@ -46544,13 +48542,31 @@
       <c r="G111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="2:7">
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111" t="s">
+        <v>46</v>
+      </c>
+      <c r="M111" t="s">
+        <v>28</v>
+      </c>
+      <c r="N111" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="112" spans="2:14">
       <c r="B112">
         <v>56</v>
       </c>
       <c r="C112" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D112">
         <v>50</v>
@@ -46564,13 +48580,31 @@
       <c r="G112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="2:7">
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112" t="s">
+        <v>31</v>
+      </c>
+      <c r="M112" t="s">
+        <v>21</v>
+      </c>
+      <c r="N112" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="2:14">
       <c r="B113">
         <v>56</v>
       </c>
       <c r="C113" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D113">
         <v>38.33333333333334</v>
@@ -46584,13 +48618,31 @@
       <c r="G113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="2:7">
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113" t="s">
+        <v>26</v>
+      </c>
+      <c r="M113" t="s">
+        <v>33</v>
+      </c>
+      <c r="N113" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="114" spans="2:14">
       <c r="B114">
         <v>57</v>
       </c>
       <c r="C114" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D114">
         <v>45.00000000000001</v>
@@ -46604,13 +48656,31 @@
       <c r="G114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="2:7">
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114" t="s">
+        <v>31</v>
+      </c>
+      <c r="M114" t="s">
+        <v>21</v>
+      </c>
+      <c r="N114" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="2:14">
       <c r="B115">
         <v>57</v>
       </c>
       <c r="C115" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D115">
         <v>40</v>
@@ -46624,13 +48694,31 @@
       <c r="G115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="2:7">
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115" t="s">
+        <v>26</v>
+      </c>
+      <c r="M115" t="s">
+        <v>33</v>
+      </c>
+      <c r="N115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="116" spans="2:14">
       <c r="B116">
         <v>58</v>
       </c>
       <c r="C116" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D116">
         <v>15</v>
@@ -46644,13 +48732,31 @@
       <c r="G116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="2:7">
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116" t="s">
+        <v>31</v>
+      </c>
+      <c r="M116" t="s">
+        <v>21</v>
+      </c>
+      <c r="N116" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" spans="2:14">
       <c r="B117">
         <v>58</v>
       </c>
       <c r="C117" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D117">
         <v>15</v>
@@ -46664,13 +48770,31 @@
       <c r="G117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="2:7">
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117" t="s">
+        <v>26</v>
+      </c>
+      <c r="M117" t="s">
+        <v>33</v>
+      </c>
+      <c r="N117" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="118" spans="2:14">
       <c r="B118">
         <v>59</v>
       </c>
       <c r="C118" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D118">
         <v>38.33333333333333</v>
@@ -46684,13 +48808,31 @@
       <c r="G118">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="119" spans="2:7">
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118" t="s">
+        <v>31</v>
+      </c>
+      <c r="M118" t="s">
+        <v>21</v>
+      </c>
+      <c r="N118" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="2:14">
       <c r="B119">
         <v>59</v>
       </c>
       <c r="C119" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D119">
         <v>35</v>
@@ -46704,13 +48846,31 @@
       <c r="G119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="2:7">
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>11.25</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119" t="s">
+        <v>26</v>
+      </c>
+      <c r="M119" t="s">
+        <v>33</v>
+      </c>
+      <c r="N119" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="120" spans="2:14">
       <c r="B120">
         <v>60</v>
       </c>
       <c r="C120" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D120">
         <v>38.33333333333333</v>
@@ -46724,13 +48884,31 @@
       <c r="G120">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="121" spans="2:7">
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120" t="s">
+        <v>31</v>
+      </c>
+      <c r="M120" t="s">
+        <v>21</v>
+      </c>
+      <c r="N120" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="2:14">
       <c r="B121">
         <v>60</v>
       </c>
       <c r="C121" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D121">
         <v>15</v>
@@ -46744,13 +48922,31 @@
       <c r="G121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="2:7">
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121" t="s">
+        <v>26</v>
+      </c>
+      <c r="M121" t="s">
+        <v>33</v>
+      </c>
+      <c r="N121" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="122" spans="2:14">
       <c r="B122">
         <v>61</v>
       </c>
       <c r="C122" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D122">
         <v>50</v>
@@ -46764,13 +48960,31 @@
       <c r="G122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="2:7">
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122" t="s">
+        <v>44</v>
+      </c>
+      <c r="M122" t="s">
+        <v>50</v>
+      </c>
+      <c r="N122" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="2:14">
       <c r="B123">
         <v>61</v>
       </c>
       <c r="C123" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D123">
         <v>35</v>
@@ -46784,13 +48998,31 @@
       <c r="G123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="2:7">
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123" t="s">
+        <v>46</v>
+      </c>
+      <c r="M123" t="s">
+        <v>28</v>
+      </c>
+      <c r="N123" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="124" spans="2:14">
       <c r="B124">
         <v>62</v>
       </c>
       <c r="C124" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D124">
         <v>30</v>
@@ -46804,13 +49036,31 @@
       <c r="G124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="2:7">
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124" t="s">
+        <v>44</v>
+      </c>
+      <c r="M124" t="s">
+        <v>50</v>
+      </c>
+      <c r="N124" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="2:14">
       <c r="B125">
         <v>62</v>
       </c>
       <c r="C125" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D125">
         <v>85</v>
@@ -46824,13 +49074,31 @@
       <c r="G125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="2:7">
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125" t="s">
+        <v>46</v>
+      </c>
+      <c r="M125" t="s">
+        <v>28</v>
+      </c>
+      <c r="N125" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="126" spans="2:14">
       <c r="B126">
         <v>63</v>
       </c>
       <c r="C126" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D126">
         <v>15</v>
@@ -46844,13 +49112,31 @@
       <c r="G126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="2:7">
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126" t="s">
+        <v>44</v>
+      </c>
+      <c r="M126" t="s">
+        <v>50</v>
+      </c>
+      <c r="N126" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="2:14">
       <c r="B127">
         <v>63</v>
       </c>
       <c r="C127" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D127">
         <v>25</v>
@@ -46864,13 +49150,31 @@
       <c r="G127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="2:7">
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127" t="s">
+        <v>46</v>
+      </c>
+      <c r="M127" t="s">
+        <v>28</v>
+      </c>
+      <c r="N127" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="128" spans="2:14">
       <c r="B128">
         <v>64</v>
       </c>
       <c r="C128" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D128">
         <v>58.33333333333333</v>
@@ -46884,13 +49188,31 @@
       <c r="G128">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="129" spans="2:7">
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128" t="s">
+        <v>44</v>
+      </c>
+      <c r="M128" t="s">
+        <v>50</v>
+      </c>
+      <c r="N128" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" spans="2:14">
       <c r="B129">
         <v>64</v>
       </c>
       <c r="C129" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D129">
         <v>20</v>
@@ -46904,13 +49226,31 @@
       <c r="G129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="2:7">
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129" t="s">
+        <v>46</v>
+      </c>
+      <c r="M129" t="s">
+        <v>28</v>
+      </c>
+      <c r="N129" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="130" spans="2:14">
       <c r="B130">
         <v>65</v>
       </c>
       <c r="C130" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D130">
         <v>15</v>
@@ -46924,13 +49264,31 @@
       <c r="G130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="2:7">
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130" t="s">
+        <v>44</v>
+      </c>
+      <c r="M130" t="s">
+        <v>50</v>
+      </c>
+      <c r="N130" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="2:14">
       <c r="B131">
         <v>65</v>
       </c>
       <c r="C131" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D131">
         <v>35</v>
@@ -46944,13 +49302,31 @@
       <c r="G131">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="2:7">
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131" t="s">
+        <v>46</v>
+      </c>
+      <c r="M131" t="s">
+        <v>28</v>
+      </c>
+      <c r="N131" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="132" spans="2:14">
       <c r="B132">
         <v>66</v>
       </c>
       <c r="C132" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D132">
         <v>30</v>
@@ -46964,13 +49340,31 @@
       <c r="G132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="2:7">
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132" t="s">
+        <v>31</v>
+      </c>
+      <c r="M132" t="s">
+        <v>21</v>
+      </c>
+      <c r="N132" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="2:14">
       <c r="B133">
         <v>66</v>
       </c>
       <c r="C133" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D133">
         <v>33.33333333333334</v>
@@ -46984,13 +49378,31 @@
       <c r="G133">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="2:7">
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133" t="s">
+        <v>26</v>
+      </c>
+      <c r="M133" t="s">
+        <v>33</v>
+      </c>
+      <c r="N133" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="134" spans="2:14">
       <c r="B134">
         <v>67</v>
       </c>
       <c r="C134" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D134">
         <v>30</v>
@@ -47004,13 +49416,31 @@
       <c r="G134">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="2:7">
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134" t="s">
+        <v>31</v>
+      </c>
+      <c r="M134" t="s">
+        <v>21</v>
+      </c>
+      <c r="N134" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="135" spans="2:14">
       <c r="B135">
         <v>67</v>
       </c>
       <c r="C135" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D135">
         <v>15</v>
@@ -47024,13 +49454,31 @@
       <c r="G135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="2:7">
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135" t="s">
+        <v>26</v>
+      </c>
+      <c r="M135" t="s">
+        <v>33</v>
+      </c>
+      <c r="N135" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="136" spans="2:14">
       <c r="B136">
         <v>68</v>
       </c>
       <c r="C136" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D136">
         <v>15</v>
@@ -47044,13 +49492,31 @@
       <c r="G136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="2:7">
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136" t="s">
+        <v>31</v>
+      </c>
+      <c r="M136" t="s">
+        <v>21</v>
+      </c>
+      <c r="N136" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="137" spans="2:14">
       <c r="B137">
         <v>68</v>
       </c>
       <c r="C137" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D137">
         <v>68.33333333333333</v>
@@ -47064,13 +49530,31 @@
       <c r="G137">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="138" spans="2:7">
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137" t="s">
+        <v>26</v>
+      </c>
+      <c r="M137" t="s">
+        <v>33</v>
+      </c>
+      <c r="N137" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="138" spans="2:14">
       <c r="B138">
         <v>69</v>
       </c>
       <c r="C138" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D138">
         <v>40</v>
@@ -47084,13 +49568,31 @@
       <c r="G138">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="2:7">
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138" t="s">
+        <v>31</v>
+      </c>
+      <c r="M138" t="s">
+        <v>21</v>
+      </c>
+      <c r="N138" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="139" spans="2:14">
       <c r="B139">
         <v>69</v>
       </c>
       <c r="C139" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D139">
         <v>30</v>
@@ -47104,13 +49606,31 @@
       <c r="G139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="2:7">
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139" t="s">
+        <v>26</v>
+      </c>
+      <c r="M139" t="s">
+        <v>33</v>
+      </c>
+      <c r="N139" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="140" spans="2:14">
       <c r="B140">
         <v>70</v>
       </c>
       <c r="C140" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D140">
         <v>10</v>
@@ -47124,13 +49644,31 @@
       <c r="G140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="2:7">
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140" t="s">
+        <v>31</v>
+      </c>
+      <c r="M140" t="s">
+        <v>21</v>
+      </c>
+      <c r="N140" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="141" spans="2:14">
       <c r="B141">
         <v>70</v>
       </c>
       <c r="C141" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D141">
         <v>35</v>
@@ -47144,13 +49682,31 @@
       <c r="G141">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="2:7">
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141" t="s">
+        <v>26</v>
+      </c>
+      <c r="M141" t="s">
+        <v>33</v>
+      </c>
+      <c r="N141" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="142" spans="2:14">
       <c r="B142">
         <v>71</v>
       </c>
       <c r="C142" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D142">
         <v>5</v>
@@ -47164,13 +49720,31 @@
       <c r="G142">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="2:7">
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142" t="s">
+        <v>44</v>
+      </c>
+      <c r="M142" t="s">
+        <v>50</v>
+      </c>
+      <c r="N142" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143" spans="2:14">
       <c r="B143">
         <v>71</v>
       </c>
       <c r="C143" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D143">
         <v>140</v>
@@ -47184,13 +49758,31 @@
       <c r="G143">
         <v>100</v>
       </c>
-    </row>
-    <row r="144" spans="2:7">
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143" t="s">
+        <v>46</v>
+      </c>
+      <c r="M143" t="s">
+        <v>28</v>
+      </c>
+      <c r="N143" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="144" spans="2:14">
       <c r="B144">
         <v>72</v>
       </c>
       <c r="C144" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D144">
         <v>55.00000000000001</v>
@@ -47204,13 +49796,31 @@
       <c r="G144">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="2:7">
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144" t="s">
+        <v>44</v>
+      </c>
+      <c r="M144" t="s">
+        <v>50</v>
+      </c>
+      <c r="N144" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="145" spans="2:14">
       <c r="B145">
         <v>72</v>
       </c>
       <c r="C145" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D145">
         <v>40</v>
@@ -47224,13 +49834,31 @@
       <c r="G145">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="2:7">
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145" t="s">
+        <v>46</v>
+      </c>
+      <c r="M145" t="s">
+        <v>28</v>
+      </c>
+      <c r="N145" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="146" spans="2:14">
       <c r="B146">
         <v>73</v>
       </c>
       <c r="C146" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D146">
         <v>30</v>
@@ -47244,13 +49872,31 @@
       <c r="G146">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="2:7">
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146" t="s">
+        <v>44</v>
+      </c>
+      <c r="M146" t="s">
+        <v>50</v>
+      </c>
+      <c r="N146" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="2:14">
       <c r="B147">
         <v>73</v>
       </c>
       <c r="C147" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D147">
         <v>45</v>
@@ -47264,13 +49910,31 @@
       <c r="G147">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="2:7">
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147" t="s">
+        <v>46</v>
+      </c>
+      <c r="M147" t="s">
+        <v>28</v>
+      </c>
+      <c r="N147" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="148" spans="2:14">
       <c r="B148">
         <v>74</v>
       </c>
       <c r="C148" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D148">
         <v>10</v>
@@ -47284,13 +49948,31 @@
       <c r="G148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="2:7">
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148" t="s">
+        <v>44</v>
+      </c>
+      <c r="M148" t="s">
+        <v>50</v>
+      </c>
+      <c r="N148" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149" spans="2:14">
       <c r="B149">
         <v>74</v>
       </c>
       <c r="C149" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D149">
         <v>20</v>
@@ -47304,13 +49986,31 @@
       <c r="G149">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="2:7">
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149" t="s">
+        <v>46</v>
+      </c>
+      <c r="M149" t="s">
+        <v>28</v>
+      </c>
+      <c r="N149" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="150" spans="2:14">
       <c r="B150">
         <v>75</v>
       </c>
       <c r="C150" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D150">
         <v>43.33333333333334</v>
@@ -47324,13 +50024,31 @@
       <c r="G150">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="2:7">
+      <c r="I150">
+        <v>4.615384615384614</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150" t="s">
+        <v>44</v>
+      </c>
+      <c r="M150" t="s">
+        <v>50</v>
+      </c>
+      <c r="N150" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="2:14">
       <c r="B151">
         <v>75</v>
       </c>
       <c r="C151" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D151">
         <v>5</v>
@@ -47344,13 +50062,31 @@
       <c r="G151">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="2:7">
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151" t="s">
+        <v>46</v>
+      </c>
+      <c r="M151" t="s">
+        <v>28</v>
+      </c>
+      <c r="N151" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="152" spans="2:14">
       <c r="B152">
         <v>76</v>
       </c>
       <c r="C152" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D152">
         <v>30</v>
@@ -47364,13 +50100,31 @@
       <c r="G152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="2:7">
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152" t="s">
+        <v>31</v>
+      </c>
+      <c r="M152" t="s">
+        <v>21</v>
+      </c>
+      <c r="N152" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="153" spans="2:14">
       <c r="B153">
         <v>76</v>
       </c>
       <c r="C153" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D153">
         <v>73.33333333333333</v>
@@ -47384,13 +50138,31 @@
       <c r="G153">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="154" spans="2:7">
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153" t="s">
+        <v>24</v>
+      </c>
+      <c r="M153" t="s">
+        <v>33</v>
+      </c>
+      <c r="N153" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="154" spans="2:14">
       <c r="B154">
         <v>77</v>
       </c>
       <c r="C154" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D154">
         <v>35</v>
@@ -47404,13 +50176,31 @@
       <c r="G154">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="2:7">
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154" t="s">
+        <v>31</v>
+      </c>
+      <c r="M154" t="s">
+        <v>21</v>
+      </c>
+      <c r="N154" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="155" spans="2:14">
       <c r="B155">
         <v>77</v>
       </c>
       <c r="C155" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D155">
         <v>48.33333333333333</v>
@@ -47424,13 +50214,31 @@
       <c r="G155">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="156" spans="2:7">
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155" t="s">
+        <v>24</v>
+      </c>
+      <c r="M155" t="s">
+        <v>33</v>
+      </c>
+      <c r="N155" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="156" spans="2:14">
       <c r="B156">
         <v>78</v>
       </c>
       <c r="C156" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D156">
         <v>40</v>
@@ -47444,13 +50252,31 @@
       <c r="G156">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="2:7">
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156" t="s">
+        <v>31</v>
+      </c>
+      <c r="M156" t="s">
+        <v>21</v>
+      </c>
+      <c r="N156" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="157" spans="2:14">
       <c r="B157">
         <v>78</v>
       </c>
       <c r="C157" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D157">
         <v>30</v>
@@ -47464,13 +50290,31 @@
       <c r="G157">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="2:7">
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157" t="s">
+        <v>24</v>
+      </c>
+      <c r="M157" t="s">
+        <v>33</v>
+      </c>
+      <c r="N157" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="158" spans="2:14">
       <c r="B158">
         <v>79</v>
       </c>
       <c r="C158" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D158">
         <v>5</v>
@@ -47484,13 +50328,31 @@
       <c r="G158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="2:7">
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158" t="s">
+        <v>31</v>
+      </c>
+      <c r="M158" t="s">
+        <v>21</v>
+      </c>
+      <c r="N158" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="159" spans="2:14">
       <c r="B159">
         <v>79</v>
       </c>
       <c r="C159" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D159">
         <v>75</v>
@@ -47504,13 +50366,31 @@
       <c r="G159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="2:7">
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159" t="s">
+        <v>24</v>
+      </c>
+      <c r="M159" t="s">
+        <v>33</v>
+      </c>
+      <c r="N159" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="160" spans="2:14">
       <c r="B160">
         <v>80</v>
       </c>
       <c r="C160" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D160">
         <v>40</v>
@@ -47524,13 +50404,31 @@
       <c r="G160">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="2:7">
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160" t="s">
+        <v>31</v>
+      </c>
+      <c r="M160" t="s">
+        <v>21</v>
+      </c>
+      <c r="N160" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="161" spans="2:14">
       <c r="B161">
         <v>80</v>
       </c>
       <c r="C161" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D161">
         <v>10</v>
@@ -47544,13 +50442,31 @@
       <c r="G161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="2:7">
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161" t="s">
+        <v>24</v>
+      </c>
+      <c r="M161" t="s">
+        <v>33</v>
+      </c>
+      <c r="N161" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="162" spans="2:14">
       <c r="B162">
         <v>81</v>
       </c>
       <c r="C162" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D162">
         <v>15</v>
@@ -47564,13 +50480,31 @@
       <c r="G162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="2:7">
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162" t="s">
+        <v>44</v>
+      </c>
+      <c r="M162" t="s">
+        <v>50</v>
+      </c>
+      <c r="N162" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" spans="2:14">
       <c r="B163">
         <v>81</v>
       </c>
       <c r="C163" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D163">
         <v>86.66666666666666</v>
@@ -47584,13 +50518,31 @@
       <c r="G163">
         <v>66.66666666666666</v>
       </c>
-    </row>
-    <row r="164" spans="2:7">
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163" t="s">
+        <v>46</v>
+      </c>
+      <c r="M163" t="s">
+        <v>28</v>
+      </c>
+      <c r="N163" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="164" spans="2:14">
       <c r="B164">
         <v>82</v>
       </c>
       <c r="C164" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D164">
         <v>15</v>
@@ -47604,13 +50556,31 @@
       <c r="G164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="2:7">
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164" t="s">
+        <v>44</v>
+      </c>
+      <c r="M164" t="s">
+        <v>50</v>
+      </c>
+      <c r="N164" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" spans="2:14">
       <c r="B165">
         <v>82</v>
       </c>
       <c r="C165" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D165">
         <v>45.00000000000001</v>
@@ -47624,13 +50594,31 @@
       <c r="G165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="2:7">
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165" t="s">
+        <v>46</v>
+      </c>
+      <c r="M165" t="s">
+        <v>28</v>
+      </c>
+      <c r="N165" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="166" spans="2:14">
       <c r="B166">
         <v>83</v>
       </c>
       <c r="C166" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D166">
         <v>38.33333333333334</v>
@@ -47644,13 +50632,31 @@
       <c r="G166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="2:7">
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>3.789473684210526</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166" t="s">
+        <v>44</v>
+      </c>
+      <c r="M166" t="s">
+        <v>50</v>
+      </c>
+      <c r="N166" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="167" spans="2:14">
       <c r="B167">
         <v>83</v>
       </c>
       <c r="C167" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D167">
         <v>20</v>
@@ -47664,13 +50670,31 @@
       <c r="G167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="2:7">
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167" t="s">
+        <v>46</v>
+      </c>
+      <c r="M167" t="s">
+        <v>28</v>
+      </c>
+      <c r="N167" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="168" spans="2:14">
       <c r="B168">
         <v>84</v>
       </c>
       <c r="C168" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D168">
         <v>20</v>
@@ -47684,13 +50708,31 @@
       <c r="G168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="2:7">
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168" t="s">
+        <v>44</v>
+      </c>
+      <c r="M168" t="s">
+        <v>50</v>
+      </c>
+      <c r="N168" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169" spans="2:14">
       <c r="B169">
         <v>84</v>
       </c>
       <c r="C169" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D169">
         <v>50</v>
@@ -47704,13 +50746,31 @@
       <c r="G169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="2:7">
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169" t="s">
+        <v>46</v>
+      </c>
+      <c r="M169" t="s">
+        <v>28</v>
+      </c>
+      <c r="N169" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="170" spans="2:14">
       <c r="B170">
         <v>85</v>
       </c>
       <c r="C170" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D170">
         <v>23.33333333333334</v>
@@ -47724,13 +50784,31 @@
       <c r="G170">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="2:7">
+      <c r="I170">
+        <v>20</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170" t="s">
+        <v>44</v>
+      </c>
+      <c r="M170" t="s">
+        <v>50</v>
+      </c>
+      <c r="N170" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" spans="2:14">
       <c r="B171">
         <v>85</v>
       </c>
       <c r="C171" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D171">
         <v>20</v>
@@ -47744,13 +50822,31 @@
       <c r="G171">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="2:7">
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171" t="s">
+        <v>46</v>
+      </c>
+      <c r="M171" t="s">
+        <v>28</v>
+      </c>
+      <c r="N171" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="172" spans="2:14">
       <c r="B172">
         <v>86</v>
       </c>
       <c r="C172" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D172">
         <v>83.33333333333333</v>
@@ -47764,13 +50860,31 @@
       <c r="G172">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="173" spans="2:7">
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172" t="s">
+        <v>31</v>
+      </c>
+      <c r="M172" t="s">
+        <v>21</v>
+      </c>
+      <c r="N172" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="173" spans="2:14">
       <c r="B173">
         <v>86</v>
       </c>
       <c r="C173" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D173">
         <v>78.33333333333331</v>
@@ -47784,13 +50898,31 @@
       <c r="G173">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="174" spans="2:7">
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173" t="s">
+        <v>26</v>
+      </c>
+      <c r="M173" t="s">
+        <v>33</v>
+      </c>
+      <c r="N173" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="174" spans="2:14">
       <c r="B174">
         <v>87</v>
       </c>
       <c r="C174" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D174">
         <v>50</v>
@@ -47804,13 +50936,31 @@
       <c r="G174">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="2:7">
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174" t="s">
+        <v>31</v>
+      </c>
+      <c r="M174" t="s">
+        <v>21</v>
+      </c>
+      <c r="N174" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="175" spans="2:14">
       <c r="B175">
         <v>87</v>
       </c>
       <c r="C175" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D175">
         <v>48.33333333333333</v>
@@ -47824,13 +50974,31 @@
       <c r="G175">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="176" spans="2:7">
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175" t="s">
+        <v>26</v>
+      </c>
+      <c r="M175" t="s">
+        <v>33</v>
+      </c>
+      <c r="N175" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="176" spans="2:14">
       <c r="B176">
         <v>88</v>
       </c>
       <c r="C176" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D176">
         <v>71.66666666666666</v>
@@ -47844,13 +51012,31 @@
       <c r="G176">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="177" spans="2:7">
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>22</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176" t="s">
+        <v>31</v>
+      </c>
+      <c r="M176" t="s">
+        <v>21</v>
+      </c>
+      <c r="N176" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="177" spans="2:14">
       <c r="B177">
         <v>88</v>
       </c>
       <c r="C177" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D177">
         <v>53.33333333333333</v>
@@ -47864,13 +51050,31 @@
       <c r="G177">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="178" spans="2:7">
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177" t="s">
+        <v>26</v>
+      </c>
+      <c r="M177" t="s">
+        <v>33</v>
+      </c>
+      <c r="N177" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="178" spans="2:14">
       <c r="B178">
         <v>89</v>
       </c>
       <c r="C178" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D178">
         <v>25</v>
@@ -47884,13 +51088,31 @@
       <c r="G178">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="2:7">
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178" t="s">
+        <v>31</v>
+      </c>
+      <c r="M178" t="s">
+        <v>21</v>
+      </c>
+      <c r="N178" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="179" spans="2:14">
       <c r="B179">
         <v>89</v>
       </c>
       <c r="C179" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D179">
         <v>116.6666666666667</v>
@@ -47904,13 +51126,31 @@
       <c r="G179">
         <v>66.66666666666666</v>
       </c>
-    </row>
-    <row r="180" spans="2:7">
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179" t="s">
+        <v>26</v>
+      </c>
+      <c r="M179" t="s">
+        <v>33</v>
+      </c>
+      <c r="N179" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="180" spans="2:14">
       <c r="B180">
         <v>90</v>
       </c>
       <c r="C180" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D180">
         <v>20</v>
@@ -47924,13 +51164,31 @@
       <c r="G180">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="2:7">
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180" t="s">
+        <v>31</v>
+      </c>
+      <c r="M180" t="s">
+        <v>21</v>
+      </c>
+      <c r="N180" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="181" spans="2:14">
       <c r="B181">
         <v>90</v>
       </c>
       <c r="C181" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D181">
         <v>48.33333333333333</v>
@@ -47944,13 +51202,31 @@
       <c r="G181">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="182" spans="2:7">
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181" t="s">
+        <v>26</v>
+      </c>
+      <c r="M181" t="s">
+        <v>33</v>
+      </c>
+      <c r="N181" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="182" spans="2:14">
       <c r="B182">
         <v>91</v>
       </c>
       <c r="C182" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D182">
         <v>20</v>
@@ -47964,13 +51240,31 @@
       <c r="G182">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="2:7">
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182" t="s">
+        <v>44</v>
+      </c>
+      <c r="M182" t="s">
+        <v>50</v>
+      </c>
+      <c r="N182" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="2:14">
       <c r="B183">
         <v>91</v>
       </c>
       <c r="C183" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D183">
         <v>5</v>
@@ -47984,13 +51278,31 @@
       <c r="G183">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="2:7">
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183" t="s">
+        <v>46</v>
+      </c>
+      <c r="M183" t="s">
+        <v>28</v>
+      </c>
+      <c r="N183" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="184" spans="2:14">
       <c r="B184">
         <v>92</v>
       </c>
       <c r="C184" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D184">
         <v>35</v>
@@ -48004,13 +51316,31 @@
       <c r="G184">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="2:7">
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184" t="s">
+        <v>44</v>
+      </c>
+      <c r="M184" t="s">
+        <v>50</v>
+      </c>
+      <c r="N184" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="185" spans="2:14">
       <c r="B185">
         <v>92</v>
       </c>
       <c r="C185" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D185">
         <v>143.3333333333333</v>
@@ -48024,13 +51354,31 @@
       <c r="G185">
         <v>33.33333333333333</v>
       </c>
-    </row>
-    <row r="186" spans="2:7">
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185" t="s">
+        <v>46</v>
+      </c>
+      <c r="M185" t="s">
+        <v>50</v>
+      </c>
+      <c r="N185" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="186" spans="2:14">
       <c r="B186">
         <v>93</v>
       </c>
       <c r="C186" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D186">
         <v>10</v>
@@ -48044,13 +51392,31 @@
       <c r="G186">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="2:7">
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186" t="s">
+        <v>44</v>
+      </c>
+      <c r="M186" t="s">
+        <v>50</v>
+      </c>
+      <c r="N186" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="187" spans="2:14">
       <c r="B187">
         <v>93</v>
       </c>
       <c r="C187" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D187">
         <v>20</v>
@@ -48064,13 +51430,31 @@
       <c r="G187">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="2:7">
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187" t="s">
+        <v>46</v>
+      </c>
+      <c r="M187" t="s">
+        <v>28</v>
+      </c>
+      <c r="N187" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="188" spans="2:14">
       <c r="B188">
         <v>94</v>
       </c>
       <c r="C188" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D188">
         <v>10</v>
@@ -48084,13 +51468,31 @@
       <c r="G188">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="2:7">
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188" t="s">
+        <v>44</v>
+      </c>
+      <c r="M188" t="s">
+        <v>50</v>
+      </c>
+      <c r="N188" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="189" spans="2:14">
       <c r="B189">
         <v>94</v>
       </c>
       <c r="C189" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D189">
         <v>128.3333333333333</v>
@@ -48103,6 +51505,24 @@
       </c>
       <c r="G189">
         <v>33.33333333333333</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189" t="s">
+        <v>28</v>
+      </c>
+      <c r="M189" t="s">
+        <v>28</v>
+      </c>
+      <c r="N189" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/output_data.xlsx
+++ b/output_data.xlsx
@@ -44705,10 +44705,10 @@
         <v>66.66666666666666</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>63.33333333333333</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -44784,7 +44784,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -44939,7 +44939,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>2.222222222222221</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L16" t="s">
         <v>31</v>
@@ -44977,7 +44977,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>2.222222222222221</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L17" t="s">
         <v>24</v>
@@ -45316,7 +45316,7 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -45845,10 +45845,10 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -46304,7 +46304,7 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -46339,7 +46339,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -46535,7 +46535,7 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L58" t="s">
         <v>31</v>
@@ -46573,7 +46573,7 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L59" t="s">
         <v>24</v>
@@ -46646,7 +46646,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>16.36363636363636</v>
       </c>
       <c r="K61">
         <v>22.5</v>
@@ -47517,7 +47517,7 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -48207,7 +48207,7 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>10</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L102" t="s">
         <v>44</v>
@@ -48245,7 +48245,7 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>10</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L103" t="s">
         <v>46</v>
@@ -48280,7 +48280,7 @@
         <v>7.499999999999998</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>16.36363636363636</v>
       </c>
       <c r="K104">
         <v>0</v>
@@ -48508,7 +48508,7 @@
         <v>359.9999999999999</v>
       </c>
       <c r="J110">
-        <v>0</v>
+        <v>255.7894736842105</v>
       </c>
       <c r="K110">
         <v>0</v>
@@ -48587,7 +48587,7 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L112" t="s">
         <v>31</v>
@@ -48625,7 +48625,7 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L113" t="s">
         <v>26</v>
@@ -49075,7 +49075,7 @@
         <v>0</v>
       </c>
       <c r="I125">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -49347,7 +49347,7 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L132" t="s">
         <v>31</v>
@@ -49385,7 +49385,7 @@
         <v>0</v>
       </c>
       <c r="K133">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L133" t="s">
         <v>26</v>
@@ -50025,7 +50025,7 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <v>4.615384615384614</v>
+        <v>0</v>
       </c>
       <c r="J150">
         <v>0</v>
@@ -50636,7 +50636,7 @@
         <v>0</v>
       </c>
       <c r="J166">
-        <v>3.789473684210526</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="K166">
         <v>0</v>
@@ -50785,10 +50785,10 @@
         <v>0</v>
       </c>
       <c r="I170">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="K170">
         <v>0</v>
@@ -51013,10 +51013,10 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I176">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="J176">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K176">
         <v>0</v>
@@ -51358,7 +51358,7 @@
         <v>0</v>
       </c>
       <c r="J185">
-        <v>0</v>
+        <v>89.99999999999999</v>
       </c>
       <c r="K185">
         <v>0</v>
@@ -51507,10 +51507,10 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I189">
-        <v>0</v>
+        <v>16.36363636363636</v>
       </c>
       <c r="J189">
-        <v>0</v>
+        <v>16.36363636363636</v>
       </c>
       <c r="K189">
         <v>0</v>

--- a/output_data.xlsx
+++ b/output_data.xlsx
@@ -44401,13 +44401,13 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>3.559322033898305</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="L2" t="s">
         <v>44</v>
@@ -44439,13 +44439,13 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2.125984251968504</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.9246575342465754</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>3.214285714285715</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -44477,13 +44477,13 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>39.00000000000001</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>33.00000000000001</v>
       </c>
       <c r="L4" t="s">
         <v>44</v>
@@ -44515,13 +44515,13 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>130.9090909090909</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>391.4999999999999</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="L5" t="s">
         <v>46</v>
@@ -44553,13 +44553,13 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>7.500000000000001</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1.569767441860465</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.576923076923077</v>
       </c>
       <c r="L6" t="s">
         <v>44</v>
@@ -44591,13 +44591,13 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.7031249999999999</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>31.00000000000001</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
@@ -44629,13 +44629,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>35.91954022988506</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>6.923076923076922</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="L8" t="s">
         <v>44</v>
@@ -44667,7 +44667,7 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -44705,13 +44705,13 @@
         <v>66.66666666666666</v>
       </c>
       <c r="I10">
-        <v>18</v>
+        <v>57.46969696969697</v>
       </c>
       <c r="J10">
-        <v>63.33333333333333</v>
+        <v>101.6666666666667</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="L10" t="s">
         <v>44</v>
@@ -44743,13 +44743,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>39.13978494623655</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="L11" t="s">
         <v>46</v>
@@ -44784,10 +44784,10 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>277.5</v>
       </c>
       <c r="L12" t="s">
         <v>31</v>
@@ -44819,13 +44819,13 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>139.5</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>41.24999999999999</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s">
         <v>24</v>
@@ -44857,13 +44857,13 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="L14" t="s">
         <v>31</v>
@@ -44898,10 +44898,10 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="L15" t="s">
         <v>24</v>
@@ -44939,7 +44939,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>13.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="L16" t="s">
         <v>31</v>
@@ -44971,13 +44971,13 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K17">
-        <v>13.33333333333333</v>
+        <v>17.57861635220126</v>
       </c>
       <c r="L17" t="s">
         <v>24</v>
@@ -45009,13 +45009,13 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L18" t="s">
         <v>31</v>
@@ -45047,13 +45047,13 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>5.861842105263158</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>8.678571428571429</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="L19" t="s">
         <v>24</v>
@@ -45085,13 +45085,13 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>5.172413793103449</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>58.18181818181819</v>
       </c>
       <c r="L20" t="s">
         <v>31</v>
@@ -45123,13 +45123,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>86.00000000000001</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>44.58333333333333</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>6.428571428571428</v>
       </c>
       <c r="L21" t="s">
         <v>24</v>
@@ -45161,13 +45161,13 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1.027397260273973</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="s">
         <v>44</v>
@@ -45199,13 +45199,13 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>9.254032258064518</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="L23" t="s">
         <v>46</v>
@@ -45237,13 +45237,13 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>3.879310344827587</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>6.000000000000001</v>
       </c>
       <c r="L24" t="s">
         <v>44</v>
@@ -45275,13 +45275,13 @@
         <v>66.66666666666666</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>6.402439024390244</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>45.65942028985507</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>53.92156862745098</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
@@ -45313,13 +45313,13 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>33.75</v>
       </c>
       <c r="J26">
         <v>13.33333333333333</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L26" t="s">
         <v>44</v>
@@ -45351,13 +45351,13 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>5.192307692307692</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>61.36363636363637</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>8.231707317073171</v>
       </c>
       <c r="L27" t="s">
         <v>46</v>
@@ -45389,13 +45389,13 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>2.307692307692308</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>62.00000000000001</v>
       </c>
       <c r="L28" t="s">
         <v>44</v>
@@ -45427,13 +45427,13 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>0.4724409448818898</v>
       </c>
       <c r="L29" t="s">
         <v>46</v>
@@ -45465,13 +45465,13 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>55.99999999999999</v>
       </c>
       <c r="L30" t="s">
         <v>44</v>
@@ -45544,7 +45544,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -45579,13 +45579,13 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L33" t="s">
         <v>26</v>
@@ -45617,10 +45617,10 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>12.27272727272727</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -45655,13 +45655,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1.171875</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>0.6122448979591837</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>35.75124378109453</v>
       </c>
       <c r="L35" t="s">
         <v>26</v>
@@ -45693,13 +45693,13 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1.415094339622642</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>8.000000000000002</v>
       </c>
       <c r="L36" t="s">
         <v>31</v>
@@ -45731,13 +45731,13 @@
         <v>66.66666666666666</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>43.92156862745098</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>46.66666666666667</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>69.33333333333334</v>
       </c>
       <c r="L37" t="s">
         <v>26</v>
@@ -45769,13 +45769,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>82.42424242424242</v>
       </c>
       <c r="L38" t="s">
         <v>31</v>
@@ -45807,13 +45807,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>19.44915254237288</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>391.4999999999999</v>
       </c>
       <c r="L39" t="s">
         <v>26</v>
@@ -45845,13 +45845,13 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>18</v>
+        <v>28.22727272727272</v>
       </c>
       <c r="J40">
-        <v>9</v>
+        <v>20.53846153846154</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>2.721774193548387</v>
       </c>
       <c r="L40" t="s">
         <v>31</v>
@@ -45883,13 +45883,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>64.50000000000003</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>76.96969696969698</v>
       </c>
       <c r="L41" t="s">
         <v>26</v>
@@ -45921,13 +45921,13 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>8.231707317073173</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L42" t="s">
         <v>44</v>
@@ -45997,13 +45997,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>4.500000000000001</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>34.19871794871795</v>
       </c>
       <c r="L44" t="s">
         <v>44</v>
@@ -46035,13 +46035,13 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>31.00000000000001</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L45" t="s">
         <v>46</v>
@@ -46073,13 +46073,13 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>2.34375</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>9.642857142857144</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L46" t="s">
         <v>44</v>
@@ -46111,13 +46111,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>25.45454545454546</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>229.3333333333333</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L47" t="s">
         <v>46</v>
@@ -46149,13 +46149,13 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>7.500000000000001</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L48" t="s">
         <v>44</v>
@@ -46190,10 +46190,10 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="L49" t="s">
         <v>46</v>
@@ -46225,13 +46225,13 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L50" t="s">
         <v>44</v>
@@ -46263,13 +46263,13 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>3.543307086614174</v>
       </c>
       <c r="L51" t="s">
         <v>46</v>
@@ -46301,10 +46301,10 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>15.88235294117647</v>
       </c>
       <c r="J52">
-        <v>27</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -46339,13 +46339,13 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>18</v>
+        <v>23.08474576271187</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>10.58823529411765</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L53" t="s">
         <v>24</v>
@@ -46377,13 +46377,13 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>4.500000000000001</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="L54" t="s">
         <v>31</v>
@@ -46415,13 +46415,13 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>11.63793103448276</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>6.367924528301888</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>4.835820895522388</v>
       </c>
       <c r="L55" t="s">
         <v>24</v>
@@ -46453,13 +46453,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>47.84946236559139</v>
       </c>
       <c r="L56" t="s">
         <v>31</v>
@@ -46491,13 +46491,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>2.769230769230769</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>34.97716894977169</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>7.043478260869564</v>
       </c>
       <c r="L57" t="s">
         <v>24</v>
@@ -46529,13 +46529,13 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K58">
-        <v>13.33333333333333</v>
+        <v>48.46153846153845</v>
       </c>
       <c r="L58" t="s">
         <v>31</v>
@@ -46567,13 +46567,13 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>34.54545454545455</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K59">
-        <v>13.33333333333333</v>
+        <v>41.33333333333334</v>
       </c>
       <c r="L59" t="s">
         <v>24</v>
@@ -46605,13 +46605,13 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>8.04435483870968</v>
       </c>
       <c r="K60">
-        <v>22.5</v>
+        <v>8.555555555555557</v>
       </c>
       <c r="L60" t="s">
         <v>31</v>
@@ -46643,13 +46643,13 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J61">
-        <v>16.36363636363636</v>
+        <v>45.45454545454546</v>
       </c>
       <c r="K61">
-        <v>22.5</v>
+        <v>44.5</v>
       </c>
       <c r="L61" t="s">
         <v>24</v>
@@ -46681,13 +46681,13 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>13.43023255813953</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>3.01829268292683</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>47.90322580645161</v>
       </c>
       <c r="L62" t="s">
         <v>44</v>
@@ -46722,10 +46722,10 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>0.5113636363636362</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L63" t="s">
         <v>46</v>
@@ -46757,13 +46757,13 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>1.40625</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>3.636363636363637</v>
       </c>
       <c r="L64" t="s">
         <v>44</v>
@@ -46833,13 +46833,13 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>2.033898305084746</v>
       </c>
       <c r="L66" t="s">
         <v>44</v>
@@ -46874,10 +46874,10 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>5.172413793103449</v>
       </c>
       <c r="L67" t="s">
         <v>46</v>
@@ -46909,13 +46909,13 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>1.760869565217391</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="L68" t="s">
         <v>44</v>
@@ -46947,13 +46947,13 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>44.00000000000001</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>6.575342465753424</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="L69" t="s">
         <v>46</v>
@@ -47023,13 +47023,13 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="s">
         <v>46</v>
@@ -47061,13 +47061,13 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>4.952830188679245</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>10.86206896551724</v>
       </c>
       <c r="L72" t="s">
         <v>31</v>
@@ -47102,10 +47102,10 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>7.440944881889763</v>
       </c>
       <c r="L73" t="s">
         <v>26</v>
@@ -47137,13 +47137,13 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>4.835820895522388</v>
       </c>
       <c r="L74" t="s">
         <v>31</v>
@@ -47175,13 +47175,13 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>3.970588235294117</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>18.5625</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="L75" t="s">
         <v>26</v>
@@ -47213,13 +47213,13 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>14.53846153846154</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>24.75</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>5.232558139534882</v>
       </c>
       <c r="L76" t="s">
         <v>31</v>
@@ -47251,13 +47251,13 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>7.734374999999999</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>6.048387096774193</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L77" t="s">
         <v>26</v>
@@ -47289,13 +47289,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>45.33333333333333</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L78" t="s">
         <v>31</v>
@@ -47327,13 +47327,13 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>9.55263157894737</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L79" t="s">
         <v>26</v>
@@ -47365,13 +47365,13 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>1.451612903225807</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>6.164383561643836</v>
       </c>
       <c r="L80" t="s">
         <v>31</v>
@@ -47403,13 +47403,13 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>5.4</v>
+        <v>261.4</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>55.99999999999999</v>
       </c>
       <c r="L81" t="s">
         <v>26</v>
@@ -47441,13 +47441,13 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>0</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>15.55555555555556</v>
       </c>
       <c r="L82" t="s">
         <v>44</v>
@@ -47485,7 +47485,7 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>3.409090909090909</v>
       </c>
       <c r="L83" t="s">
         <v>46</v>
@@ -47517,13 +47517,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I84">
-        <v>13.33333333333333</v>
+        <v>14.13690476190476</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>4.0748031496063</v>
       </c>
       <c r="L84" t="s">
         <v>44</v>
@@ -47555,13 +47555,13 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>7.500000000000001</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="L85" t="s">
         <v>46</v>
@@ -47593,13 +47593,13 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>7.408536585365855</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>25.31249999999999</v>
       </c>
       <c r="L86" t="s">
         <v>44</v>
@@ -47631,13 +47631,13 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>19.89795918367347</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>2.867647058823529</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>32.49999999999999</v>
       </c>
       <c r="L87" t="s">
         <v>46</v>
@@ -47669,13 +47669,13 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>9.310344827586208</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>13.80681818181818</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>24.54545454545455</v>
       </c>
       <c r="L88" t="s">
         <v>44</v>
@@ -47707,10 +47707,10 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J89">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="K89">
         <v>0</v>
@@ -47745,13 +47745,13 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>21.95121951219512</v>
       </c>
       <c r="J90">
-        <v>0</v>
+        <v>8.000000000000002</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L90" t="s">
         <v>44</v>
@@ -47783,13 +47783,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>14.08695652173913</v>
       </c>
       <c r="J91">
-        <v>0</v>
+        <v>3.39622641509434</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>41.33333333333334</v>
       </c>
       <c r="L91" t="s">
         <v>46</v>
@@ -47821,13 +47821,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I92">
-        <v>0</v>
+        <v>141.8333333333333</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>10.67796610169492</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>6.176470588235295</v>
       </c>
       <c r="L92" t="s">
         <v>31</v>
@@ -47859,13 +47859,13 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>0</v>
+        <v>1.343283582089552</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L93" t="s">
         <v>24</v>
@@ -47897,13 +47897,13 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L94" t="s">
         <v>31</v>
@@ -47935,13 +47935,13 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J95">
-        <v>0</v>
+        <v>44.00000000000001</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>15.55555555555556</v>
       </c>
       <c r="L95" t="s">
         <v>24</v>
@@ -47973,7 +47973,7 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>4.883720930232557</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -48014,10 +48014,10 @@
         <v>0</v>
       </c>
       <c r="J97">
-        <v>0</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>7.500000000000001</v>
       </c>
       <c r="L97" t="s">
         <v>24</v>
@@ -48049,13 +48049,13 @@
         <v>66.66666666666666</v>
       </c>
       <c r="I98">
-        <v>0</v>
+        <v>48.88888888888889</v>
       </c>
       <c r="J98">
-        <v>0</v>
+        <v>37.45833333333334</v>
       </c>
       <c r="K98">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L98" t="s">
         <v>31</v>
@@ -48087,13 +48087,13 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J99">
-        <v>0</v>
+        <v>6.206896551724139</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>6.774193548387098</v>
       </c>
       <c r="L99" t="s">
         <v>24</v>
@@ -48125,13 +48125,13 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>36.00000000000001</v>
       </c>
       <c r="J100">
-        <v>0</v>
+        <v>6.838815789473686</v>
       </c>
       <c r="K100">
-        <v>0</v>
+        <v>12.65625</v>
       </c>
       <c r="L100" t="s">
         <v>31</v>
@@ -48163,10 +48163,10 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>0</v>
+        <v>24.54545454545455</v>
       </c>
       <c r="J101">
-        <v>0</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="K101">
         <v>0</v>
@@ -48201,13 +48201,13 @@
         <v>0</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102">
-        <v>13.33333333333333</v>
+        <v>33.00000000000001</v>
       </c>
       <c r="L102" t="s">
         <v>44</v>
@@ -48239,13 +48239,13 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="J103">
-        <v>0</v>
+        <v>2.884615384615385</v>
       </c>
       <c r="K103">
-        <v>13.33333333333333</v>
+        <v>17.95662100456621</v>
       </c>
       <c r="L103" t="s">
         <v>46</v>
@@ -48277,13 +48277,13 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>7.499999999999998</v>
+        <v>11.63385826771654</v>
       </c>
       <c r="J104">
-        <v>16.36363636363636</v>
+        <v>24.09801136363636</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="L104" t="s">
         <v>44</v>
@@ -48315,13 +48315,13 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="J105">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>13.80681818181818</v>
       </c>
       <c r="L105" t="s">
         <v>46</v>
@@ -48353,13 +48353,13 @@
         <v>0</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>2.538461538461538</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>1.071428571428572</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L106" t="s">
         <v>44</v>
@@ -48391,13 +48391,13 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>0.9183673469387754</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>3.461538461538461</v>
       </c>
       <c r="L107" t="s">
         <v>46</v>
@@ -48429,13 +48429,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I108">
-        <v>0</v>
+        <v>44.22043010752687</v>
       </c>
       <c r="J108">
-        <v>0</v>
+        <v>24.17910447761194</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L108" t="s">
         <v>44</v>
@@ -48467,13 +48467,13 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J109">
-        <v>0</v>
+        <v>1.205357142857143</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="L109" t="s">
         <v>46</v>
@@ -48505,13 +48505,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I110">
-        <v>359.9999999999999</v>
+        <v>372.4137931034482</v>
       </c>
       <c r="J110">
-        <v>255.7894736842105</v>
+        <v>442.4561403508771</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="L110" t="s">
         <v>44</v>
@@ -48543,13 +48543,13 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>17.83018867924528</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="L111" t="s">
         <v>46</v>
@@ -48581,13 +48581,13 @@
         <v>0</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>36.29032258064516</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>11.89024390243902</v>
       </c>
       <c r="K112">
-        <v>13.33333333333333</v>
+        <v>110</v>
       </c>
       <c r="L112" t="s">
         <v>31</v>
@@ -48619,13 +48619,13 @@
         <v>0</v>
       </c>
       <c r="I113">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="J113">
-        <v>0</v>
+        <v>3.409090909090909</v>
       </c>
       <c r="K113">
-        <v>13.33333333333333</v>
+        <v>160.8333333333333</v>
       </c>
       <c r="L113" t="s">
         <v>26</v>
@@ -48657,13 +48657,13 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>0</v>
+        <v>13.67763157894737</v>
       </c>
       <c r="J114">
-        <v>0</v>
+        <v>110.4545454545455</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="L114" t="s">
         <v>31</v>
@@ -48695,13 +48695,13 @@
         <v>0</v>
       </c>
       <c r="I115">
-        <v>0</v>
+        <v>2.465753424657534</v>
       </c>
       <c r="J115">
-        <v>0</v>
+        <v>6.97674418604651</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>8.18181818181818</v>
       </c>
       <c r="L115" t="s">
         <v>26</v>
@@ -48733,13 +48733,13 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>11.6015625</v>
       </c>
       <c r="L116" t="s">
         <v>31</v>
@@ -48771,13 +48771,13 @@
         <v>0</v>
       </c>
       <c r="I117">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>5.785714285714286</v>
       </c>
       <c r="L117" t="s">
         <v>26</v>
@@ -48809,13 +48809,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J118">
-        <v>0</v>
+        <v>34.33333333333334</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="L118" t="s">
         <v>31</v>
@@ -48847,13 +48847,13 @@
         <v>0</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="J119">
-        <v>11.25</v>
+        <v>15.25</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L119" t="s">
         <v>26</v>
@@ -48885,13 +48885,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I120">
-        <v>0</v>
+        <v>36.96969696969697</v>
       </c>
       <c r="J120">
-        <v>0</v>
+        <v>0.6716417910447761</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L120" t="s">
         <v>31</v>
@@ -48923,13 +48923,13 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>0</v>
+        <v>1.594488188976378</v>
       </c>
       <c r="J121">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K121">
-        <v>0</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="L121" t="s">
         <v>26</v>
@@ -48961,13 +48961,13 @@
         <v>0</v>
       </c>
       <c r="I122">
-        <v>0</v>
+        <v>8.088235294117647</v>
       </c>
       <c r="J122">
-        <v>0</v>
+        <v>7.075471698113208</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L122" t="s">
         <v>44</v>
@@ -49002,10 +49002,10 @@
         <v>0</v>
       </c>
       <c r="J123">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K123">
-        <v>0</v>
+        <v>5.431034482758621</v>
       </c>
       <c r="L123" t="s">
         <v>46</v>
@@ -49037,13 +49037,13 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>0</v>
+        <v>2.903225806451613</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>19.28571428571429</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>13.84615384615385</v>
       </c>
       <c r="L124" t="s">
         <v>44</v>
@@ -49075,13 +49075,13 @@
         <v>0</v>
       </c>
       <c r="I125">
-        <v>27</v>
+        <v>39.07317073170732</v>
       </c>
       <c r="J125">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>11.06707317073171</v>
       </c>
       <c r="L125" t="s">
         <v>46</v>
@@ -49116,10 +49116,10 @@
         <v>0</v>
       </c>
       <c r="J126">
-        <v>0</v>
+        <v>4.500000000000001</v>
       </c>
       <c r="K126">
-        <v>0</v>
+        <v>7.923913043478262</v>
       </c>
       <c r="L126" t="s">
         <v>44</v>
@@ -49151,13 +49151,13 @@
         <v>0</v>
       </c>
       <c r="I127">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J127">
-        <v>0</v>
+        <v>1.271186440677966</v>
       </c>
       <c r="K127">
-        <v>0</v>
+        <v>3.409090909090909</v>
       </c>
       <c r="L127" t="s">
         <v>46</v>
@@ -49189,13 +49189,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I128">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J128">
-        <v>0</v>
+        <v>4.687499999999999</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="L128" t="s">
         <v>44</v>
@@ -49227,13 +49227,13 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>2.307692307692308</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>2.769230769230769</v>
       </c>
       <c r="L129" t="s">
         <v>46</v>
@@ -49265,13 +49265,13 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>33.00000000000001</v>
       </c>
       <c r="J130">
-        <v>0</v>
+        <v>46.50000000000001</v>
       </c>
       <c r="K130">
-        <v>0</v>
+        <v>0.9183673469387756</v>
       </c>
       <c r="L130" t="s">
         <v>44</v>
@@ -49303,13 +49303,13 @@
         <v>0</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="J131">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>1.810344827586207</v>
       </c>
       <c r="L131" t="s">
         <v>46</v>
@@ -49341,13 +49341,13 @@
         <v>0</v>
       </c>
       <c r="I132">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J132">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K132">
-        <v>13.33333333333333</v>
+        <v>5.861842105263158</v>
       </c>
       <c r="L132" t="s">
         <v>31</v>
@@ -49379,13 +49379,13 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J133">
         <v>0</v>
       </c>
       <c r="K133">
-        <v>13.33333333333333</v>
+        <v>17.33333333333334</v>
       </c>
       <c r="L133" t="s">
         <v>26</v>
@@ -49417,13 +49417,13 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>0</v>
+        <v>7.620967741935483</v>
       </c>
       <c r="J134">
-        <v>0</v>
+        <v>4.655172413793104</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L134" t="s">
         <v>31</v>
@@ -49455,13 +49455,13 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="J135">
-        <v>0</v>
+        <v>33.00000000000001</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>2.410714285714286</v>
       </c>
       <c r="L135" t="s">
         <v>26</v>
@@ -49493,13 +49493,13 @@
         <v>0</v>
       </c>
       <c r="I136">
-        <v>0</v>
+        <v>1.546875</v>
       </c>
       <c r="J136">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="L136" t="s">
         <v>31</v>
@@ -49531,13 +49531,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I137">
-        <v>0</v>
+        <v>75.33333333333334</v>
       </c>
       <c r="J137">
-        <v>0</v>
+        <v>1.438356164383562</v>
       </c>
       <c r="K137">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="L137" t="s">
         <v>26</v>
@@ -49569,13 +49569,13 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <v>0</v>
+        <v>6.923076923076923</v>
       </c>
       <c r="J138">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>6.101694915254237</v>
       </c>
       <c r="L138" t="s">
         <v>31</v>
@@ -49610,10 +49610,10 @@
         <v>0</v>
       </c>
       <c r="J139">
-        <v>0</v>
+        <v>9.264705882352944</v>
       </c>
       <c r="K139">
-        <v>0</v>
+        <v>21.81818181818182</v>
       </c>
       <c r="L139" t="s">
         <v>26</v>
@@ -49645,10 +49645,10 @@
         <v>0</v>
       </c>
       <c r="I140">
-        <v>0</v>
+        <v>1.415094339622642</v>
       </c>
       <c r="J140">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="K140">
         <v>0</v>
@@ -49683,13 +49683,13 @@
         <v>0</v>
       </c>
       <c r="I141">
-        <v>0</v>
+        <v>6.057692307692307</v>
       </c>
       <c r="J141">
-        <v>0</v>
+        <v>3.841463414634147</v>
       </c>
       <c r="K141">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="L141" t="s">
         <v>26</v>
@@ -49721,13 +49721,13 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <v>0</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>1.2890625</v>
       </c>
       <c r="L142" t="s">
         <v>44</v>
@@ -49759,13 +49759,13 @@
         <v>100</v>
       </c>
       <c r="I143">
-        <v>0</v>
+        <v>40.65040650406504</v>
       </c>
       <c r="J143">
-        <v>0</v>
+        <v>69.33333333333334</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>153.3333333333333</v>
       </c>
       <c r="L143" t="s">
         <v>46</v>
@@ -49797,13 +49797,13 @@
         <v>0</v>
       </c>
       <c r="I144">
-        <v>0</v>
+        <v>5.689655172413794</v>
       </c>
       <c r="J144">
-        <v>0</v>
+        <v>13.30645161290322</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L144" t="s">
         <v>44</v>
@@ -49835,13 +49835,13 @@
         <v>0</v>
       </c>
       <c r="I145">
-        <v>0</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="J145">
-        <v>0</v>
+        <v>8.000000000000002</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="L145" t="s">
         <v>46</v>
@@ -49873,13 +49873,13 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <v>0</v>
+        <v>42.00000000000001</v>
       </c>
       <c r="J146">
-        <v>0</v>
+        <v>66.00000000000001</v>
       </c>
       <c r="K146">
-        <v>0</v>
+        <v>7.941176470588236</v>
       </c>
       <c r="L146" t="s">
         <v>44</v>
@@ -49911,10 +49911,10 @@
         <v>0</v>
       </c>
       <c r="I147">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="J147">
-        <v>0</v>
+        <v>1.062992125984252</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -49949,13 +49949,13 @@
         <v>0</v>
       </c>
       <c r="I148">
-        <v>0</v>
+        <v>2.686567164179104</v>
       </c>
       <c r="J148">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>1.395348837209302</v>
       </c>
       <c r="L148" t="s">
         <v>44</v>
@@ -49990,10 +49990,10 @@
         <v>0</v>
       </c>
       <c r="J149">
-        <v>0</v>
+        <v>51.11111111111112</v>
       </c>
       <c r="K149">
-        <v>0</v>
+        <v>3.673469387755102</v>
       </c>
       <c r="L149" t="s">
         <v>46</v>
@@ -50025,13 +50025,13 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J150">
-        <v>0</v>
+        <v>6.000000000000001</v>
       </c>
       <c r="K150">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L150" t="s">
         <v>44</v>
@@ -50063,13 +50063,13 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>0</v>
+        <v>1.534090909090909</v>
       </c>
       <c r="J151">
-        <v>0</v>
+        <v>1.875</v>
       </c>
       <c r="K151">
-        <v>0</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="L151" t="s">
         <v>46</v>
@@ -50101,13 +50101,13 @@
         <v>0</v>
       </c>
       <c r="I152">
-        <v>0</v>
+        <v>3.461538461538462</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>21.81818181818182</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>9.246575342465755</v>
       </c>
       <c r="L152" t="s">
         <v>31</v>
@@ -50139,13 +50139,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I153">
-        <v>0</v>
+        <v>60.00000000000001</v>
       </c>
       <c r="J153">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>35.52845528455285</v>
       </c>
       <c r="L153" t="s">
         <v>24</v>
@@ -50177,13 +50177,13 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <v>0</v>
+        <v>206.5</v>
       </c>
       <c r="J154">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K154">
-        <v>0</v>
+        <v>4.952830188679245</v>
       </c>
       <c r="L154" t="s">
         <v>31</v>
@@ -50215,13 +50215,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I155">
-        <v>0</v>
+        <v>43.63636363636365</v>
       </c>
       <c r="J155">
-        <v>0</v>
+        <v>2.109375</v>
       </c>
       <c r="K155">
-        <v>0</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="L155" t="s">
         <v>24</v>
@@ -50253,13 +50253,13 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="J156">
-        <v>0</v>
+        <v>60.00000000000001</v>
       </c>
       <c r="K156">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="L156" t="s">
         <v>31</v>
@@ -50294,10 +50294,10 @@
         <v>0</v>
       </c>
       <c r="J157">
-        <v>0</v>
+        <v>7.258064516129034</v>
       </c>
       <c r="K157">
-        <v>0</v>
+        <v>3.907894736842105</v>
       </c>
       <c r="L157" t="s">
         <v>24</v>
@@ -50329,13 +50329,13 @@
         <v>0</v>
       </c>
       <c r="I158">
-        <v>0</v>
+        <v>0.8823529411764708</v>
       </c>
       <c r="J158">
-        <v>0</v>
+        <v>4.500000000000001</v>
       </c>
       <c r="K158">
-        <v>0</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="L158" t="s">
         <v>31</v>
@@ -50367,13 +50367,13 @@
         <v>0</v>
       </c>
       <c r="I159">
-        <v>0</v>
+        <v>19.39655172413793</v>
       </c>
       <c r="J159">
-        <v>0</v>
+        <v>17.30769230769231</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="L159" t="s">
         <v>24</v>
@@ -50405,13 +50405,13 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="J160">
-        <v>0</v>
+        <v>6.614173228346456</v>
       </c>
       <c r="K160">
-        <v>0</v>
+        <v>8.597014925373132</v>
       </c>
       <c r="L160" t="s">
         <v>31</v>
@@ -50443,13 +50443,13 @@
         <v>0</v>
       </c>
       <c r="I161">
-        <v>0</v>
+        <v>5.785714285714286</v>
       </c>
       <c r="J161">
-        <v>0</v>
+        <v>1.395348837209302</v>
       </c>
       <c r="K161">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L161" t="s">
         <v>24</v>
@@ -50481,13 +50481,13 @@
         <v>0</v>
       </c>
       <c r="I162">
-        <v>0</v>
+        <v>6.000000000000001</v>
       </c>
       <c r="J162">
-        <v>0</v>
+        <v>66.00000000000001</v>
       </c>
       <c r="K162">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L162" t="s">
         <v>44</v>
@@ -50519,13 +50519,13 @@
         <v>66.66666666666666</v>
       </c>
       <c r="I163">
-        <v>0</v>
+        <v>48.88888888888889</v>
       </c>
       <c r="J163">
-        <v>0</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="K163">
-        <v>0</v>
+        <v>43.33333333333333</v>
       </c>
       <c r="L163" t="s">
         <v>46</v>
@@ -50557,13 +50557,13 @@
         <v>0</v>
       </c>
       <c r="I164">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="J164">
-        <v>0</v>
+        <v>2.295918367346939</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="L164" t="s">
         <v>44</v>
@@ -50595,13 +50595,13 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <v>0</v>
+        <v>110.4545454545455</v>
       </c>
       <c r="J165">
         <v>0</v>
       </c>
       <c r="K165">
-        <v>0</v>
+        <v>7.500000000000003</v>
       </c>
       <c r="L165" t="s">
         <v>46</v>
@@ -50633,13 +50633,13 @@
         <v>0</v>
       </c>
       <c r="I166">
-        <v>0</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="J166">
-        <v>13.33333333333333</v>
+        <v>16.07723577235772</v>
       </c>
       <c r="K166">
-        <v>0</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="L166" t="s">
         <v>44</v>
@@ -50671,13 +50671,13 @@
         <v>0</v>
       </c>
       <c r="I167">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J167">
-        <v>0</v>
+        <v>1.071428571428572</v>
       </c>
       <c r="K167">
-        <v>0</v>
+        <v>8.18181818181818</v>
       </c>
       <c r="L167" t="s">
         <v>46</v>
@@ -50709,10 +50709,10 @@
         <v>0</v>
       </c>
       <c r="I168">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J168">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K168">
         <v>0</v>
@@ -50750,10 +50750,10 @@
         <v>0</v>
       </c>
       <c r="J169">
-        <v>0</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="K169">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L169" t="s">
         <v>46</v>
@@ -50785,13 +50785,13 @@
         <v>0</v>
       </c>
       <c r="I170">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J170">
-        <v>13.33333333333333</v>
+        <v>14.20175438596491</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L170" t="s">
         <v>44</v>
@@ -50823,13 +50823,13 @@
         <v>0</v>
       </c>
       <c r="I171">
-        <v>0</v>
+        <v>1.451612903225807</v>
       </c>
       <c r="J171">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="K171">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L171" t="s">
         <v>46</v>
@@ -50861,13 +50861,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I172">
-        <v>0</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="J172">
-        <v>0</v>
+        <v>38.64829396325459</v>
       </c>
       <c r="K172">
-        <v>0</v>
+        <v>3.515624999999999</v>
       </c>
       <c r="L172" t="s">
         <v>31</v>
@@ -50899,13 +50899,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I173">
-        <v>0</v>
+        <v>13.99390243902439</v>
       </c>
       <c r="J173">
-        <v>0</v>
+        <v>9.671641791044774</v>
       </c>
       <c r="K173">
-        <v>0</v>
+        <v>40.29427083333333</v>
       </c>
       <c r="L173" t="s">
         <v>26</v>
@@ -50937,13 +50937,13 @@
         <v>0</v>
       </c>
       <c r="I174">
-        <v>0</v>
+        <v>6.164383561643835</v>
       </c>
       <c r="J174">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K174">
-        <v>0</v>
+        <v>8.490566037735849</v>
       </c>
       <c r="L174" t="s">
         <v>31</v>
@@ -50975,13 +50975,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I175">
-        <v>0</v>
+        <v>66.33333333333333</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="K175">
-        <v>0</v>
+        <v>46.50000000000001</v>
       </c>
       <c r="L175" t="s">
         <v>26</v>
@@ -51013,13 +51013,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I176">
-        <v>13.33333333333333</v>
+        <v>18.33333333333334</v>
       </c>
       <c r="J176">
         <v>0</v>
       </c>
       <c r="K176">
-        <v>0</v>
+        <v>94.6969696969697</v>
       </c>
       <c r="L176" t="s">
         <v>31</v>
@@ -51051,13 +51051,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I177">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="K177">
-        <v>0</v>
+        <v>85.33333333333333</v>
       </c>
       <c r="L177" t="s">
         <v>26</v>
@@ -51092,10 +51092,10 @@
         <v>0</v>
       </c>
       <c r="J178">
-        <v>0</v>
+        <v>4.261363636363636</v>
       </c>
       <c r="K178">
-        <v>0</v>
+        <v>3.879310344827586</v>
       </c>
       <c r="L178" t="s">
         <v>31</v>
@@ -51127,13 +51127,13 @@
         <v>66.66666666666666</v>
       </c>
       <c r="I179">
-        <v>0</v>
+        <v>73.51190476190477</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="K179">
-        <v>0</v>
+        <v>38.50574712643678</v>
       </c>
       <c r="L179" t="s">
         <v>26</v>
@@ -51165,13 +51165,13 @@
         <v>0</v>
       </c>
       <c r="I180">
-        <v>0</v>
+        <v>44.00000000000001</v>
       </c>
       <c r="J180">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K180">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="L180" t="s">
         <v>31</v>
@@ -51203,13 +51203,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I181">
-        <v>0</v>
+        <v>4.821428571428572</v>
       </c>
       <c r="J181">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K181">
-        <v>0</v>
+        <v>70.15151515151516</v>
       </c>
       <c r="L181" t="s">
         <v>26</v>
@@ -51244,10 +51244,10 @@
         <v>0</v>
       </c>
       <c r="J182">
-        <v>0</v>
+        <v>1.935483870967742</v>
       </c>
       <c r="K182">
-        <v>0</v>
+        <v>6.428571428571428</v>
       </c>
       <c r="L182" t="s">
         <v>44</v>
@@ -51279,13 +51279,13 @@
         <v>0</v>
       </c>
       <c r="I183">
-        <v>0</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="J183">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K183">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L183" t="s">
         <v>46</v>
@@ -51317,13 +51317,13 @@
         <v>0</v>
       </c>
       <c r="I184">
-        <v>0</v>
+        <v>77.00000000000001</v>
       </c>
       <c r="J184">
-        <v>0</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="K184">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="L184" t="s">
         <v>44</v>
@@ -51358,10 +51358,10 @@
         <v>0</v>
       </c>
       <c r="J185">
-        <v>89.99999999999999</v>
+        <v>133.3333333333333</v>
       </c>
       <c r="K185">
-        <v>0</v>
+        <v>3.488372093023255</v>
       </c>
       <c r="L185" t="s">
         <v>46</v>
@@ -51393,13 +51393,13 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>0</v>
+        <v>1.928571428571428</v>
       </c>
       <c r="J186">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K186">
-        <v>0</v>
+        <v>8.000000000000002</v>
       </c>
       <c r="L186" t="s">
         <v>44</v>
@@ -51431,13 +51431,13 @@
         <v>0</v>
       </c>
       <c r="I187">
-        <v>0</v>
+        <v>14.54545454545455</v>
       </c>
       <c r="J187">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K187">
-        <v>0</v>
+        <v>4.615384615384616</v>
       </c>
       <c r="L187" t="s">
         <v>46</v>
@@ -51469,13 +51469,13 @@
         <v>0</v>
       </c>
       <c r="I188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J188">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K188">
-        <v>0</v>
+        <v>4.125000000000001</v>
       </c>
       <c r="L188" t="s">
         <v>44</v>
@@ -51507,10 +51507,10 @@
         <v>33.33333333333333</v>
       </c>
       <c r="I189">
-        <v>16.36363636363636</v>
+        <v>238.7878787878788</v>
       </c>
       <c r="J189">
-        <v>16.36363636363636</v>
+        <v>205.4545454545455</v>
       </c>
       <c r="K189">
         <v>0</v>

--- a/output_data.xlsx
+++ b/output_data.xlsx
@@ -1575,7 +1575,7 @@
     <t>Climb%</t>
   </si>
   <si>
-    <t>robot1</t>
+    <t>robot1%</t>
   </si>
   <si>
     <t>robot2%</t>
@@ -1612,12 +1612,42 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF008000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF800080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1632,8 +1662,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -44388,7 +44423,7 @@
       <c r="C2" t="s">
         <v>503</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>35</v>
       </c>
       <c r="E2">
@@ -44400,22 +44435,22 @@
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>3.559322033898305</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>7.000000000000001</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -44426,7 +44461,7 @@
       <c r="C3" t="s">
         <v>504</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>15</v>
       </c>
       <c r="E3">
@@ -44438,22 +44473,22 @@
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>2.125984251968504</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>0.9246575342465754</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>3.214285714285715</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -44464,7 +44499,7 @@
       <c r="C4" t="s">
         <v>503</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>15</v>
       </c>
       <c r="E4">
@@ -44476,22 +44511,22 @@
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>39.00000000000001</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>15</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>33.00000000000001</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -44502,7 +44537,7 @@
       <c r="C5" t="s">
         <v>504</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>44.99999999999999</v>
       </c>
       <c r="E5">
@@ -44514,22 +44549,22 @@
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="4">
         <v>130.9090909090909</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="4">
         <v>391.4999999999999</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>13.5</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -44540,7 +44575,7 @@
       <c r="C6" t="s">
         <v>503</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>5</v>
       </c>
       <c r="E6">
@@ -44552,22 +44587,22 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>7.500000000000001</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>1.569767441860465</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0.576923076923077</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -44578,7 +44613,7 @@
       <c r="C7" t="s">
         <v>504</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>10</v>
       </c>
       <c r="E7">
@@ -44590,22 +44625,22 @@
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>0.7031249999999999</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>31.00000000000001</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>4.000000000000001</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -44616,7 +44651,7 @@
       <c r="C8" t="s">
         <v>503</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>58.33333333333333</v>
       </c>
       <c r="E8">
@@ -44628,22 +44663,22 @@
       <c r="G8">
         <v>33.33333333333333</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>35.91954022988506</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>6.923076923076922</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>8.333333333333334</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -44654,7 +44689,7 @@
       <c r="C9" t="s">
         <v>504</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>33.33333333333333</v>
       </c>
       <c r="E9">
@@ -44666,22 +44701,22 @@
       <c r="G9">
         <v>33.33333333333333</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>33.33333333333333</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -44692,7 +44727,7 @@
       <c r="C10" t="s">
         <v>503</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>111.6666666666667</v>
       </c>
       <c r="E10">
@@ -44704,22 +44739,22 @@
       <c r="G10">
         <v>66.66666666666666</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="3">
         <v>57.46969696969697</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="4">
         <v>101.6666666666667</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>33.33333333333333</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -44730,7 +44765,7 @@
       <c r="C11" t="s">
         <v>504</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="4">
         <v>73.33333333333333</v>
       </c>
       <c r="E11">
@@ -44742,22 +44777,22 @@
       <c r="G11">
         <v>33.33333333333333</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>14.66666666666667</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>39.13978494623655</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="4">
         <v>328</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -44768,7 +44803,7 @@
       <c r="C12" t="s">
         <v>503</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <v>55</v>
       </c>
       <c r="E12">
@@ -44780,22 +44815,22 @@
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>0</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>27.5</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="4">
         <v>277.5</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -44806,7 +44841,7 @@
       <c r="C13" t="s">
         <v>504</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="3">
         <v>44.99999999999999</v>
       </c>
       <c r="E13">
@@ -44818,22 +44853,22 @@
       <c r="G13">
         <v>0</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="4">
         <v>139.5</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="3">
         <v>41.24999999999999</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="4">
         <v>126</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N13" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -44844,7 +44879,7 @@
       <c r="C14" t="s">
         <v>503</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>5</v>
       </c>
       <c r="E14">
@@ -44856,22 +44891,22 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>3</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>6</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>20.5</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N14" t="s">
+      <c r="N14" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -44882,7 +44917,7 @@
       <c r="C15" t="s">
         <v>504</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="3">
         <v>48.33333333333333</v>
       </c>
       <c r="E15">
@@ -44894,22 +44929,22 @@
       <c r="G15">
         <v>33.33333333333333</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>0</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>36.33333333333334</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>13.5</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M15" t="s">
+      <c r="M15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N15" t="s">
+      <c r="N15" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -44920,7 +44955,7 @@
       <c r="C16" t="s">
         <v>503</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16">
@@ -44932,22 +44967,22 @@
       <c r="G16">
         <v>0</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>0</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>0</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>0</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -44958,7 +44993,7 @@
       <c r="C17" t="s">
         <v>504</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="3">
         <v>43.33333333333334</v>
       </c>
       <c r="E17">
@@ -44970,22 +45005,22 @@
       <c r="G17">
         <v>0</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>27</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="3">
         <v>66</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>17.57861635220126</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N17" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -44996,7 +45031,7 @@
       <c r="C18" t="s">
         <v>503</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>5</v>
       </c>
       <c r="E18">
@@ -45008,22 +45043,22 @@
       <c r="G18">
         <v>0</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>28</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>17</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>22</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N18" t="s">
+      <c r="N18" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -45034,7 +45069,7 @@
       <c r="C19" t="s">
         <v>504</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="3">
         <v>45.00000000000001</v>
       </c>
       <c r="E19">
@@ -45046,22 +45081,22 @@
       <c r="G19">
         <v>0</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>5.861842105263158</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>8.678571428571429</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>22.5</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N19" t="s">
+      <c r="N19" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -45072,7 +45107,7 @@
       <c r="C20" t="s">
         <v>503</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>20</v>
       </c>
       <c r="E20">
@@ -45084,22 +45119,22 @@
       <c r="G20">
         <v>0</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>36</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>5.172413793103449</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="3">
         <v>58.18181818181819</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N20" t="s">
+      <c r="N20" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -45110,7 +45145,7 @@
       <c r="C21" t="s">
         <v>504</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="3">
         <v>53.33333333333333</v>
       </c>
       <c r="E21">
@@ -45122,22 +45157,22 @@
       <c r="G21">
         <v>33.33333333333333</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="4">
         <v>86.00000000000001</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="3">
         <v>44.58333333333333</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>6.428571428571428</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M21" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N21" t="s">
+      <c r="N21" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -45148,7 +45183,7 @@
       <c r="C22" t="s">
         <v>503</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>5</v>
       </c>
       <c r="E22">
@@ -45160,22 +45195,22 @@
       <c r="G22">
         <v>0</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>1.027397260273973</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>3.888888888888889</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>4.5</v>
       </c>
-      <c r="L22" t="s">
+      <c r="L22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N22" t="s">
+      <c r="N22" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -45186,7 +45221,7 @@
       <c r="C23" t="s">
         <v>504</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="3">
         <v>45.00000000000001</v>
       </c>
       <c r="E23">
@@ -45198,22 +45233,22 @@
       <c r="G23">
         <v>0</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="1">
         <v>9.254032258064518</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="1">
         <v>18</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>13.5</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M23" t="s">
+      <c r="M23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N23" t="s">
+      <c r="N23" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -45224,7 +45259,7 @@
       <c r="C24" t="s">
         <v>503</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>15</v>
       </c>
       <c r="E24">
@@ -45236,22 +45271,22 @@
       <c r="G24">
         <v>0</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="1">
         <v>3.879310344827587</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="1">
         <v>3</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>6.000000000000001</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M24" t="s">
+      <c r="M24" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N24" t="s">
+      <c r="N24" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -45262,7 +45297,7 @@
       <c r="C25" t="s">
         <v>504</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="4">
         <v>136.6666666666667</v>
       </c>
       <c r="E25">
@@ -45274,22 +45309,22 @@
       <c r="G25">
         <v>66.66666666666666</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="1">
         <v>6.402439024390244</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="3">
         <v>45.65942028985507</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="3">
         <v>53.92156862745098</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M25" t="s">
+      <c r="M25" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N25" t="s">
+      <c r="N25" s="5" t="s">
         <v>35</v>
       </c>
     </row>
@@ -45300,7 +45335,7 @@
       <c r="C26" t="s">
         <v>503</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="3">
         <v>58.33333333333334</v>
       </c>
       <c r="E26">
@@ -45312,22 +45347,22 @@
       <c r="G26">
         <v>0</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="1">
         <v>33.75</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="1">
         <v>13.33333333333333</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="3">
         <v>45</v>
       </c>
-      <c r="L26" t="s">
+      <c r="L26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M26" t="s">
+      <c r="M26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N26" t="s">
+      <c r="N26" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -45338,7 +45373,7 @@
       <c r="C27" t="s">
         <v>504</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>25</v>
       </c>
       <c r="E27">
@@ -45350,22 +45385,22 @@
       <c r="G27">
         <v>0</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="1">
         <v>5.192307692307692</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="3">
         <v>61.36363636363637</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>8.231707317073171</v>
       </c>
-      <c r="L27" t="s">
+      <c r="L27" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M27" t="s">
+      <c r="M27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N27" t="s">
+      <c r="N27" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -45376,7 +45411,7 @@
       <c r="C28" t="s">
         <v>503</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>20</v>
       </c>
       <c r="E28">
@@ -45388,22 +45423,22 @@
       <c r="G28">
         <v>0</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="1">
         <v>2.307692307692308</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
         <v>0</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="3">
         <v>62.00000000000001</v>
       </c>
-      <c r="L28" t="s">
+      <c r="L28" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M28" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N28" t="s">
+      <c r="N28" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -45414,7 +45449,7 @@
       <c r="C29" t="s">
         <v>504</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>5</v>
       </c>
       <c r="E29">
@@ -45426,22 +45461,22 @@
       <c r="G29">
         <v>0</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="1">
         <v>1.363636363636364</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
         <v>11</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>0.4724409448818898</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L29" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M29" t="s">
+      <c r="M29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N29" t="s">
+      <c r="N29" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -45452,7 +45487,7 @@
       <c r="C30" t="s">
         <v>503</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>20</v>
       </c>
       <c r="E30">
@@ -45464,22 +45499,22 @@
       <c r="G30">
         <v>0</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="1">
         <v>30</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="1">
         <v>2.666666666666667</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="3">
         <v>55.99999999999999</v>
       </c>
-      <c r="L30" t="s">
+      <c r="L30" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M30" t="s">
+      <c r="M30" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N30" t="s">
+      <c r="N30" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -45490,7 +45525,7 @@
       <c r="C31" t="s">
         <v>504</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31">
@@ -45502,22 +45537,22 @@
       <c r="G31">
         <v>0</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="1">
         <v>0</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="1">
         <v>0</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>0</v>
       </c>
-      <c r="L31" t="s">
+      <c r="L31" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M31" t="s">
+      <c r="M31" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N31" t="s">
+      <c r="N31" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -45528,7 +45563,7 @@
       <c r="C32" t="s">
         <v>503</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>33.33333333333333</v>
       </c>
       <c r="E32">
@@ -45540,22 +45575,22 @@
       <c r="G32">
         <v>33.33333333333333</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="1">
         <v>0</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="1">
         <v>33.33333333333333</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>0</v>
       </c>
-      <c r="L32" t="s">
+      <c r="L32" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M32" t="s">
+      <c r="M32" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="N32" t="s">
+      <c r="N32" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -45566,7 +45601,7 @@
       <c r="C33" t="s">
         <v>504</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>10</v>
       </c>
       <c r="E33">
@@ -45578,22 +45613,22 @@
       <c r="G33">
         <v>0</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="1">
         <v>30</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="1">
         <v>0</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>5</v>
       </c>
-      <c r="L33" t="s">
+      <c r="L33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M33" t="s">
+      <c r="M33" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N33" t="s">
+      <c r="N33" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -45604,7 +45639,7 @@
       <c r="C34" t="s">
         <v>503</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>40</v>
       </c>
       <c r="E34">
@@ -45616,22 +45651,22 @@
       <c r="G34">
         <v>0</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="1">
         <v>12.27272727272727</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="1">
         <v>27.27272727272727</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>0</v>
       </c>
-      <c r="L34" t="s">
+      <c r="L34" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M34" t="s">
+      <c r="M34" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N34" t="s">
+      <c r="N34" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -45642,7 +45677,7 @@
       <c r="C35" t="s">
         <v>504</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="3">
         <v>43.33333333333333</v>
       </c>
       <c r="E35">
@@ -45654,22 +45689,22 @@
       <c r="G35">
         <v>33.33333333333333</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="1">
         <v>1.171875</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="1">
         <v>0.6122448979591837</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="1">
         <v>35.75124378109453</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M35" t="s">
+      <c r="M35" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N35" t="s">
+      <c r="N35" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -45680,7 +45715,7 @@
       <c r="C36" t="s">
         <v>503</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="1">
         <v>10</v>
       </c>
       <c r="E36">
@@ -45692,22 +45727,22 @@
       <c r="G36">
         <v>0</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="1">
         <v>1.415094339622642</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="1">
         <v>2.5</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="1">
         <v>8.000000000000002</v>
       </c>
-      <c r="L36" t="s">
+      <c r="L36" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M36" t="s">
+      <c r="M36" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N36" t="s">
+      <c r="N36" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -45718,7 +45753,7 @@
       <c r="C37" t="s">
         <v>504</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="4">
         <v>96.66666666666666</v>
       </c>
       <c r="E37">
@@ -45730,22 +45765,22 @@
       <c r="G37">
         <v>66.66666666666666</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="3">
         <v>43.92156862745098</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="3">
         <v>46.66666666666667</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="3">
         <v>69.33333333333334</v>
       </c>
-      <c r="L37" t="s">
+      <c r="L37" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M37" t="s">
+      <c r="M37" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N37" t="s">
+      <c r="N37" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -45756,7 +45791,7 @@
       <c r="C38" t="s">
         <v>503</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="3">
         <v>53.33333333333333</v>
       </c>
       <c r="E38">
@@ -45768,22 +45803,22 @@
       <c r="G38">
         <v>33.33333333333333</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="1">
         <v>22</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="1">
         <v>18</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="4">
         <v>82.42424242424242</v>
       </c>
-      <c r="L38" t="s">
+      <c r="L38" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M38" t="s">
+      <c r="M38" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N38" t="s">
+      <c r="N38" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -45794,7 +45829,7 @@
       <c r="C39" t="s">
         <v>504</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="4">
         <v>78.33333333333331</v>
       </c>
       <c r="E39">
@@ -45806,22 +45841,22 @@
       <c r="G39">
         <v>33.33333333333333</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="1">
         <v>19.44915254237288</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="3">
         <v>55.83333333333334</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="4">
         <v>391.4999999999999</v>
       </c>
-      <c r="L39" t="s">
+      <c r="L39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M39" t="s">
+      <c r="M39" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N39" t="s">
+      <c r="N39" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -45832,7 +45867,7 @@
       <c r="C40" t="s">
         <v>503</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="3">
         <v>55</v>
       </c>
       <c r="E40">
@@ -45844,22 +45879,22 @@
       <c r="G40">
         <v>0</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="1">
         <v>28.22727272727272</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="1">
         <v>20.53846153846154</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="1">
         <v>2.721774193548387</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L40" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M40" t="s">
+      <c r="M40" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N40" t="s">
+      <c r="N40" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -45870,7 +45905,7 @@
       <c r="C41" t="s">
         <v>504</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="3">
         <v>48.33333333333333</v>
       </c>
       <c r="E41">
@@ -45882,22 +45917,22 @@
       <c r="G41">
         <v>33.33333333333333</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="3">
         <v>64.50000000000003</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="1">
         <v>9.000000000000002</v>
       </c>
-      <c r="K41">
+      <c r="K41" s="4">
         <v>76.96969696969698</v>
       </c>
-      <c r="L41" t="s">
+      <c r="L41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M41" t="s">
+      <c r="M41" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N41" t="s">
+      <c r="N41" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -45908,7 +45943,7 @@
       <c r="C42" t="s">
         <v>503</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="1">
         <v>30</v>
       </c>
       <c r="E42">
@@ -45920,22 +45955,22 @@
       <c r="G42">
         <v>0</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="1">
         <v>8.231707317073173</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="1">
         <v>0</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="1">
         <v>27</v>
       </c>
-      <c r="L42" t="s">
+      <c r="L42" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M42" t="s">
+      <c r="M42" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N42" t="s">
+      <c r="N42" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -45946,7 +45981,7 @@
       <c r="C43" t="s">
         <v>504</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43">
@@ -45958,22 +45993,22 @@
       <c r="G43">
         <v>0</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="1">
         <v>0</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="1">
         <v>0</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="1">
         <v>0</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L43" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M43" t="s">
+      <c r="M43" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N43" t="s">
+      <c r="N43" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -45984,7 +46019,7 @@
       <c r="C44" t="s">
         <v>503</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="1">
         <v>38.33333333333333</v>
       </c>
       <c r="E44">
@@ -45996,22 +46031,22 @@
       <c r="G44">
         <v>33.33333333333333</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="1">
         <v>1</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="1">
         <v>4.500000000000001</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="1">
         <v>34.19871794871795</v>
       </c>
-      <c r="L44" t="s">
+      <c r="L44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M44" t="s">
+      <c r="M44" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N44" t="s">
+      <c r="N44" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -46022,7 +46057,7 @@
       <c r="C45" t="s">
         <v>504</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="1">
         <v>10</v>
       </c>
       <c r="E45">
@@ -46034,22 +46069,22 @@
       <c r="G45">
         <v>0</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="1">
         <v>14</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="1">
         <v>31.00000000000001</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="1">
         <v>15</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L45" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M45" t="s">
+      <c r="M45" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N45" t="s">
+      <c r="N45" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -46060,7 +46095,7 @@
       <c r="C46" t="s">
         <v>503</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="1">
         <v>25</v>
       </c>
       <c r="E46">
@@ -46072,22 +46107,22 @@
       <c r="G46">
         <v>0</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="1">
         <v>2.34375</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="1">
         <v>9.642857142857144</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="4">
         <v>110</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M46" t="s">
+      <c r="M46" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N46" t="s">
+      <c r="N46" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -46098,7 +46133,7 @@
       <c r="C47" t="s">
         <v>504</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="3">
         <v>68.33333333333333</v>
       </c>
       <c r="E47">
@@ -46110,22 +46145,22 @@
       <c r="G47">
         <v>33.33333333333333</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="1">
         <v>25.45454545454546</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="4">
         <v>229.3333333333333</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="1">
         <v>35</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L47" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M47" t="s">
+      <c r="M47" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N47" t="s">
+      <c r="N47" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -46136,7 +46171,7 @@
       <c r="C48" t="s">
         <v>503</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="1">
         <v>10</v>
       </c>
       <c r="E48">
@@ -46148,22 +46183,22 @@
       <c r="G48">
         <v>0</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="1">
         <v>2</v>
       </c>
-      <c r="J48">
+      <c r="J48" s="1">
         <v>7.500000000000001</v>
       </c>
-      <c r="K48">
+      <c r="K48" s="3">
         <v>45</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L48" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M48" t="s">
+      <c r="M48" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N48" t="s">
+      <c r="N48" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -46174,7 +46209,7 @@
       <c r="C49" t="s">
         <v>504</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="1">
         <v>10</v>
       </c>
       <c r="E49">
@@ -46186,22 +46221,22 @@
       <c r="G49">
         <v>0</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="1">
         <v>0</v>
       </c>
-      <c r="J49">
+      <c r="J49" s="1">
         <v>4.000000000000001</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="1">
         <v>1.363636363636364</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L49" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M49" t="s">
+      <c r="M49" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N49" t="s">
+      <c r="N49" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -46212,7 +46247,7 @@
       <c r="C50" t="s">
         <v>503</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="1">
         <v>35</v>
       </c>
       <c r="E50">
@@ -46224,22 +46259,22 @@
       <c r="G50">
         <v>0</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="1">
         <v>17.5</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="1">
         <v>10.5</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="1">
         <v>15</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L50" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M50" t="s">
+      <c r="M50" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N50" t="s">
+      <c r="N50" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -46250,7 +46285,7 @@
       <c r="C51" t="s">
         <v>504</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="1">
         <v>20</v>
       </c>
       <c r="E51">
@@ -46262,22 +46297,22 @@
       <c r="G51">
         <v>0</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="1">
         <v>4.000000000000001</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="1">
         <v>24</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="1">
         <v>3.543307086614174</v>
       </c>
-      <c r="L51" t="s">
+      <c r="L51" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M51" t="s">
+      <c r="M51" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N51" t="s">
+      <c r="N51" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -46288,7 +46323,7 @@
       <c r="C52" t="s">
         <v>503</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="4">
         <v>93.33333333333333</v>
       </c>
       <c r="E52">
@@ -46300,22 +46335,22 @@
       <c r="G52">
         <v>33.33333333333333</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="1">
         <v>15.88235294117647</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="4">
         <v>183.3333333333333</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="1">
         <v>0</v>
       </c>
-      <c r="L52" t="s">
+      <c r="L52" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M52" t="s">
+      <c r="M52" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N52" t="s">
+      <c r="N52" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -46326,7 +46361,7 @@
       <c r="C53" t="s">
         <v>504</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="3">
         <v>50</v>
       </c>
       <c r="E53">
@@ -46338,22 +46373,22 @@
       <c r="G53">
         <v>0</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="1">
         <v>23.08474576271187</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="1">
         <v>10.58823529411765</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="1">
         <v>22</v>
       </c>
-      <c r="L53" t="s">
+      <c r="L53" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M53" t="s">
+      <c r="M53" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N53" t="s">
+      <c r="N53" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -46364,7 +46399,7 @@
       <c r="C54" t="s">
         <v>503</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="1">
         <v>5</v>
       </c>
       <c r="E54">
@@ -46376,22 +46411,22 @@
       <c r="G54">
         <v>0</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="1">
         <v>4.500000000000001</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="1">
         <v>0</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="1">
         <v>4.000000000000001</v>
       </c>
-      <c r="L54" t="s">
+      <c r="L54" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M54" t="s">
+      <c r="M54" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N54" t="s">
+      <c r="N54" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -46402,7 +46437,7 @@
       <c r="C55" t="s">
         <v>504</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="3">
         <v>45.00000000000001</v>
       </c>
       <c r="E55">
@@ -46414,22 +46449,22 @@
       <c r="G55">
         <v>0</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="1">
         <v>11.63793103448276</v>
       </c>
-      <c r="J55">
+      <c r="J55" s="1">
         <v>6.367924528301888</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="1">
         <v>4.835820895522388</v>
       </c>
-      <c r="L55" t="s">
+      <c r="L55" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M55" t="s">
+      <c r="M55" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N55" t="s">
+      <c r="N55" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -46440,7 +46475,7 @@
       <c r="C56" t="s">
         <v>503</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="3">
         <v>58.33333333333333</v>
       </c>
       <c r="E56">
@@ -46452,22 +46487,22 @@
       <c r="G56">
         <v>33.33333333333333</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="1">
         <v>5.88235294117647</v>
       </c>
-      <c r="J56">
+      <c r="J56" s="1">
         <v>38.88888888888889</v>
       </c>
-      <c r="K56">
+      <c r="K56" s="3">
         <v>47.84946236559139</v>
       </c>
-      <c r="L56" t="s">
+      <c r="L56" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M56" t="s">
+      <c r="M56" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N56" t="s">
+      <c r="N56" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -46478,7 +46513,7 @@
       <c r="C57" t="s">
         <v>504</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="4">
         <v>73.33333333333333</v>
       </c>
       <c r="E57">
@@ -46490,22 +46525,22 @@
       <c r="G57">
         <v>33.33333333333333</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="1">
         <v>2.769230769230769</v>
       </c>
-      <c r="J57">
+      <c r="J57" s="1">
         <v>34.97716894977169</v>
       </c>
-      <c r="K57">
+      <c r="K57" s="1">
         <v>7.043478260869564</v>
       </c>
-      <c r="L57" t="s">
+      <c r="L57" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M57" t="s">
+      <c r="M57" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N57" t="s">
+      <c r="N57" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -46516,7 +46551,7 @@
       <c r="C58" t="s">
         <v>503</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="3">
         <v>50</v>
       </c>
       <c r="E58">
@@ -46528,22 +46563,22 @@
       <c r="G58">
         <v>0</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="1">
         <v>12</v>
       </c>
-      <c r="J58">
+      <c r="J58" s="1">
         <v>28</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="3">
         <v>48.46153846153845</v>
       </c>
-      <c r="L58" t="s">
+      <c r="L58" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M58" t="s">
+      <c r="M58" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N58" t="s">
+      <c r="N58" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -46554,7 +46589,7 @@
       <c r="C59" t="s">
         <v>504</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="1">
         <v>18.33333333333334</v>
       </c>
       <c r="E59">
@@ -46566,22 +46601,22 @@
       <c r="G59">
         <v>0</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="1">
         <v>34.54545454545455</v>
       </c>
-      <c r="J59">
+      <c r="J59" s="1">
         <v>4.5</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="3">
         <v>41.33333333333334</v>
       </c>
-      <c r="L59" t="s">
+      <c r="L59" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M59" t="s">
+      <c r="M59" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N59" t="s">
+      <c r="N59" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -46592,7 +46627,7 @@
       <c r="C60" t="s">
         <v>503</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="1">
         <v>35</v>
       </c>
       <c r="E60">
@@ -46604,22 +46639,22 @@
       <c r="G60">
         <v>0</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="1">
         <v>13.5</v>
       </c>
-      <c r="J60">
+      <c r="J60" s="1">
         <v>8.04435483870968</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="1">
         <v>8.555555555555557</v>
       </c>
-      <c r="L60" t="s">
+      <c r="L60" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M60" t="s">
+      <c r="M60" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N60" t="s">
+      <c r="N60" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -46630,7 +46665,7 @@
       <c r="C61" t="s">
         <v>504</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="1">
         <v>40</v>
       </c>
       <c r="E61">
@@ -46642,22 +46677,22 @@
       <c r="G61">
         <v>0</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="1">
         <v>26</v>
       </c>
-      <c r="J61">
+      <c r="J61" s="3">
         <v>45.45454545454546</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="3">
         <v>44.5</v>
       </c>
-      <c r="L61" t="s">
+      <c r="L61" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M61" t="s">
+      <c r="M61" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N61" t="s">
+      <c r="N61" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -46668,7 +46703,7 @@
       <c r="C62" t="s">
         <v>503</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="3">
         <v>55.00000000000001</v>
       </c>
       <c r="E62">
@@ -46680,22 +46715,22 @@
       <c r="G62">
         <v>0</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="1">
         <v>13.43023255813953</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="1">
         <v>3.01829268292683</v>
       </c>
-      <c r="K62">
+      <c r="K62" s="3">
         <v>47.90322580645161</v>
       </c>
-      <c r="L62" t="s">
+      <c r="L62" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M62" t="s">
+      <c r="M62" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N62" t="s">
+      <c r="N62" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -46706,7 +46741,7 @@
       <c r="C63" t="s">
         <v>504</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="1">
         <v>5</v>
       </c>
       <c r="E63">
@@ -46718,22 +46753,22 @@
       <c r="G63">
         <v>0</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="1">
         <v>0</v>
       </c>
-      <c r="J63">
+      <c r="J63" s="1">
         <v>0.5113636363636362</v>
       </c>
-      <c r="K63">
+      <c r="K63" s="1">
         <v>6</v>
       </c>
-      <c r="L63" t="s">
+      <c r="L63" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M63" t="s">
+      <c r="M63" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N63" t="s">
+      <c r="N63" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -46744,7 +46779,7 @@
       <c r="C64" t="s">
         <v>503</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="1">
         <v>5</v>
       </c>
       <c r="E64">
@@ -46756,22 +46791,22 @@
       <c r="G64">
         <v>0</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="1">
         <v>0.6818181818181818</v>
       </c>
-      <c r="J64">
+      <c r="J64" s="1">
         <v>1.40625</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="1">
         <v>3.636363636363637</v>
       </c>
-      <c r="L64" t="s">
+      <c r="L64" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M64" t="s">
+      <c r="M64" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N64" t="s">
+      <c r="N64" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -46782,7 +46817,7 @@
       <c r="C65" t="s">
         <v>504</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65">
@@ -46794,22 +46829,22 @@
       <c r="G65">
         <v>0</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="1">
         <v>0</v>
       </c>
-      <c r="J65">
+      <c r="J65" s="1">
         <v>0</v>
       </c>
-      <c r="K65">
+      <c r="K65" s="1">
         <v>0</v>
       </c>
-      <c r="L65" t="s">
+      <c r="L65" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M65" t="s">
+      <c r="M65" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N65" t="s">
+      <c r="N65" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -46820,7 +46855,7 @@
       <c r="C66" t="s">
         <v>503</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="1">
         <v>10</v>
       </c>
       <c r="E66">
@@ -46832,22 +46867,22 @@
       <c r="G66">
         <v>0</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="1">
         <v>15</v>
       </c>
-      <c r="J66">
+      <c r="J66" s="1">
         <v>0</v>
       </c>
-      <c r="K66">
+      <c r="K66" s="1">
         <v>2.033898305084746</v>
       </c>
-      <c r="L66" t="s">
+      <c r="L66" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M66" t="s">
+      <c r="M66" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N66" t="s">
+      <c r="N66" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -46858,7 +46893,7 @@
       <c r="C67" t="s">
         <v>504</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="1">
         <v>20</v>
       </c>
       <c r="E67">
@@ -46870,22 +46905,22 @@
       <c r="G67">
         <v>0</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="1">
         <v>0</v>
       </c>
-      <c r="J67">
+      <c r="J67" s="1">
         <v>9.333333333333334</v>
       </c>
-      <c r="K67">
+      <c r="K67" s="1">
         <v>5.172413793103449</v>
       </c>
-      <c r="L67" t="s">
+      <c r="L67" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M67" t="s">
+      <c r="M67" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N67" t="s">
+      <c r="N67" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -46896,7 +46931,7 @@
       <c r="C68" t="s">
         <v>503</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="1">
         <v>15</v>
       </c>
       <c r="E68">
@@ -46908,22 +46943,22 @@
       <c r="G68">
         <v>0</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="1">
         <v>1.760869565217391</v>
       </c>
-      <c r="J68">
+      <c r="J68" s="1">
         <v>13.5</v>
       </c>
-      <c r="K68">
+      <c r="K68" s="1">
         <v>7.5</v>
       </c>
-      <c r="L68" t="s">
+      <c r="L68" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M68" t="s">
+      <c r="M68" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N68" t="s">
+      <c r="N68" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -46934,7 +46969,7 @@
       <c r="C69" t="s">
         <v>504</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="1">
         <v>40</v>
       </c>
       <c r="E69">
@@ -46946,22 +46981,22 @@
       <c r="G69">
         <v>0</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="3">
         <v>44.00000000000001</v>
       </c>
-      <c r="J69">
+      <c r="J69" s="1">
         <v>6.575342465753424</v>
       </c>
-      <c r="K69">
+      <c r="K69" s="1">
         <v>4.285714285714286</v>
       </c>
-      <c r="L69" t="s">
+      <c r="L69" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M69" t="s">
+      <c r="M69" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N69" t="s">
+      <c r="N69" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -46972,7 +47007,7 @@
       <c r="C70" t="s">
         <v>503</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70">
@@ -46984,22 +47019,22 @@
       <c r="G70">
         <v>0</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="1">
         <v>0</v>
       </c>
-      <c r="J70">
+      <c r="J70" s="1">
         <v>0</v>
       </c>
-      <c r="K70">
+      <c r="K70" s="1">
         <v>0</v>
       </c>
-      <c r="L70" t="s">
+      <c r="L70" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M70" t="s">
+      <c r="M70" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N70" t="s">
+      <c r="N70" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -47010,7 +47045,7 @@
       <c r="C71" t="s">
         <v>504</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="1">
         <v>5</v>
       </c>
       <c r="E71">
@@ -47022,22 +47057,22 @@
       <c r="G71">
         <v>0</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="1">
         <v>1.5</v>
       </c>
-      <c r="J71">
+      <c r="J71" s="1">
         <v>20.5</v>
       </c>
-      <c r="K71">
+      <c r="K71" s="1">
         <v>1</v>
       </c>
-      <c r="L71" t="s">
+      <c r="L71" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M71" t="s">
+      <c r="M71" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N71" t="s">
+      <c r="N71" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -47048,7 +47083,7 @@
       <c r="C72" t="s">
         <v>503</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="1">
         <v>35</v>
       </c>
       <c r="E72">
@@ -47060,22 +47095,22 @@
       <c r="G72">
         <v>0</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="1">
         <v>4.952830188679245</v>
       </c>
-      <c r="J72">
+      <c r="J72" s="1">
         <v>10.5</v>
       </c>
-      <c r="K72">
+      <c r="K72" s="1">
         <v>10.86206896551724</v>
       </c>
-      <c r="L72" t="s">
+      <c r="L72" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M72" t="s">
+      <c r="M72" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N72" t="s">
+      <c r="N72" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -47086,7 +47121,7 @@
       <c r="C73" t="s">
         <v>504</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="1">
         <v>30</v>
       </c>
       <c r="E73">
@@ -47098,22 +47133,22 @@
       <c r="G73">
         <v>0</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="1">
         <v>0</v>
       </c>
-      <c r="J73">
+      <c r="J73" s="4">
         <v>93</v>
       </c>
-      <c r="K73">
+      <c r="K73" s="1">
         <v>7.440944881889763</v>
       </c>
-      <c r="L73" t="s">
+      <c r="L73" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M73" t="s">
+      <c r="M73" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N73" t="s">
+      <c r="N73" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -47124,7 +47159,7 @@
       <c r="C74" t="s">
         <v>503</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="1">
         <v>30</v>
       </c>
       <c r="E74">
@@ -47136,22 +47171,22 @@
       <c r="G74">
         <v>0</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="1">
         <v>24</v>
       </c>
-      <c r="J74">
+      <c r="J74" s="1">
         <v>9.000000000000002</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="1">
         <v>4.835820895522388</v>
       </c>
-      <c r="L74" t="s">
+      <c r="L74" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M74" t="s">
+      <c r="M74" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N74" t="s">
+      <c r="N74" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -47162,7 +47197,7 @@
       <c r="C75" t="s">
         <v>504</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="3">
         <v>45</v>
       </c>
       <c r="E75">
@@ -47174,22 +47209,22 @@
       <c r="G75">
         <v>0</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="1">
         <v>3.970588235294117</v>
       </c>
-      <c r="J75">
+      <c r="J75" s="1">
         <v>18.5625</v>
       </c>
-      <c r="K75">
+      <c r="K75" s="1">
         <v>9.000000000000002</v>
       </c>
-      <c r="L75" t="s">
+      <c r="L75" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M75" t="s">
+      <c r="M75" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N75" t="s">
+      <c r="N75" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -47200,7 +47235,7 @@
       <c r="C76" t="s">
         <v>503</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="1">
         <v>30</v>
       </c>
       <c r="E76">
@@ -47212,22 +47247,22 @@
       <c r="G76">
         <v>0</v>
       </c>
-      <c r="I76">
+      <c r="I76" s="1">
         <v>14.53846153846154</v>
       </c>
-      <c r="J76">
+      <c r="J76" s="1">
         <v>24.75</v>
       </c>
-      <c r="K76">
+      <c r="K76" s="1">
         <v>5.232558139534882</v>
       </c>
-      <c r="L76" t="s">
+      <c r="L76" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M76" t="s">
+      <c r="M76" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N76" t="s">
+      <c r="N76" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -47238,7 +47273,7 @@
       <c r="C77" t="s">
         <v>504</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="1">
         <v>25</v>
       </c>
       <c r="E77">
@@ -47250,22 +47285,22 @@
       <c r="G77">
         <v>0</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="1">
         <v>7.734374999999999</v>
       </c>
-      <c r="J77">
+      <c r="J77" s="1">
         <v>6.048387096774193</v>
       </c>
-      <c r="K77">
+      <c r="K77" s="4">
         <v>85</v>
       </c>
-      <c r="L77" t="s">
+      <c r="L77" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M77" t="s">
+      <c r="M77" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N77" t="s">
+      <c r="N77" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -47276,7 +47311,7 @@
       <c r="C78" t="s">
         <v>503</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="3">
         <v>53.33333333333333</v>
       </c>
       <c r="E78">
@@ -47288,22 +47323,22 @@
       <c r="G78">
         <v>33.33333333333333</v>
       </c>
-      <c r="I78">
+      <c r="I78" s="3">
         <v>45.33333333333333</v>
       </c>
-      <c r="J78">
+      <c r="J78" s="4">
         <v>174</v>
       </c>
-      <c r="K78">
+      <c r="K78" s="1">
         <v>24</v>
       </c>
-      <c r="L78" t="s">
+      <c r="L78" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M78" t="s">
+      <c r="M78" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N78" t="s">
+      <c r="N78" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -47314,7 +47349,7 @@
       <c r="C79" t="s">
         <v>504</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="1">
         <v>40</v>
       </c>
       <c r="E79">
@@ -47326,22 +47361,22 @@
       <c r="G79">
         <v>0</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="4">
         <v>104</v>
       </c>
-      <c r="J79">
+      <c r="J79" s="1">
         <v>9.55263157894737</v>
       </c>
-      <c r="K79">
+      <c r="K79" s="1">
         <v>24</v>
       </c>
-      <c r="L79" t="s">
+      <c r="L79" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M79" t="s">
+      <c r="M79" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N79" t="s">
+      <c r="N79" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -47352,7 +47387,7 @@
       <c r="C80" t="s">
         <v>503</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="1">
         <v>20</v>
       </c>
       <c r="E80">
@@ -47364,22 +47399,22 @@
       <c r="G80">
         <v>0</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="1">
         <v>18</v>
       </c>
-      <c r="J80">
+      <c r="J80" s="1">
         <v>1.451612903225807</v>
       </c>
-      <c r="K80">
+      <c r="K80" s="1">
         <v>6.164383561643836</v>
       </c>
-      <c r="L80" t="s">
+      <c r="L80" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M80" t="s">
+      <c r="M80" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N80" t="s">
+      <c r="N80" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -47390,7 +47425,7 @@
       <c r="C81" t="s">
         <v>504</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="3">
         <v>70</v>
       </c>
       <c r="E81">
@@ -47402,22 +47437,22 @@
       <c r="G81">
         <v>0</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="4">
         <v>261.4</v>
       </c>
-      <c r="J81">
+      <c r="J81" s="1">
         <v>0</v>
       </c>
-      <c r="K81">
+      <c r="K81" s="3">
         <v>55.99999999999999</v>
       </c>
-      <c r="L81" t="s">
+      <c r="L81" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M81" t="s">
+      <c r="M81" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N81" t="s">
+      <c r="N81" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -47428,7 +47463,7 @@
       <c r="C82" t="s">
         <v>503</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="1">
         <v>10</v>
       </c>
       <c r="E82">
@@ -47440,22 +47475,22 @@
       <c r="G82">
         <v>0</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="1">
         <v>1.363636363636364</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="1">
         <v>7.777777777777778</v>
       </c>
-      <c r="K82">
+      <c r="K82" s="1">
         <v>15.55555555555556</v>
       </c>
-      <c r="L82" t="s">
+      <c r="L82" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M82" t="s">
+      <c r="M82" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N82" t="s">
+      <c r="N82" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -47466,7 +47501,7 @@
       <c r="C83" t="s">
         <v>504</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="1">
         <v>5</v>
       </c>
       <c r="E83">
@@ -47478,22 +47513,22 @@
       <c r="G83">
         <v>0</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="1">
         <v>0</v>
       </c>
-      <c r="J83">
+      <c r="J83" s="1">
         <v>0</v>
       </c>
-      <c r="K83">
+      <c r="K83" s="1">
         <v>3.409090909090909</v>
       </c>
-      <c r="L83" t="s">
+      <c r="L83" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M83" t="s">
+      <c r="M83" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N83" t="s">
+      <c r="N83" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -47504,7 +47539,7 @@
       <c r="C84" t="s">
         <v>503</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="3">
         <v>61.66666666666666</v>
       </c>
       <c r="E84">
@@ -47516,22 +47551,22 @@
       <c r="G84">
         <v>33.33333333333333</v>
       </c>
-      <c r="I84">
+      <c r="I84" s="1">
         <v>14.13690476190476</v>
       </c>
-      <c r="J84">
+      <c r="J84" s="1">
         <v>36.33333333333334</v>
       </c>
-      <c r="K84">
+      <c r="K84" s="1">
         <v>4.0748031496063</v>
       </c>
-      <c r="L84" t="s">
+      <c r="L84" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M84" t="s">
+      <c r="M84" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="N84" t="s">
+      <c r="N84" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -47542,7 +47577,7 @@
       <c r="C85" t="s">
         <v>504</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="3">
         <v>45.00000000000001</v>
       </c>
       <c r="E85">
@@ -47554,22 +47589,22 @@
       <c r="G85">
         <v>0</v>
       </c>
-      <c r="I85">
+      <c r="I85" s="1">
         <v>7.500000000000001</v>
       </c>
-      <c r="J85">
+      <c r="J85" s="1">
         <v>0</v>
       </c>
-      <c r="K85">
+      <c r="K85" s="1">
         <v>8.25</v>
       </c>
-      <c r="L85" t="s">
+      <c r="L85" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M85" t="s">
+      <c r="M85" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N85" t="s">
+      <c r="N85" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -47580,7 +47615,7 @@
       <c r="C86" t="s">
         <v>503</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="3">
         <v>45</v>
       </c>
       <c r="E86">
@@ -47592,22 +47627,22 @@
       <c r="G86">
         <v>0</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="1">
         <v>7.408536585365855</v>
       </c>
-      <c r="J86">
+      <c r="J86" s="1">
         <v>4.5</v>
       </c>
-      <c r="K86">
+      <c r="K86" s="1">
         <v>25.31249999999999</v>
       </c>
-      <c r="L86" t="s">
+      <c r="L86" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M86" t="s">
+      <c r="M86" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N86" t="s">
+      <c r="N86" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -47618,7 +47653,7 @@
       <c r="C87" t="s">
         <v>504</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="3">
         <v>65</v>
       </c>
       <c r="E87">
@@ -47630,22 +47665,22 @@
       <c r="G87">
         <v>0</v>
       </c>
-      <c r="I87">
+      <c r="I87" s="1">
         <v>19.89795918367347</v>
       </c>
-      <c r="J87">
+      <c r="J87" s="1">
         <v>2.867647058823529</v>
       </c>
-      <c r="K87">
+      <c r="K87" s="1">
         <v>32.49999999999999</v>
       </c>
-      <c r="L87" t="s">
+      <c r="L87" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M87" t="s">
+      <c r="M87" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N87" t="s">
+      <c r="N87" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -47656,7 +47691,7 @@
       <c r="C88" t="s">
         <v>503</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="3">
         <v>45</v>
       </c>
       <c r="E88">
@@ -47668,22 +47703,22 @@
       <c r="G88">
         <v>0</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="1">
         <v>9.310344827586208</v>
       </c>
-      <c r="J88">
+      <c r="J88" s="1">
         <v>13.80681818181818</v>
       </c>
-      <c r="K88">
+      <c r="K88" s="1">
         <v>24.54545454545455</v>
       </c>
-      <c r="L88" t="s">
+      <c r="L88" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M88" t="s">
+      <c r="M88" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N88" t="s">
+      <c r="N88" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -47694,7 +47729,7 @@
       <c r="C89" t="s">
         <v>504</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="1">
         <v>5</v>
       </c>
       <c r="E89">
@@ -47706,22 +47741,22 @@
       <c r="G89">
         <v>0</v>
       </c>
-      <c r="I89">
+      <c r="I89" s="1">
         <v>2</v>
       </c>
-      <c r="J89">
+      <c r="J89" s="1">
         <v>32.5</v>
       </c>
-      <c r="K89">
+      <c r="K89" s="1">
         <v>0</v>
       </c>
-      <c r="L89" t="s">
+      <c r="L89" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M89" t="s">
+      <c r="M89" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N89" t="s">
+      <c r="N89" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -47732,7 +47767,7 @@
       <c r="C90" t="s">
         <v>503</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="1">
         <v>40</v>
       </c>
       <c r="E90">
@@ -47744,22 +47779,22 @@
       <c r="G90">
         <v>0</v>
       </c>
-      <c r="I90">
+      <c r="I90" s="1">
         <v>21.95121951219512</v>
       </c>
-      <c r="J90">
+      <c r="J90" s="1">
         <v>8.000000000000002</v>
       </c>
-      <c r="K90">
+      <c r="K90" s="1">
         <v>40</v>
       </c>
-      <c r="L90" t="s">
+      <c r="L90" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M90" t="s">
+      <c r="M90" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N90" t="s">
+      <c r="N90" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -47770,7 +47805,7 @@
       <c r="C91" t="s">
         <v>504</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="4">
         <v>73.33333333333333</v>
       </c>
       <c r="E91">
@@ -47782,22 +47817,22 @@
       <c r="G91">
         <v>33.33333333333333</v>
       </c>
-      <c r="I91">
+      <c r="I91" s="1">
         <v>14.08695652173913</v>
       </c>
-      <c r="J91">
+      <c r="J91" s="1">
         <v>3.39622641509434</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="3">
         <v>41.33333333333334</v>
       </c>
-      <c r="L91" t="s">
+      <c r="L91" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M91" t="s">
+      <c r="M91" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N91" t="s">
+      <c r="N91" s="5" t="s">
         <v>35</v>
       </c>
     </row>
@@ -47808,7 +47843,7 @@
       <c r="C92" t="s">
         <v>503</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="3">
         <v>68.33333333333333</v>
       </c>
       <c r="E92">
@@ -47820,22 +47855,22 @@
       <c r="G92">
         <v>33.33333333333333</v>
       </c>
-      <c r="I92">
+      <c r="I92" s="4">
         <v>141.8333333333333</v>
       </c>
-      <c r="J92">
+      <c r="J92" s="1">
         <v>10.67796610169492</v>
       </c>
-      <c r="K92">
+      <c r="K92" s="1">
         <v>6.176470588235295</v>
       </c>
-      <c r="L92" t="s">
+      <c r="L92" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M92" t="s">
+      <c r="M92" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N92" t="s">
+      <c r="N92" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -47846,7 +47881,7 @@
       <c r="C93" t="s">
         <v>504</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="1">
         <v>10</v>
       </c>
       <c r="E93">
@@ -47858,22 +47893,22 @@
       <c r="G93">
         <v>0</v>
       </c>
-      <c r="I93">
+      <c r="I93" s="1">
         <v>1.343283582089552</v>
       </c>
-      <c r="J93">
+      <c r="J93" s="1">
         <v>26</v>
       </c>
-      <c r="K93">
+      <c r="K93" s="1">
         <v>9</v>
       </c>
-      <c r="L93" t="s">
+      <c r="L93" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M93" t="s">
+      <c r="M93" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N93" t="s">
+      <c r="N93" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -47884,7 +47919,7 @@
       <c r="C94" t="s">
         <v>503</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="1">
         <v>20</v>
       </c>
       <c r="E94">
@@ -47896,22 +47931,22 @@
       <c r="G94">
         <v>0</v>
       </c>
-      <c r="I94">
+      <c r="I94" s="1">
         <v>36</v>
       </c>
-      <c r="J94">
+      <c r="J94" s="1">
         <v>4.285714285714286</v>
       </c>
-      <c r="K94">
+      <c r="K94" s="1">
         <v>28</v>
       </c>
-      <c r="L94" t="s">
+      <c r="L94" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M94" t="s">
+      <c r="M94" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N94" t="s">
+      <c r="N94" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -47922,7 +47957,7 @@
       <c r="C95" t="s">
         <v>504</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="1">
         <v>20</v>
       </c>
       <c r="E95">
@@ -47934,22 +47969,22 @@
       <c r="G95">
         <v>0</v>
       </c>
-      <c r="I95">
+      <c r="I95" s="1">
         <v>6</v>
       </c>
-      <c r="J95">
+      <c r="J95" s="3">
         <v>44.00000000000001</v>
       </c>
-      <c r="K95">
+      <c r="K95" s="1">
         <v>15.55555555555556</v>
       </c>
-      <c r="L95" t="s">
+      <c r="L95" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M95" t="s">
+      <c r="M95" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N95" t="s">
+      <c r="N95" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -47960,7 +47995,7 @@
       <c r="C96" t="s">
         <v>503</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="1">
         <v>20</v>
       </c>
       <c r="E96">
@@ -47972,22 +48007,22 @@
       <c r="G96">
         <v>0</v>
       </c>
-      <c r="I96">
+      <c r="I96" s="1">
         <v>4.883720930232557</v>
       </c>
-      <c r="J96">
+      <c r="J96" s="1">
         <v>0</v>
       </c>
-      <c r="K96">
+      <c r="K96" s="1">
         <v>0</v>
       </c>
-      <c r="L96" t="s">
+      <c r="L96" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M96" t="s">
+      <c r="M96" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N96" t="s">
+      <c r="N96" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -47998,7 +48033,7 @@
       <c r="C97" t="s">
         <v>504</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="1">
         <v>15</v>
       </c>
       <c r="E97">
@@ -48010,22 +48045,22 @@
       <c r="G97">
         <v>0</v>
       </c>
-      <c r="I97">
+      <c r="I97" s="1">
         <v>0</v>
       </c>
-      <c r="J97">
+      <c r="J97" s="1">
         <v>9.000000000000002</v>
       </c>
-      <c r="K97">
+      <c r="K97" s="1">
         <v>7.500000000000001</v>
       </c>
-      <c r="L97" t="s">
+      <c r="L97" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M97" t="s">
+      <c r="M97" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N97" t="s">
+      <c r="N97" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -48036,7 +48071,7 @@
       <c r="C98" t="s">
         <v>503</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="4">
         <v>76.66666666666666</v>
       </c>
       <c r="E98">
@@ -48048,22 +48083,22 @@
       <c r="G98">
         <v>66.66666666666666</v>
       </c>
-      <c r="I98">
+      <c r="I98" s="3">
         <v>48.88888888888889</v>
       </c>
-      <c r="J98">
+      <c r="J98" s="1">
         <v>37.45833333333334</v>
       </c>
-      <c r="K98">
+      <c r="K98" s="1">
         <v>11</v>
       </c>
-      <c r="L98" t="s">
+      <c r="L98" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M98" t="s">
+      <c r="M98" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="N98" t="s">
+      <c r="N98" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -48074,7 +48109,7 @@
       <c r="C99" t="s">
         <v>504</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="1">
         <v>40</v>
       </c>
       <c r="E99">
@@ -48086,22 +48121,22 @@
       <c r="G99">
         <v>0</v>
       </c>
-      <c r="I99">
+      <c r="I99" s="1">
         <v>6</v>
       </c>
-      <c r="J99">
+      <c r="J99" s="1">
         <v>6.206896551724139</v>
       </c>
-      <c r="K99">
+      <c r="K99" s="1">
         <v>6.774193548387098</v>
       </c>
-      <c r="L99" t="s">
+      <c r="L99" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M99" t="s">
+      <c r="M99" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N99" t="s">
+      <c r="N99" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -48112,7 +48147,7 @@
       <c r="C100" t="s">
         <v>503</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="3">
         <v>45</v>
       </c>
       <c r="E100">
@@ -48124,22 +48159,22 @@
       <c r="G100">
         <v>0</v>
       </c>
-      <c r="I100">
+      <c r="I100" s="1">
         <v>36.00000000000001</v>
       </c>
-      <c r="J100">
+      <c r="J100" s="1">
         <v>6.838815789473686</v>
       </c>
-      <c r="K100">
+      <c r="K100" s="1">
         <v>12.65625</v>
       </c>
-      <c r="L100" t="s">
+      <c r="L100" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M100" t="s">
+      <c r="M100" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N100" t="s">
+      <c r="N100" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -48150,7 +48185,7 @@
       <c r="C101" t="s">
         <v>504</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="1">
         <v>10</v>
       </c>
       <c r="E101">
@@ -48162,22 +48197,22 @@
       <c r="G101">
         <v>0</v>
       </c>
-      <c r="I101">
+      <c r="I101" s="1">
         <v>24.54545454545455</v>
       </c>
-      <c r="J101">
+      <c r="J101" s="1">
         <v>4.000000000000001</v>
       </c>
-      <c r="K101">
+      <c r="K101" s="1">
         <v>0</v>
       </c>
-      <c r="L101" t="s">
+      <c r="L101" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M101" t="s">
+      <c r="M101" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N101" t="s">
+      <c r="N101" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -48188,7 +48223,7 @@
       <c r="C102" t="s">
         <v>503</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="1">
         <v>15</v>
       </c>
       <c r="E102">
@@ -48200,22 +48235,22 @@
       <c r="G102">
         <v>0</v>
       </c>
-      <c r="I102">
+      <c r="I102" s="1">
         <v>3</v>
       </c>
-      <c r="J102">
+      <c r="J102" s="1">
         <v>0</v>
       </c>
-      <c r="K102">
+      <c r="K102" s="1">
         <v>33.00000000000001</v>
       </c>
-      <c r="L102" t="s">
+      <c r="L102" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M102" t="s">
+      <c r="M102" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N102" t="s">
+      <c r="N102" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -48226,7 +48261,7 @@
       <c r="C103" t="s">
         <v>504</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="1">
         <v>38.33333333333334</v>
       </c>
       <c r="E103">
@@ -48238,22 +48273,22 @@
       <c r="G103">
         <v>0</v>
       </c>
-      <c r="I103">
+      <c r="I103" s="1">
         <v>22.5</v>
       </c>
-      <c r="J103">
+      <c r="J103" s="1">
         <v>2.884615384615385</v>
       </c>
-      <c r="K103">
+      <c r="K103" s="1">
         <v>17.95662100456621</v>
       </c>
-      <c r="L103" t="s">
+      <c r="L103" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M103" t="s">
+      <c r="M103" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N103" t="s">
+      <c r="N103" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -48264,7 +48299,7 @@
       <c r="C104" t="s">
         <v>503</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="3">
         <v>55</v>
       </c>
       <c r="E104">
@@ -48276,22 +48311,22 @@
       <c r="G104">
         <v>0</v>
       </c>
-      <c r="I104">
+      <c r="I104" s="1">
         <v>11.63385826771654</v>
       </c>
-      <c r="J104">
+      <c r="J104" s="1">
         <v>24.09801136363636</v>
       </c>
-      <c r="K104">
+      <c r="K104" s="3">
         <v>48.5</v>
       </c>
-      <c r="L104" t="s">
+      <c r="L104" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M104" t="s">
+      <c r="M104" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N104" t="s">
+      <c r="N104" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -48302,7 +48337,7 @@
       <c r="C105" t="s">
         <v>504</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="3">
         <v>44.99999999999999</v>
       </c>
       <c r="E105">
@@ -48314,22 +48349,22 @@
       <c r="G105">
         <v>0</v>
       </c>
-      <c r="I105">
+      <c r="I105" s="1">
         <v>22.5</v>
       </c>
-      <c r="J105">
+      <c r="J105" s="1">
         <v>11.25</v>
       </c>
-      <c r="K105">
+      <c r="K105" s="1">
         <v>13.80681818181818</v>
       </c>
-      <c r="L105" t="s">
+      <c r="L105" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M105" t="s">
+      <c r="M105" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N105" t="s">
+      <c r="N105" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -48340,7 +48375,7 @@
       <c r="C106" t="s">
         <v>503</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="1">
         <v>10</v>
       </c>
       <c r="E106">
@@ -48352,22 +48387,22 @@
       <c r="G106">
         <v>0</v>
       </c>
-      <c r="I106">
+      <c r="I106" s="1">
         <v>2.538461538461538</v>
       </c>
-      <c r="J106">
+      <c r="J106" s="1">
         <v>1.071428571428572</v>
       </c>
-      <c r="K106">
+      <c r="K106" s="1">
         <v>15</v>
       </c>
-      <c r="L106" t="s">
+      <c r="L106" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M106" t="s">
+      <c r="M106" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N106" t="s">
+      <c r="N106" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -48378,7 +48413,7 @@
       <c r="C107" t="s">
         <v>504</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="1">
         <v>10</v>
       </c>
       <c r="E107">
@@ -48390,22 +48425,22 @@
       <c r="G107">
         <v>0</v>
       </c>
-      <c r="I107">
+      <c r="I107" s="1">
         <v>0.9183673469387754</v>
       </c>
-      <c r="J107">
+      <c r="J107" s="1">
         <v>12</v>
       </c>
-      <c r="K107">
+      <c r="K107" s="1">
         <v>3.461538461538461</v>
       </c>
-      <c r="L107" t="s">
+      <c r="L107" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M107" t="s">
+      <c r="M107" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N107" t="s">
+      <c r="N107" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -48416,7 +48451,7 @@
       <c r="C108" t="s">
         <v>503</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="4">
         <v>108.3333333333333</v>
       </c>
       <c r="E108">
@@ -48428,22 +48463,22 @@
       <c r="G108">
         <v>33.33333333333333</v>
       </c>
-      <c r="I108">
+      <c r="I108" s="3">
         <v>44.22043010752687</v>
       </c>
-      <c r="J108">
+      <c r="J108" s="1">
         <v>24.17910447761194</v>
       </c>
-      <c r="K108">
+      <c r="K108" s="1">
         <v>15</v>
       </c>
-      <c r="L108" t="s">
+      <c r="L108" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M108" t="s">
+      <c r="M108" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N108" t="s">
+      <c r="N108" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -48454,7 +48489,7 @@
       <c r="C109" t="s">
         <v>504</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="1">
         <v>15</v>
       </c>
       <c r="E109">
@@ -48466,22 +48501,22 @@
       <c r="G109">
         <v>0</v>
       </c>
-      <c r="I109">
+      <c r="I109" s="1">
         <v>27</v>
       </c>
-      <c r="J109">
+      <c r="J109" s="1">
         <v>1.205357142857143</v>
       </c>
-      <c r="K109">
+      <c r="K109" s="3">
         <v>61.5</v>
       </c>
-      <c r="L109" t="s">
+      <c r="L109" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M109" t="s">
+      <c r="M109" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N109" t="s">
+      <c r="N109" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -48492,7 +48527,7 @@
       <c r="C110" t="s">
         <v>503</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="4">
         <v>333.3333333333333</v>
       </c>
       <c r="E110">
@@ -48504,22 +48539,22 @@
       <c r="G110">
         <v>33.33333333333333</v>
       </c>
-      <c r="I110">
+      <c r="I110" s="4">
         <v>372.4137931034482</v>
       </c>
-      <c r="J110">
+      <c r="J110" s="4">
         <v>442.4561403508771</v>
       </c>
-      <c r="K110">
+      <c r="K110" s="4">
         <v>318</v>
       </c>
-      <c r="L110" t="s">
+      <c r="L110" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M110" t="s">
+      <c r="M110" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="N110" t="s">
+      <c r="N110" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -48530,7 +48565,7 @@
       <c r="C111" t="s">
         <v>504</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="3">
         <v>70</v>
       </c>
       <c r="E111">
@@ -48542,22 +48577,22 @@
       <c r="G111">
         <v>0</v>
       </c>
-      <c r="I111">
+      <c r="I111" s="1">
         <v>21</v>
       </c>
-      <c r="J111">
+      <c r="J111" s="1">
         <v>17.83018867924528</v>
       </c>
-      <c r="K111">
+      <c r="K111" s="4">
         <v>238</v>
       </c>
-      <c r="L111" t="s">
+      <c r="L111" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M111" t="s">
+      <c r="M111" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N111" t="s">
+      <c r="N111" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -48568,7 +48603,7 @@
       <c r="C112" t="s">
         <v>503</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="3">
         <v>50</v>
       </c>
       <c r="E112">
@@ -48580,22 +48615,22 @@
       <c r="G112">
         <v>0</v>
       </c>
-      <c r="I112">
+      <c r="I112" s="1">
         <v>36.29032258064516</v>
       </c>
-      <c r="J112">
+      <c r="J112" s="1">
         <v>11.89024390243902</v>
       </c>
-      <c r="K112">
+      <c r="K112" s="4">
         <v>110</v>
       </c>
-      <c r="L112" t="s">
+      <c r="L112" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M112" t="s">
+      <c r="M112" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N112" t="s">
+      <c r="N112" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -48606,7 +48641,7 @@
       <c r="C113" t="s">
         <v>504</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="1">
         <v>38.33333333333334</v>
       </c>
       <c r="E113">
@@ -48618,22 +48653,22 @@
       <c r="G113">
         <v>0</v>
       </c>
-      <c r="I113">
+      <c r="I113" s="1">
         <v>22.5</v>
       </c>
-      <c r="J113">
+      <c r="J113" s="1">
         <v>3.409090909090909</v>
       </c>
-      <c r="K113">
+      <c r="K113" s="4">
         <v>160.8333333333333</v>
       </c>
-      <c r="L113" t="s">
+      <c r="L113" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M113" t="s">
+      <c r="M113" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N113" t="s">
+      <c r="N113" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -48644,7 +48679,7 @@
       <c r="C114" t="s">
         <v>503</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="3">
         <v>45.00000000000001</v>
       </c>
       <c r="E114">
@@ -48656,22 +48691,22 @@
       <c r="G114">
         <v>0</v>
       </c>
-      <c r="I114">
+      <c r="I114" s="1">
         <v>13.67763157894737</v>
       </c>
-      <c r="J114">
+      <c r="J114" s="4">
         <v>110.4545454545455</v>
       </c>
-      <c r="K114">
+      <c r="K114" s="1">
         <v>11.25</v>
       </c>
-      <c r="L114" t="s">
+      <c r="L114" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M114" t="s">
+      <c r="M114" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N114" t="s">
+      <c r="N114" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -48682,7 +48717,7 @@
       <c r="C115" t="s">
         <v>504</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="1">
         <v>40</v>
       </c>
       <c r="E115">
@@ -48694,22 +48729,22 @@
       <c r="G115">
         <v>0</v>
       </c>
-      <c r="I115">
+      <c r="I115" s="1">
         <v>2.465753424657534</v>
       </c>
-      <c r="J115">
+      <c r="J115" s="1">
         <v>6.97674418604651</v>
       </c>
-      <c r="K115">
+      <c r="K115" s="1">
         <v>8.18181818181818</v>
       </c>
-      <c r="L115" t="s">
+      <c r="L115" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M115" t="s">
+      <c r="M115" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N115" t="s">
+      <c r="N115" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -48720,7 +48755,7 @@
       <c r="C116" t="s">
         <v>503</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="1">
         <v>15</v>
       </c>
       <c r="E116">
@@ -48732,22 +48767,22 @@
       <c r="G116">
         <v>0</v>
       </c>
-      <c r="I116">
+      <c r="I116" s="1">
         <v>11.66666666666667</v>
       </c>
-      <c r="J116">
+      <c r="J116" s="1">
         <v>0</v>
       </c>
-      <c r="K116">
+      <c r="K116" s="1">
         <v>11.6015625</v>
       </c>
-      <c r="L116" t="s">
+      <c r="L116" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M116" t="s">
+      <c r="M116" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N116" t="s">
+      <c r="N116" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -48758,7 +48793,7 @@
       <c r="C117" t="s">
         <v>504</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="1">
         <v>15</v>
       </c>
       <c r="E117">
@@ -48770,22 +48805,22 @@
       <c r="G117">
         <v>0</v>
       </c>
-      <c r="I117">
+      <c r="I117" s="1">
         <v>13.5</v>
       </c>
-      <c r="J117">
+      <c r="J117" s="1">
         <v>0</v>
       </c>
-      <c r="K117">
+      <c r="K117" s="1">
         <v>5.785714285714286</v>
       </c>
-      <c r="L117" t="s">
+      <c r="L117" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M117" t="s">
+      <c r="M117" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N117" t="s">
+      <c r="N117" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -48796,7 +48831,7 @@
       <c r="C118" t="s">
         <v>503</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="1">
         <v>38.33333333333333</v>
       </c>
       <c r="E118">
@@ -48808,22 +48843,22 @@
       <c r="G118">
         <v>33.33333333333333</v>
       </c>
-      <c r="I118">
+      <c r="I118" s="1">
         <v>14</v>
       </c>
-      <c r="J118">
+      <c r="J118" s="1">
         <v>34.33333333333334</v>
       </c>
-      <c r="K118">
+      <c r="K118" s="3">
         <v>62</v>
       </c>
-      <c r="L118" t="s">
+      <c r="L118" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M118" t="s">
+      <c r="M118" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="N118" t="s">
+      <c r="N118" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -48834,7 +48869,7 @@
       <c r="C119" t="s">
         <v>504</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="1">
         <v>35</v>
       </c>
       <c r="E119">
@@ -48846,22 +48881,22 @@
       <c r="G119">
         <v>0</v>
       </c>
-      <c r="I119">
+      <c r="I119" s="1">
         <v>3.75</v>
       </c>
-      <c r="J119">
+      <c r="J119" s="1">
         <v>15.25</v>
       </c>
-      <c r="K119">
+      <c r="K119" s="1">
         <v>2.5</v>
       </c>
-      <c r="L119" t="s">
+      <c r="L119" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M119" t="s">
+      <c r="M119" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N119" t="s">
+      <c r="N119" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -48872,7 +48907,7 @@
       <c r="C120" t="s">
         <v>503</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="1">
         <v>38.33333333333333</v>
       </c>
       <c r="E120">
@@ -48884,22 +48919,22 @@
       <c r="G120">
         <v>33.33333333333333</v>
       </c>
-      <c r="I120">
+      <c r="I120" s="1">
         <v>36.96969696969697</v>
       </c>
-      <c r="J120">
+      <c r="J120" s="1">
         <v>0.6716417910447761</v>
       </c>
-      <c r="K120">
+      <c r="K120" s="1">
         <v>9</v>
       </c>
-      <c r="L120" t="s">
+      <c r="L120" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M120" t="s">
+      <c r="M120" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N120" t="s">
+      <c r="N120" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -48910,7 +48945,7 @@
       <c r="C121" t="s">
         <v>504</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="1">
         <v>15</v>
       </c>
       <c r="E121">
@@ -48922,22 +48957,22 @@
       <c r="G121">
         <v>0</v>
       </c>
-      <c r="I121">
+      <c r="I121" s="1">
         <v>1.594488188976378</v>
       </c>
-      <c r="J121">
+      <c r="J121" s="1">
         <v>3</v>
       </c>
-      <c r="K121">
+      <c r="K121" s="1">
         <v>9.000000000000002</v>
       </c>
-      <c r="L121" t="s">
+      <c r="L121" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M121" t="s">
+      <c r="M121" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N121" t="s">
+      <c r="N121" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -48948,7 +48983,7 @@
       <c r="C122" t="s">
         <v>503</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="3">
         <v>50</v>
       </c>
       <c r="E122">
@@ -48960,22 +48995,22 @@
       <c r="G122">
         <v>0</v>
       </c>
-      <c r="I122">
+      <c r="I122" s="1">
         <v>8.088235294117647</v>
       </c>
-      <c r="J122">
+      <c r="J122" s="1">
         <v>7.075471698113208</v>
       </c>
-      <c r="K122">
+      <c r="K122" s="3">
         <v>60</v>
       </c>
-      <c r="L122" t="s">
+      <c r="L122" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M122" t="s">
+      <c r="M122" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N122" t="s">
+      <c r="N122" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -48986,7 +49021,7 @@
       <c r="C123" t="s">
         <v>504</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="1">
         <v>35</v>
       </c>
       <c r="E123">
@@ -48998,22 +49033,22 @@
       <c r="G123">
         <v>0</v>
       </c>
-      <c r="I123">
+      <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123">
+      <c r="J123" s="1">
         <v>15</v>
       </c>
-      <c r="K123">
+      <c r="K123" s="1">
         <v>5.431034482758621</v>
       </c>
-      <c r="L123" t="s">
+      <c r="L123" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M123" t="s">
+      <c r="M123" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N123" t="s">
+      <c r="N123" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -49024,7 +49059,7 @@
       <c r="C124" t="s">
         <v>503</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="1">
         <v>30</v>
       </c>
       <c r="E124">
@@ -49036,22 +49071,22 @@
       <c r="G124">
         <v>0</v>
       </c>
-      <c r="I124">
+      <c r="I124" s="1">
         <v>2.903225806451613</v>
       </c>
-      <c r="J124">
+      <c r="J124" s="1">
         <v>19.28571428571429</v>
       </c>
-      <c r="K124">
+      <c r="K124" s="1">
         <v>13.84615384615385</v>
       </c>
-      <c r="L124" t="s">
+      <c r="L124" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M124" t="s">
+      <c r="M124" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N124" t="s">
+      <c r="N124" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -49062,7 +49097,7 @@
       <c r="C125" t="s">
         <v>504</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="4">
         <v>85</v>
       </c>
       <c r="E125">
@@ -49074,22 +49109,22 @@
       <c r="G125">
         <v>0</v>
       </c>
-      <c r="I125">
+      <c r="I125" s="1">
         <v>39.07317073170732</v>
       </c>
-      <c r="J125">
+      <c r="J125" s="1">
         <v>30</v>
       </c>
-      <c r="K125">
+      <c r="K125" s="1">
         <v>11.06707317073171</v>
       </c>
-      <c r="L125" t="s">
+      <c r="L125" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M125" t="s">
+      <c r="M125" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N125" t="s">
+      <c r="N125" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -49100,7 +49135,7 @@
       <c r="C126" t="s">
         <v>503</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="1">
         <v>15</v>
       </c>
       <c r="E126">
@@ -49112,22 +49147,22 @@
       <c r="G126">
         <v>0</v>
       </c>
-      <c r="I126">
+      <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126">
+      <c r="J126" s="1">
         <v>4.500000000000001</v>
       </c>
-      <c r="K126">
+      <c r="K126" s="1">
         <v>7.923913043478262</v>
       </c>
-      <c r="L126" t="s">
+      <c r="L126" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M126" t="s">
+      <c r="M126" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N126" t="s">
+      <c r="N126" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -49138,7 +49173,7 @@
       <c r="C127" t="s">
         <v>504</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="1">
         <v>25</v>
       </c>
       <c r="E127">
@@ -49150,22 +49185,22 @@
       <c r="G127">
         <v>0</v>
       </c>
-      <c r="I127">
+      <c r="I127" s="4">
         <v>110</v>
       </c>
-      <c r="J127">
+      <c r="J127" s="1">
         <v>1.271186440677966</v>
       </c>
-      <c r="K127">
+      <c r="K127" s="1">
         <v>3.409090909090909</v>
       </c>
-      <c r="L127" t="s">
+      <c r="L127" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M127" t="s">
+      <c r="M127" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N127" t="s">
+      <c r="N127" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -49176,7 +49211,7 @@
       <c r="C128" t="s">
         <v>503</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="3">
         <v>58.33333333333333</v>
       </c>
       <c r="E128">
@@ -49188,22 +49223,22 @@
       <c r="G128">
         <v>33.33333333333333</v>
       </c>
-      <c r="I128">
+      <c r="I128" s="1">
         <v>2.5</v>
       </c>
-      <c r="J128">
+      <c r="J128" s="1">
         <v>4.687499999999999</v>
       </c>
-      <c r="K128">
+      <c r="K128" s="1">
         <v>33.33333333333333</v>
       </c>
-      <c r="L128" t="s">
+      <c r="L128" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M128" t="s">
+      <c r="M128" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N128" t="s">
+      <c r="N128" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -49214,7 +49249,7 @@
       <c r="C129" t="s">
         <v>504</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="1">
         <v>20</v>
       </c>
       <c r="E129">
@@ -49226,22 +49261,22 @@
       <c r="G129">
         <v>0</v>
       </c>
-      <c r="I129">
+      <c r="I129" s="1">
         <v>4.000000000000001</v>
       </c>
-      <c r="J129">
+      <c r="J129" s="1">
         <v>2.307692307692308</v>
       </c>
-      <c r="K129">
+      <c r="K129" s="1">
         <v>2.769230769230769</v>
       </c>
-      <c r="L129" t="s">
+      <c r="L129" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M129" t="s">
+      <c r="M129" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N129" t="s">
+      <c r="N129" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -49252,7 +49287,7 @@
       <c r="C130" t="s">
         <v>503</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="1">
         <v>15</v>
       </c>
       <c r="E130">
@@ -49264,22 +49299,22 @@
       <c r="G130">
         <v>0</v>
       </c>
-      <c r="I130">
+      <c r="I130" s="1">
         <v>33.00000000000001</v>
       </c>
-      <c r="J130">
+      <c r="J130" s="3">
         <v>46.50000000000001</v>
       </c>
-      <c r="K130">
+      <c r="K130" s="1">
         <v>0.9183673469387756</v>
       </c>
-      <c r="L130" t="s">
+      <c r="L130" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M130" t="s">
+      <c r="M130" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N130" t="s">
+      <c r="N130" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -49290,7 +49325,7 @@
       <c r="C131" t="s">
         <v>504</v>
       </c>
-      <c r="D131">
+      <c r="D131" s="1">
         <v>35</v>
       </c>
       <c r="E131">
@@ -49302,22 +49337,22 @@
       <c r="G131">
         <v>0</v>
       </c>
-      <c r="I131">
+      <c r="I131" s="1">
         <v>23.33333333333334</v>
       </c>
-      <c r="J131">
+      <c r="J131" s="4">
         <v>119</v>
       </c>
-      <c r="K131">
+      <c r="K131" s="1">
         <v>1.810344827586207</v>
       </c>
-      <c r="L131" t="s">
+      <c r="L131" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M131" t="s">
+      <c r="M131" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N131" t="s">
+      <c r="N131" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -49328,7 +49363,7 @@
       <c r="C132" t="s">
         <v>503</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="1">
         <v>30</v>
       </c>
       <c r="E132">
@@ -49340,22 +49375,22 @@
       <c r="G132">
         <v>0</v>
       </c>
-      <c r="I132">
+      <c r="I132" s="1">
         <v>27</v>
       </c>
-      <c r="J132">
+      <c r="J132" s="1">
         <v>10</v>
       </c>
-      <c r="K132">
+      <c r="K132" s="1">
         <v>5.861842105263158</v>
       </c>
-      <c r="L132" t="s">
+      <c r="L132" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M132" t="s">
+      <c r="M132" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N132" t="s">
+      <c r="N132" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -49366,7 +49401,7 @@
       <c r="C133" t="s">
         <v>504</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="1">
         <v>33.33333333333334</v>
       </c>
       <c r="E133">
@@ -49378,22 +49413,22 @@
       <c r="G133">
         <v>0</v>
       </c>
-      <c r="I133">
+      <c r="I133" s="1">
         <v>20</v>
       </c>
-      <c r="J133">
+      <c r="J133" s="1">
         <v>0</v>
       </c>
-      <c r="K133">
+      <c r="K133" s="1">
         <v>17.33333333333334</v>
       </c>
-      <c r="L133" t="s">
+      <c r="L133" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M133" t="s">
+      <c r="M133" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N133" t="s">
+      <c r="N133" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -49404,7 +49439,7 @@
       <c r="C134" t="s">
         <v>503</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="1">
         <v>30</v>
       </c>
       <c r="E134">
@@ -49416,22 +49451,22 @@
       <c r="G134">
         <v>0</v>
       </c>
-      <c r="I134">
+      <c r="I134" s="1">
         <v>7.620967741935483</v>
       </c>
-      <c r="J134">
+      <c r="J134" s="1">
         <v>4.655172413793104</v>
       </c>
-      <c r="K134">
+      <c r="K134" s="1">
         <v>18</v>
       </c>
-      <c r="L134" t="s">
+      <c r="L134" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M134" t="s">
+      <c r="M134" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N134" t="s">
+      <c r="N134" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -49442,7 +49477,7 @@
       <c r="C135" t="s">
         <v>504</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="1">
         <v>15</v>
       </c>
       <c r="E135">
@@ -49454,22 +49489,22 @@
       <c r="G135">
         <v>0</v>
       </c>
-      <c r="I135">
+      <c r="I135" s="1">
         <v>13.5</v>
       </c>
-      <c r="J135">
+      <c r="J135" s="1">
         <v>33.00000000000001</v>
       </c>
-      <c r="K135">
+      <c r="K135" s="1">
         <v>2.410714285714286</v>
       </c>
-      <c r="L135" t="s">
+      <c r="L135" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M135" t="s">
+      <c r="M135" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N135" t="s">
+      <c r="N135" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -49480,7 +49515,7 @@
       <c r="C136" t="s">
         <v>503</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="1">
         <v>15</v>
       </c>
       <c r="E136">
@@ -49492,22 +49527,22 @@
       <c r="G136">
         <v>0</v>
       </c>
-      <c r="I136">
+      <c r="I136" s="1">
         <v>1.546875</v>
       </c>
-      <c r="J136">
+      <c r="J136" s="1">
         <v>16.5</v>
       </c>
-      <c r="K136">
+      <c r="K136" s="1">
         <v>11.25</v>
       </c>
-      <c r="L136" t="s">
+      <c r="L136" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M136" t="s">
+      <c r="M136" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N136" t="s">
+      <c r="N136" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -49518,7 +49553,7 @@
       <c r="C137" t="s">
         <v>504</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="3">
         <v>68.33333333333333</v>
       </c>
       <c r="E137">
@@ -49530,22 +49565,22 @@
       <c r="G137">
         <v>33.33333333333333</v>
       </c>
-      <c r="I137">
+      <c r="I137" s="4">
         <v>75.33333333333334</v>
       </c>
-      <c r="J137">
+      <c r="J137" s="1">
         <v>1.438356164383562</v>
       </c>
-      <c r="K137">
+      <c r="K137" s="1">
         <v>11.25</v>
       </c>
-      <c r="L137" t="s">
+      <c r="L137" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M137" t="s">
+      <c r="M137" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N137" t="s">
+      <c r="N137" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -49556,7 +49591,7 @@
       <c r="C138" t="s">
         <v>503</v>
       </c>
-      <c r="D138">
+      <c r="D138" s="1">
         <v>40</v>
       </c>
       <c r="E138">
@@ -49568,22 +49603,22 @@
       <c r="G138">
         <v>0</v>
       </c>
-      <c r="I138">
+      <c r="I138" s="1">
         <v>6.923076923076923</v>
       </c>
-      <c r="J138">
+      <c r="J138" s="1">
         <v>12</v>
       </c>
-      <c r="K138">
+      <c r="K138" s="1">
         <v>6.101694915254237</v>
       </c>
-      <c r="L138" t="s">
+      <c r="L138" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M138" t="s">
+      <c r="M138" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N138" t="s">
+      <c r="N138" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -49594,7 +49629,7 @@
       <c r="C139" t="s">
         <v>504</v>
       </c>
-      <c r="D139">
+      <c r="D139" s="1">
         <v>30</v>
       </c>
       <c r="E139">
@@ -49606,22 +49641,22 @@
       <c r="G139">
         <v>0</v>
       </c>
-      <c r="I139">
+      <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139">
+      <c r="J139" s="1">
         <v>9.264705882352944</v>
       </c>
-      <c r="K139">
+      <c r="K139" s="1">
         <v>21.81818181818182</v>
       </c>
-      <c r="L139" t="s">
+      <c r="L139" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M139" t="s">
+      <c r="M139" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N139" t="s">
+      <c r="N139" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -49632,7 +49667,7 @@
       <c r="C140" t="s">
         <v>503</v>
       </c>
-      <c r="D140">
+      <c r="D140" s="1">
         <v>10</v>
       </c>
       <c r="E140">
@@ -49644,22 +49679,22 @@
       <c r="G140">
         <v>0</v>
       </c>
-      <c r="I140">
+      <c r="I140" s="1">
         <v>1.415094339622642</v>
       </c>
-      <c r="J140">
+      <c r="J140" s="3">
         <v>65</v>
       </c>
-      <c r="K140">
+      <c r="K140" s="1">
         <v>0</v>
       </c>
-      <c r="L140" t="s">
+      <c r="L140" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M140" t="s">
+      <c r="M140" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N140" t="s">
+      <c r="N140" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -49670,7 +49705,7 @@
       <c r="C141" t="s">
         <v>504</v>
       </c>
-      <c r="D141">
+      <c r="D141" s="1">
         <v>35</v>
       </c>
       <c r="E141">
@@ -49682,22 +49717,22 @@
       <c r="G141">
         <v>0</v>
       </c>
-      <c r="I141">
+      <c r="I141" s="1">
         <v>6.057692307692307</v>
       </c>
-      <c r="J141">
+      <c r="J141" s="1">
         <v>3.841463414634147</v>
       </c>
-      <c r="K141">
+      <c r="K141" s="1">
         <v>20.25</v>
       </c>
-      <c r="L141" t="s">
+      <c r="L141" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M141" t="s">
+      <c r="M141" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N141" t="s">
+      <c r="N141" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -49708,7 +49743,7 @@
       <c r="C142" t="s">
         <v>503</v>
       </c>
-      <c r="D142">
+      <c r="D142" s="1">
         <v>5</v>
       </c>
       <c r="E142">
@@ -49720,22 +49755,22 @@
       <c r="G142">
         <v>0</v>
       </c>
-      <c r="I142">
+      <c r="I142" s="1">
         <v>1.363636363636364</v>
       </c>
-      <c r="J142">
+      <c r="J142" s="1">
         <v>2.5</v>
       </c>
-      <c r="K142">
+      <c r="K142" s="1">
         <v>1.2890625</v>
       </c>
-      <c r="L142" t="s">
+      <c r="L142" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M142" t="s">
+      <c r="M142" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N142" t="s">
+      <c r="N142" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -49746,7 +49781,7 @@
       <c r="C143" t="s">
         <v>504</v>
       </c>
-      <c r="D143">
+      <c r="D143" s="4">
         <v>140</v>
       </c>
       <c r="E143">
@@ -49758,22 +49793,22 @@
       <c r="G143">
         <v>100</v>
       </c>
-      <c r="I143">
+      <c r="I143" s="3">
         <v>40.65040650406504</v>
       </c>
-      <c r="J143">
+      <c r="J143" s="3">
         <v>69.33333333333334</v>
       </c>
-      <c r="K143">
+      <c r="K143" s="4">
         <v>153.3333333333333</v>
       </c>
-      <c r="L143" t="s">
+      <c r="L143" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="M143" t="s">
+      <c r="M143" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N143" t="s">
+      <c r="N143" s="5" t="s">
         <v>35</v>
       </c>
     </row>
@@ -49784,7 +49819,7 @@
       <c r="C144" t="s">
         <v>503</v>
       </c>
-      <c r="D144">
+      <c r="D144" s="3">
         <v>55.00000000000001</v>
       </c>
       <c r="E144">
@@ -49796,22 +49831,22 @@
       <c r="G144">
         <v>0</v>
       </c>
-      <c r="I144">
+      <c r="I144" s="1">
         <v>5.689655172413794</v>
       </c>
-      <c r="J144">
+      <c r="J144" s="1">
         <v>13.30645161290322</v>
       </c>
-      <c r="K144">
+      <c r="K144" s="1">
         <v>11</v>
       </c>
-      <c r="L144" t="s">
+      <c r="L144" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M144" t="s">
+      <c r="M144" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N144" t="s">
+      <c r="N144" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -49822,7 +49857,7 @@
       <c r="C145" t="s">
         <v>504</v>
       </c>
-      <c r="D145">
+      <c r="D145" s="1">
         <v>40</v>
       </c>
       <c r="E145">
@@ -49834,22 +49869,22 @@
       <c r="G145">
         <v>0</v>
       </c>
-      <c r="I145">
+      <c r="I145" s="1">
         <v>12.22222222222222</v>
       </c>
-      <c r="J145">
+      <c r="J145" s="1">
         <v>8.000000000000002</v>
       </c>
-      <c r="K145">
+      <c r="K145" s="4">
         <v>124</v>
       </c>
-      <c r="L145" t="s">
+      <c r="L145" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M145" t="s">
+      <c r="M145" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N145" t="s">
+      <c r="N145" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -49860,7 +49895,7 @@
       <c r="C146" t="s">
         <v>503</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="1">
         <v>30</v>
       </c>
       <c r="E146">
@@ -49872,22 +49907,22 @@
       <c r="G146">
         <v>0</v>
       </c>
-      <c r="I146">
+      <c r="I146" s="3">
         <v>42.00000000000001</v>
       </c>
-      <c r="J146">
+      <c r="J146" s="3">
         <v>66.00000000000001</v>
       </c>
-      <c r="K146">
+      <c r="K146" s="1">
         <v>7.941176470588236</v>
       </c>
-      <c r="L146" t="s">
+      <c r="L146" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M146" t="s">
+      <c r="M146" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N146" t="s">
+      <c r="N146" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -49898,7 +49933,7 @@
       <c r="C147" t="s">
         <v>504</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="3">
         <v>45</v>
       </c>
       <c r="E147">
@@ -49910,22 +49945,22 @@
       <c r="G147">
         <v>0</v>
       </c>
-      <c r="I147">
+      <c r="I147" s="1">
         <v>13.5</v>
       </c>
-      <c r="J147">
+      <c r="J147" s="1">
         <v>1.062992125984252</v>
       </c>
-      <c r="K147">
+      <c r="K147" s="1">
         <v>0</v>
       </c>
-      <c r="L147" t="s">
+      <c r="L147" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M147" t="s">
+      <c r="M147" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N147" t="s">
+      <c r="N147" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -49936,7 +49971,7 @@
       <c r="C148" t="s">
         <v>503</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="1">
         <v>10</v>
       </c>
       <c r="E148">
@@ -49948,22 +49983,22 @@
       <c r="G148">
         <v>0</v>
       </c>
-      <c r="I148">
+      <c r="I148" s="1">
         <v>2.686567164179104</v>
       </c>
-      <c r="J148">
+      <c r="J148" s="1">
         <v>5</v>
       </c>
-      <c r="K148">
+      <c r="K148" s="1">
         <v>1.395348837209302</v>
       </c>
-      <c r="L148" t="s">
+      <c r="L148" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M148" t="s">
+      <c r="M148" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N148" t="s">
+      <c r="N148" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -49974,7 +50009,7 @@
       <c r="C149" t="s">
         <v>504</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="1">
         <v>20</v>
       </c>
       <c r="E149">
@@ -49986,22 +50021,22 @@
       <c r="G149">
         <v>0</v>
       </c>
-      <c r="I149">
+      <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149">
+      <c r="J149" s="3">
         <v>51.11111111111112</v>
       </c>
-      <c r="K149">
+      <c r="K149" s="1">
         <v>3.673469387755102</v>
       </c>
-      <c r="L149" t="s">
+      <c r="L149" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M149" t="s">
+      <c r="M149" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N149" t="s">
+      <c r="N149" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -50012,7 +50047,7 @@
       <c r="C150" t="s">
         <v>503</v>
       </c>
-      <c r="D150">
+      <c r="D150" s="3">
         <v>43.33333333333334</v>
       </c>
       <c r="E150">
@@ -50024,22 +50059,22 @@
       <c r="G150">
         <v>0</v>
       </c>
-      <c r="I150">
+      <c r="I150" s="1">
         <v>2</v>
       </c>
-      <c r="J150">
+      <c r="J150" s="1">
         <v>6.000000000000001</v>
       </c>
-      <c r="K150">
+      <c r="K150" s="1">
         <v>13.33333333333333</v>
       </c>
-      <c r="L150" t="s">
+      <c r="L150" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M150" t="s">
+      <c r="M150" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N150" t="s">
+      <c r="N150" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -50050,7 +50085,7 @@
       <c r="C151" t="s">
         <v>504</v>
       </c>
-      <c r="D151">
+      <c r="D151" s="1">
         <v>5</v>
       </c>
       <c r="E151">
@@ -50062,22 +50097,22 @@
       <c r="G151">
         <v>0</v>
       </c>
-      <c r="I151">
+      <c r="I151" s="1">
         <v>1.534090909090909</v>
       </c>
-      <c r="J151">
+      <c r="J151" s="1">
         <v>1.875</v>
       </c>
-      <c r="K151">
+      <c r="K151" s="1">
         <v>1.363636363636364</v>
       </c>
-      <c r="L151" t="s">
+      <c r="L151" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M151" t="s">
+      <c r="M151" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N151" t="s">
+      <c r="N151" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -50088,7 +50123,7 @@
       <c r="C152" t="s">
         <v>503</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="1">
         <v>30</v>
       </c>
       <c r="E152">
@@ -50100,22 +50135,22 @@
       <c r="G152">
         <v>0</v>
       </c>
-      <c r="I152">
+      <c r="I152" s="1">
         <v>3.461538461538462</v>
       </c>
-      <c r="J152">
+      <c r="J152" s="1">
         <v>21.81818181818182</v>
       </c>
-      <c r="K152">
+      <c r="K152" s="1">
         <v>9.246575342465755</v>
       </c>
-      <c r="L152" t="s">
+      <c r="L152" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M152" t="s">
+      <c r="M152" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N152" t="s">
+      <c r="N152" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -50126,7 +50161,7 @@
       <c r="C153" t="s">
         <v>504</v>
       </c>
-      <c r="D153">
+      <c r="D153" s="4">
         <v>73.33333333333333</v>
       </c>
       <c r="E153">
@@ -50138,22 +50173,22 @@
       <c r="G153">
         <v>33.33333333333333</v>
       </c>
-      <c r="I153">
+      <c r="I153" s="3">
         <v>60.00000000000001</v>
       </c>
-      <c r="J153">
+      <c r="J153" s="4">
         <v>348</v>
       </c>
-      <c r="K153">
+      <c r="K153" s="1">
         <v>35.52845528455285</v>
       </c>
-      <c r="L153" t="s">
+      <c r="L153" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M153" t="s">
+      <c r="M153" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N153" t="s">
+      <c r="N153" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -50164,7 +50199,7 @@
       <c r="C154" t="s">
         <v>503</v>
       </c>
-      <c r="D154">
+      <c r="D154" s="1">
         <v>35</v>
       </c>
       <c r="E154">
@@ -50176,22 +50211,22 @@
       <c r="G154">
         <v>0</v>
       </c>
-      <c r="I154">
+      <c r="I154" s="4">
         <v>206.5</v>
       </c>
-      <c r="J154">
+      <c r="J154" s="1">
         <v>21</v>
       </c>
-      <c r="K154">
+      <c r="K154" s="1">
         <v>4.952830188679245</v>
       </c>
-      <c r="L154" t="s">
+      <c r="L154" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M154" t="s">
+      <c r="M154" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N154" t="s">
+      <c r="N154" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -50202,7 +50237,7 @@
       <c r="C155" t="s">
         <v>504</v>
       </c>
-      <c r="D155">
+      <c r="D155" s="3">
         <v>48.33333333333333</v>
       </c>
       <c r="E155">
@@ -50214,22 +50249,22 @@
       <c r="G155">
         <v>33.33333333333333</v>
       </c>
-      <c r="I155">
+      <c r="I155" s="3">
         <v>43.63636363636365</v>
       </c>
-      <c r="J155">
+      <c r="J155" s="1">
         <v>2.109375</v>
       </c>
-      <c r="K155">
+      <c r="K155" s="3">
         <v>55.83333333333334</v>
       </c>
-      <c r="L155" t="s">
+      <c r="L155" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M155" t="s">
+      <c r="M155" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N155" t="s">
+      <c r="N155" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -50240,7 +50275,7 @@
       <c r="C156" t="s">
         <v>503</v>
       </c>
-      <c r="D156">
+      <c r="D156" s="1">
         <v>40</v>
       </c>
       <c r="E156">
@@ -50252,22 +50287,22 @@
       <c r="G156">
         <v>0</v>
       </c>
-      <c r="I156">
+      <c r="I156" s="4">
         <v>124</v>
       </c>
-      <c r="J156">
+      <c r="J156" s="3">
         <v>60.00000000000001</v>
       </c>
-      <c r="K156">
+      <c r="K156" s="4">
         <v>124</v>
       </c>
-      <c r="L156" t="s">
+      <c r="L156" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M156" t="s">
+      <c r="M156" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N156" t="s">
+      <c r="N156" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -50278,7 +50313,7 @@
       <c r="C157" t="s">
         <v>504</v>
       </c>
-      <c r="D157">
+      <c r="D157" s="1">
         <v>30</v>
       </c>
       <c r="E157">
@@ -50290,22 +50325,22 @@
       <c r="G157">
         <v>0</v>
       </c>
-      <c r="I157">
+      <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157">
+      <c r="J157" s="1">
         <v>7.258064516129034</v>
       </c>
-      <c r="K157">
+      <c r="K157" s="1">
         <v>3.907894736842105</v>
       </c>
-      <c r="L157" t="s">
+      <c r="L157" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M157" t="s">
+      <c r="M157" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N157" t="s">
+      <c r="N157" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -50316,7 +50351,7 @@
       <c r="C158" t="s">
         <v>503</v>
       </c>
-      <c r="D158">
+      <c r="D158" s="1">
         <v>5</v>
       </c>
       <c r="E158">
@@ -50328,22 +50363,22 @@
       <c r="G158">
         <v>0</v>
       </c>
-      <c r="I158">
+      <c r="I158" s="1">
         <v>0.8823529411764708</v>
       </c>
-      <c r="J158">
+      <c r="J158" s="1">
         <v>4.500000000000001</v>
       </c>
-      <c r="K158">
+      <c r="K158" s="1">
         <v>0.3461538461538461</v>
       </c>
-      <c r="L158" t="s">
+      <c r="L158" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M158" t="s">
+      <c r="M158" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N158" t="s">
+      <c r="N158" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -50354,7 +50389,7 @@
       <c r="C159" t="s">
         <v>504</v>
       </c>
-      <c r="D159">
+      <c r="D159" s="4">
         <v>75</v>
       </c>
       <c r="E159">
@@ -50366,22 +50401,22 @@
       <c r="G159">
         <v>0</v>
       </c>
-      <c r="I159">
+      <c r="I159" s="1">
         <v>19.39655172413793</v>
       </c>
-      <c r="J159">
+      <c r="J159" s="1">
         <v>17.30769230769231</v>
       </c>
-      <c r="K159">
+      <c r="K159" s="4">
         <v>165</v>
       </c>
-      <c r="L159" t="s">
+      <c r="L159" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M159" t="s">
+      <c r="M159" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N159" t="s">
+      <c r="N159" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -50392,7 +50427,7 @@
       <c r="C160" t="s">
         <v>503</v>
       </c>
-      <c r="D160">
+      <c r="D160" s="1">
         <v>40</v>
       </c>
       <c r="E160">
@@ -50404,22 +50439,22 @@
       <c r="G160">
         <v>0</v>
       </c>
-      <c r="I160">
+      <c r="I160" s="4">
         <v>112</v>
       </c>
-      <c r="J160">
+      <c r="J160" s="1">
         <v>6.614173228346456</v>
       </c>
-      <c r="K160">
+      <c r="K160" s="1">
         <v>8.597014925373132</v>
       </c>
-      <c r="L160" t="s">
+      <c r="L160" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M160" t="s">
+      <c r="M160" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N160" t="s">
+      <c r="N160" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -50430,7 +50465,7 @@
       <c r="C161" t="s">
         <v>504</v>
       </c>
-      <c r="D161">
+      <c r="D161" s="1">
         <v>10</v>
       </c>
       <c r="E161">
@@ -50442,22 +50477,22 @@
       <c r="G161">
         <v>0</v>
       </c>
-      <c r="I161">
+      <c r="I161" s="1">
         <v>5.785714285714286</v>
       </c>
-      <c r="J161">
+      <c r="J161" s="1">
         <v>1.395348837209302</v>
       </c>
-      <c r="K161">
+      <c r="K161" s="1">
         <v>10</v>
       </c>
-      <c r="L161" t="s">
+      <c r="L161" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M161" t="s">
+      <c r="M161" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N161" t="s">
+      <c r="N161" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -50468,7 +50503,7 @@
       <c r="C162" t="s">
         <v>503</v>
       </c>
-      <c r="D162">
+      <c r="D162" s="1">
         <v>15</v>
       </c>
       <c r="E162">
@@ -50480,22 +50515,22 @@
       <c r="G162">
         <v>0</v>
       </c>
-      <c r="I162">
+      <c r="I162" s="1">
         <v>6.000000000000001</v>
       </c>
-      <c r="J162">
+      <c r="J162" s="3">
         <v>66.00000000000001</v>
       </c>
-      <c r="K162">
+      <c r="K162" s="1">
         <v>2.25</v>
       </c>
-      <c r="L162" t="s">
+      <c r="L162" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M162" t="s">
+      <c r="M162" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N162" t="s">
+      <c r="N162" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -50506,7 +50541,7 @@
       <c r="C163" t="s">
         <v>504</v>
       </c>
-      <c r="D163">
+      <c r="D163" s="4">
         <v>86.66666666666666</v>
       </c>
       <c r="E163">
@@ -50518,22 +50553,22 @@
       <c r="G163">
         <v>66.66666666666666</v>
       </c>
-      <c r="I163">
+      <c r="I163" s="3">
         <v>48.88888888888889</v>
       </c>
-      <c r="J163">
+      <c r="J163" s="1">
         <v>4.000000000000001</v>
       </c>
-      <c r="K163">
+      <c r="K163" s="3">
         <v>43.33333333333333</v>
       </c>
-      <c r="L163" t="s">
+      <c r="L163" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="M163" t="s">
+      <c r="M163" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N163" t="s">
+      <c r="N163" s="5" t="s">
         <v>35</v>
       </c>
     </row>
@@ -50544,7 +50579,7 @@
       <c r="C164" t="s">
         <v>503</v>
       </c>
-      <c r="D164">
+      <c r="D164" s="1">
         <v>15</v>
       </c>
       <c r="E164">
@@ -50556,22 +50591,22 @@
       <c r="G164">
         <v>0</v>
       </c>
-      <c r="I164">
+      <c r="I164" s="1">
         <v>13.5</v>
       </c>
-      <c r="J164">
+      <c r="J164" s="1">
         <v>2.295918367346939</v>
       </c>
-      <c r="K164">
+      <c r="K164" s="3">
         <v>67.5</v>
       </c>
-      <c r="L164" t="s">
+      <c r="L164" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M164" t="s">
+      <c r="M164" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N164" t="s">
+      <c r="N164" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -50582,7 +50617,7 @@
       <c r="C165" t="s">
         <v>504</v>
       </c>
-      <c r="D165">
+      <c r="D165" s="3">
         <v>45.00000000000001</v>
       </c>
       <c r="E165">
@@ -50594,22 +50629,22 @@
       <c r="G165">
         <v>0</v>
       </c>
-      <c r="I165">
+      <c r="I165" s="4">
         <v>110.4545454545455</v>
       </c>
-      <c r="J165">
+      <c r="J165" s="1">
         <v>0</v>
       </c>
-      <c r="K165">
+      <c r="K165" s="1">
         <v>7.500000000000003</v>
       </c>
-      <c r="L165" t="s">
+      <c r="L165" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M165" t="s">
+      <c r="M165" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N165" t="s">
+      <c r="N165" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -50620,7 +50655,7 @@
       <c r="C166" t="s">
         <v>503</v>
       </c>
-      <c r="D166">
+      <c r="D166" s="1">
         <v>38.33333333333334</v>
       </c>
       <c r="E166">
@@ -50632,22 +50667,22 @@
       <c r="G166">
         <v>0</v>
       </c>
-      <c r="I166">
+      <c r="I166" s="3">
         <v>55.00000000000001</v>
       </c>
-      <c r="J166">
+      <c r="J166" s="1">
         <v>16.07723577235772</v>
       </c>
-      <c r="K166">
+      <c r="K166" s="3">
         <v>63.88888888888889</v>
       </c>
-      <c r="L166" t="s">
+      <c r="L166" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M166" t="s">
+      <c r="M166" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N166" t="s">
+      <c r="N166" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -50658,7 +50693,7 @@
       <c r="C167" t="s">
         <v>504</v>
       </c>
-      <c r="D167">
+      <c r="D167" s="1">
         <v>20</v>
       </c>
       <c r="E167">
@@ -50670,22 +50705,22 @@
       <c r="G167">
         <v>0</v>
       </c>
-      <c r="I167">
+      <c r="I167" s="1">
         <v>16</v>
       </c>
-      <c r="J167">
+      <c r="J167" s="1">
         <v>1.071428571428572</v>
       </c>
-      <c r="K167">
+      <c r="K167" s="1">
         <v>8.18181818181818</v>
       </c>
-      <c r="L167" t="s">
+      <c r="L167" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M167" t="s">
+      <c r="M167" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N167" t="s">
+      <c r="N167" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -50696,7 +50731,7 @@
       <c r="C168" t="s">
         <v>503</v>
       </c>
-      <c r="D168">
+      <c r="D168" s="1">
         <v>20</v>
       </c>
       <c r="E168">
@@ -50708,22 +50743,22 @@
       <c r="G168">
         <v>0</v>
       </c>
-      <c r="I168">
+      <c r="I168" s="1">
         <v>10</v>
       </c>
-      <c r="J168">
+      <c r="J168" s="1">
         <v>28</v>
       </c>
-      <c r="K168">
+      <c r="K168" s="1">
         <v>0</v>
       </c>
-      <c r="L168" t="s">
+      <c r="L168" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M168" t="s">
+      <c r="M168" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N168" t="s">
+      <c r="N168" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -50734,7 +50769,7 @@
       <c r="C169" t="s">
         <v>504</v>
       </c>
-      <c r="D169">
+      <c r="D169" s="3">
         <v>50</v>
       </c>
       <c r="E169">
@@ -50746,22 +50781,22 @@
       <c r="G169">
         <v>0</v>
       </c>
-      <c r="I169">
+      <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169">
+      <c r="J169" s="1">
         <v>5.88235294117647</v>
       </c>
-      <c r="K169">
+      <c r="K169" s="1">
         <v>15</v>
       </c>
-      <c r="L169" t="s">
+      <c r="L169" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M169" t="s">
+      <c r="M169" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N169" t="s">
+      <c r="N169" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -50772,7 +50807,7 @@
       <c r="C170" t="s">
         <v>503</v>
       </c>
-      <c r="D170">
+      <c r="D170" s="1">
         <v>23.33333333333334</v>
       </c>
       <c r="E170">
@@ -50784,22 +50819,22 @@
       <c r="G170">
         <v>0</v>
       </c>
-      <c r="I170">
+      <c r="I170" s="1">
         <v>12</v>
       </c>
-      <c r="J170">
+      <c r="J170" s="1">
         <v>14.20175438596491</v>
       </c>
-      <c r="K170">
+      <c r="K170" s="3">
         <v>65</v>
       </c>
-      <c r="L170" t="s">
+      <c r="L170" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M170" t="s">
+      <c r="M170" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N170" t="s">
+      <c r="N170" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -50810,7 +50845,7 @@
       <c r="C171" t="s">
         <v>504</v>
       </c>
-      <c r="D171">
+      <c r="D171" s="1">
         <v>20</v>
       </c>
       <c r="E171">
@@ -50822,22 +50857,22 @@
       <c r="G171">
         <v>0</v>
       </c>
-      <c r="I171">
+      <c r="I171" s="1">
         <v>1.451612903225807</v>
       </c>
-      <c r="J171">
+      <c r="J171" s="4">
         <v>118</v>
       </c>
-      <c r="K171">
+      <c r="K171" s="1">
         <v>18</v>
       </c>
-      <c r="L171" t="s">
+      <c r="L171" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M171" t="s">
+      <c r="M171" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N171" t="s">
+      <c r="N171" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -50848,7 +50883,7 @@
       <c r="C172" t="s">
         <v>503</v>
       </c>
-      <c r="D172">
+      <c r="D172" s="4">
         <v>83.33333333333333</v>
       </c>
       <c r="E172">
@@ -50860,22 +50895,22 @@
       <c r="G172">
         <v>33.33333333333333</v>
       </c>
-      <c r="I172">
+      <c r="I172" s="3">
         <v>55.00000000000001</v>
       </c>
-      <c r="J172">
+      <c r="J172" s="1">
         <v>38.64829396325459</v>
       </c>
-      <c r="K172">
+      <c r="K172" s="1">
         <v>3.515624999999999</v>
       </c>
-      <c r="L172" t="s">
+      <c r="L172" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M172" t="s">
+      <c r="M172" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="N172" t="s">
+      <c r="N172" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -50886,7 +50921,7 @@
       <c r="C173" t="s">
         <v>504</v>
       </c>
-      <c r="D173">
+      <c r="D173" s="4">
         <v>78.33333333333331</v>
       </c>
       <c r="E173">
@@ -50898,22 +50933,22 @@
       <c r="G173">
         <v>33.33333333333333</v>
       </c>
-      <c r="I173">
+      <c r="I173" s="1">
         <v>13.99390243902439</v>
       </c>
-      <c r="J173">
+      <c r="J173" s="1">
         <v>9.671641791044774</v>
       </c>
-      <c r="K173">
+      <c r="K173" s="3">
         <v>40.29427083333333</v>
       </c>
-      <c r="L173" t="s">
+      <c r="L173" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M173" t="s">
+      <c r="M173" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N173" t="s">
+      <c r="N173" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -50924,7 +50959,7 @@
       <c r="C174" t="s">
         <v>503</v>
       </c>
-      <c r="D174">
+      <c r="D174" s="3">
         <v>50</v>
       </c>
       <c r="E174">
@@ -50936,22 +50971,22 @@
       <c r="G174">
         <v>0</v>
       </c>
-      <c r="I174">
+      <c r="I174" s="1">
         <v>6.164383561643835</v>
       </c>
-      <c r="J174">
+      <c r="J174" s="1">
         <v>20</v>
       </c>
-      <c r="K174">
+      <c r="K174" s="1">
         <v>8.490566037735849</v>
       </c>
-      <c r="L174" t="s">
+      <c r="L174" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M174" t="s">
+      <c r="M174" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N174" t="s">
+      <c r="N174" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -50962,7 +50997,7 @@
       <c r="C175" t="s">
         <v>504</v>
       </c>
-      <c r="D175">
+      <c r="D175" s="3">
         <v>48.33333333333333</v>
       </c>
       <c r="E175">
@@ -50974,22 +51009,22 @@
       <c r="G175">
         <v>33.33333333333333</v>
       </c>
-      <c r="I175">
+      <c r="I175" s="3">
         <v>66.33333333333333</v>
       </c>
-      <c r="J175">
+      <c r="J175" s="1">
         <v>11.25</v>
       </c>
-      <c r="K175">
+      <c r="K175" s="3">
         <v>46.50000000000001</v>
       </c>
-      <c r="L175" t="s">
+      <c r="L175" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M175" t="s">
+      <c r="M175" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N175" t="s">
+      <c r="N175" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -51000,7 +51035,7 @@
       <c r="C176" t="s">
         <v>503</v>
       </c>
-      <c r="D176">
+      <c r="D176" s="4">
         <v>71.66666666666666</v>
       </c>
       <c r="E176">
@@ -51012,22 +51047,22 @@
       <c r="G176">
         <v>33.33333333333333</v>
       </c>
-      <c r="I176">
+      <c r="I176" s="1">
         <v>18.33333333333334</v>
       </c>
-      <c r="J176">
+      <c r="J176" s="1">
         <v>0</v>
       </c>
-      <c r="K176">
+      <c r="K176" s="4">
         <v>94.6969696969697</v>
       </c>
-      <c r="L176" t="s">
+      <c r="L176" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M176" t="s">
+      <c r="M176" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N176" t="s">
+      <c r="N176" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -51038,7 +51073,7 @@
       <c r="C177" t="s">
         <v>504</v>
       </c>
-      <c r="D177">
+      <c r="D177" s="3">
         <v>53.33333333333333</v>
       </c>
       <c r="E177">
@@ -51050,22 +51085,22 @@
       <c r="G177">
         <v>33.33333333333333</v>
       </c>
-      <c r="I177">
+      <c r="I177" s="1">
         <v>3</v>
       </c>
-      <c r="J177">
+      <c r="J177" s="3">
         <v>68</v>
       </c>
-      <c r="K177">
+      <c r="K177" s="4">
         <v>85.33333333333333</v>
       </c>
-      <c r="L177" t="s">
+      <c r="L177" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M177" t="s">
+      <c r="M177" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N177" t="s">
+      <c r="N177" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -51076,7 +51111,7 @@
       <c r="C178" t="s">
         <v>503</v>
       </c>
-      <c r="D178">
+      <c r="D178" s="1">
         <v>25</v>
       </c>
       <c r="E178">
@@ -51088,22 +51123,22 @@
       <c r="G178">
         <v>0</v>
       </c>
-      <c r="I178">
+      <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178">
+      <c r="J178" s="1">
         <v>4.261363636363636</v>
       </c>
-      <c r="K178">
+      <c r="K178" s="1">
         <v>3.879310344827586</v>
       </c>
-      <c r="L178" t="s">
+      <c r="L178" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M178" t="s">
+      <c r="M178" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N178" t="s">
+      <c r="N178" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -51114,7 +51149,7 @@
       <c r="C179" t="s">
         <v>504</v>
       </c>
-      <c r="D179">
+      <c r="D179" s="4">
         <v>116.6666666666667</v>
       </c>
       <c r="E179">
@@ -51126,22 +51161,22 @@
       <c r="G179">
         <v>66.66666666666666</v>
       </c>
-      <c r="I179">
+      <c r="I179" s="4">
         <v>73.51190476190477</v>
       </c>
-      <c r="J179">
+      <c r="J179" s="4">
         <v>205</v>
       </c>
-      <c r="K179">
+      <c r="K179" s="1">
         <v>38.50574712643678</v>
       </c>
-      <c r="L179" t="s">
+      <c r="L179" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M179" t="s">
+      <c r="M179" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N179" t="s">
+      <c r="N179" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -51152,7 +51187,7 @@
       <c r="C180" t="s">
         <v>503</v>
       </c>
-      <c r="D180">
+      <c r="D180" s="1">
         <v>20</v>
       </c>
       <c r="E180">
@@ -51164,22 +51199,22 @@
       <c r="G180">
         <v>0</v>
       </c>
-      <c r="I180">
+      <c r="I180" s="3">
         <v>44.00000000000001</v>
       </c>
-      <c r="J180">
+      <c r="J180" s="1">
         <v>18</v>
       </c>
-      <c r="K180">
+      <c r="K180" s="4">
         <v>204</v>
       </c>
-      <c r="L180" t="s">
+      <c r="L180" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M180" t="s">
+      <c r="M180" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N180" t="s">
+      <c r="N180" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -51190,7 +51225,7 @@
       <c r="C181" t="s">
         <v>504</v>
       </c>
-      <c r="D181">
+      <c r="D181" s="3">
         <v>48.33333333333333</v>
       </c>
       <c r="E181">
@@ -51202,22 +51237,22 @@
       <c r="G181">
         <v>33.33333333333333</v>
       </c>
-      <c r="I181">
+      <c r="I181" s="1">
         <v>4.821428571428572</v>
       </c>
-      <c r="J181">
+      <c r="J181" s="1">
         <v>1.5</v>
       </c>
-      <c r="K181">
+      <c r="K181" s="4">
         <v>70.15151515151516</v>
       </c>
-      <c r="L181" t="s">
+      <c r="L181" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M181" t="s">
+      <c r="M181" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N181" t="s">
+      <c r="N181" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -51228,7 +51263,7 @@
       <c r="C182" t="s">
         <v>503</v>
       </c>
-      <c r="D182">
+      <c r="D182" s="1">
         <v>20</v>
       </c>
       <c r="E182">
@@ -51240,22 +51275,22 @@
       <c r="G182">
         <v>0</v>
       </c>
-      <c r="I182">
+      <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182">
+      <c r="J182" s="1">
         <v>1.935483870967742</v>
       </c>
-      <c r="K182">
+      <c r="K182" s="1">
         <v>6.428571428571428</v>
       </c>
-      <c r="L182" t="s">
+      <c r="L182" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M182" t="s">
+      <c r="M182" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N182" t="s">
+      <c r="N182" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -51266,7 +51301,7 @@
       <c r="C183" t="s">
         <v>504</v>
       </c>
-      <c r="D183">
+      <c r="D183" s="1">
         <v>5</v>
       </c>
       <c r="E183">
@@ -51278,22 +51313,22 @@
       <c r="G183">
         <v>0</v>
       </c>
-      <c r="I183">
+      <c r="I183" s="1">
         <v>1.071428571428571</v>
       </c>
-      <c r="J183">
+      <c r="J183" s="1">
         <v>5</v>
       </c>
-      <c r="K183">
+      <c r="K183" s="1">
         <v>9</v>
       </c>
-      <c r="L183" t="s">
+      <c r="L183" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M183" t="s">
+      <c r="M183" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N183" t="s">
+      <c r="N183" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -51304,7 +51339,7 @@
       <c r="C184" t="s">
         <v>503</v>
       </c>
-      <c r="D184">
+      <c r="D184" s="1">
         <v>35</v>
       </c>
       <c r="E184">
@@ -51316,22 +51351,22 @@
       <c r="G184">
         <v>0</v>
       </c>
-      <c r="I184">
+      <c r="I184" s="4">
         <v>77.00000000000001</v>
       </c>
-      <c r="J184">
+      <c r="J184" s="1">
         <v>7.000000000000001</v>
       </c>
-      <c r="K184">
+      <c r="K184" s="1">
         <v>10.5</v>
       </c>
-      <c r="L184" t="s">
+      <c r="L184" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M184" t="s">
+      <c r="M184" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N184" t="s">
+      <c r="N184" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -51342,7 +51377,7 @@
       <c r="C185" t="s">
         <v>504</v>
       </c>
-      <c r="D185">
+      <c r="D185" s="4">
         <v>143.3333333333333</v>
       </c>
       <c r="E185">
@@ -51354,22 +51389,22 @@
       <c r="G185">
         <v>33.33333333333333</v>
       </c>
-      <c r="I185">
+      <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185">
+      <c r="J185" s="4">
         <v>133.3333333333333</v>
       </c>
-      <c r="K185">
+      <c r="K185" s="1">
         <v>3.488372093023255</v>
       </c>
-      <c r="L185" t="s">
+      <c r="L185" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M185" t="s">
+      <c r="M185" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="N185" t="s">
+      <c r="N185" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -51380,7 +51415,7 @@
       <c r="C186" t="s">
         <v>503</v>
       </c>
-      <c r="D186">
+      <c r="D186" s="1">
         <v>10</v>
       </c>
       <c r="E186">
@@ -51392,22 +51427,22 @@
       <c r="G186">
         <v>0</v>
       </c>
-      <c r="I186">
+      <c r="I186" s="1">
         <v>1.928571428571428</v>
       </c>
-      <c r="J186">
+      <c r="J186" s="1">
         <v>9</v>
       </c>
-      <c r="K186">
+      <c r="K186" s="1">
         <v>8.000000000000002</v>
       </c>
-      <c r="L186" t="s">
+      <c r="L186" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M186" t="s">
+      <c r="M186" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N186" t="s">
+      <c r="N186" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -51418,7 +51453,7 @@
       <c r="C187" t="s">
         <v>504</v>
       </c>
-      <c r="D187">
+      <c r="D187" s="1">
         <v>20</v>
       </c>
       <c r="E187">
@@ -51430,22 +51465,22 @@
       <c r="G187">
         <v>0</v>
       </c>
-      <c r="I187">
+      <c r="I187" s="1">
         <v>14.54545454545455</v>
       </c>
-      <c r="J187">
+      <c r="J187" s="1">
         <v>18</v>
       </c>
-      <c r="K187">
+      <c r="K187" s="1">
         <v>4.615384615384616</v>
       </c>
-      <c r="L187" t="s">
+      <c r="L187" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M187" t="s">
+      <c r="M187" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N187" t="s">
+      <c r="N187" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -51456,7 +51491,7 @@
       <c r="C188" t="s">
         <v>503</v>
       </c>
-      <c r="D188">
+      <c r="D188" s="1">
         <v>10</v>
       </c>
       <c r="E188">
@@ -51468,22 +51503,22 @@
       <c r="G188">
         <v>0</v>
       </c>
-      <c r="I188">
+      <c r="I188" s="1">
         <v>2</v>
       </c>
-      <c r="J188">
+      <c r="J188" s="1">
         <v>22</v>
       </c>
-      <c r="K188">
+      <c r="K188" s="1">
         <v>4.125000000000001</v>
       </c>
-      <c r="L188" t="s">
+      <c r="L188" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M188" t="s">
+      <c r="M188" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N188" t="s">
+      <c r="N188" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -51494,7 +51529,7 @@
       <c r="C189" t="s">
         <v>504</v>
       </c>
-      <c r="D189">
+      <c r="D189" s="4">
         <v>128.3333333333333</v>
       </c>
       <c r="E189">
@@ -51506,22 +51541,22 @@
       <c r="G189">
         <v>33.33333333333333</v>
       </c>
-      <c r="I189">
+      <c r="I189" s="4">
         <v>238.7878787878788</v>
       </c>
-      <c r="J189">
+      <c r="J189" s="4">
         <v>205.4545454545455</v>
       </c>
-      <c r="K189">
+      <c r="K189" s="1">
         <v>0</v>
       </c>
-      <c r="L189" t="s">
+      <c r="L189" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M189" t="s">
+      <c r="M189" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N189" t="s">
+      <c r="N189" s="2" t="s">
         <v>35</v>
       </c>
     </row>
